--- a/research/traditional_assets/database/data/kuwait/kuwait_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_environmental_waste_services.xlsx
@@ -588,118 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.008799999999999999</v>
+        <v>-0.04935</v>
       </c>
       <c r="G2">
-        <v>0.07268691588785046</v>
+        <v>0.05836065573770492</v>
       </c>
       <c r="H2">
-        <v>0.07268691588785046</v>
+        <v>0.05836065573770492</v>
       </c>
       <c r="I2">
-        <v>-0.06524532710280373</v>
+        <v>-0.09901639344262295</v>
       </c>
       <c r="J2">
-        <v>-0.06524532710280373</v>
+        <v>-0.09901639344262295</v>
       </c>
       <c r="K2">
-        <v>-14.84</v>
+        <v>-13.73</v>
       </c>
       <c r="L2">
-        <v>-0.0866822429906542</v>
+        <v>-0.09003278688524591</v>
       </c>
       <c r="M2">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0009749303621169918</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.004716981132075472</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0009749303621169918</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.004716981132075472</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>29.4</v>
+        <v>21.55</v>
       </c>
       <c r="V2">
-        <v>0.4094707520891365</v>
+        <v>0.5441919191919193</v>
       </c>
       <c r="W2">
-        <v>-0.1586147228415052</v>
+        <v>-0.08411864887879647</v>
       </c>
       <c r="X2">
-        <v>0.1416874517413886</v>
+        <v>0.3486799006077266</v>
       </c>
       <c r="Y2">
-        <v>-0.3003021745828938</v>
+        <v>-0.4327985494865231</v>
       </c>
       <c r="Z2">
-        <v>0.6478223029477428</v>
+        <v>0.550839804948528</v>
       </c>
       <c r="AA2">
-        <v>-0.06339040001965698</v>
+        <v>-0.05213494631803851</v>
       </c>
       <c r="AB2">
-        <v>0.06099385802170013</v>
+        <v>0.1074234962225213</v>
       </c>
       <c r="AC2">
-        <v>-0.1243842580413571</v>
+        <v>-0.1595584425405598</v>
       </c>
       <c r="AD2">
-        <v>191.4</v>
+        <v>200.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>191.4</v>
+        <v>200.6</v>
       </c>
       <c r="AG2">
-        <v>162</v>
+        <v>179.05</v>
       </c>
       <c r="AH2">
-        <v>0.7272036474164134</v>
+        <v>0.8351373855120733</v>
       </c>
       <c r="AI2">
-        <v>0.569303985722784</v>
+        <v>0.6102829327654397</v>
       </c>
       <c r="AJ2">
-        <v>0.6928999144568007</v>
+        <v>0.818888634804482</v>
       </c>
       <c r="AK2">
-        <v>0.5280312907431551</v>
+        <v>0.582939931629497</v>
       </c>
       <c r="AL2">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="AM2">
-        <v>2.841</v>
+        <v>2.958</v>
       </c>
       <c r="AN2">
-        <v>16.84859154929578</v>
+        <v>23.38813104815203</v>
       </c>
       <c r="AO2">
-        <v>-3.773648648648648</v>
+        <v>-4.88673139158576</v>
       </c>
       <c r="AP2">
-        <v>14.26056338028169</v>
+        <v>20.87559752827329</v>
       </c>
       <c r="AQ2">
-        <v>-3.931714185146074</v>
+        <v>-5.104800540906018</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Cleaning Co. (K.S.C.P) (KWSE:CLEANING)</t>
+          <t>Metal and Recycling Company K.S.C. (Public) (KWSE:MRC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,118 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0342</v>
+        <v>-0.0555</v>
       </c>
       <c r="G3">
-        <v>0.1127493495229835</v>
+        <v>-0.08955223880597014</v>
       </c>
       <c r="H3">
-        <v>0.1127493495229835</v>
+        <v>-0.08955223880597014</v>
       </c>
       <c r="I3">
-        <v>-0.07406764960971378</v>
+        <v>-0.04228855721393034</v>
       </c>
       <c r="J3">
-        <v>-0.07406764960971378</v>
+        <v>-0.04228855721393034</v>
       </c>
       <c r="K3">
-        <v>-6.32</v>
+        <v>-1.33</v>
       </c>
       <c r="L3">
-        <v>-0.05481352992194276</v>
+        <v>-0.03308457711442786</v>
       </c>
       <c r="M3">
-        <v>0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.001609195402298851</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.01107594936708861</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.001609195402298851</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.01107594936708861</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="V3">
-        <v>0.3333333333333333</v>
+        <v>1.08843537414966</v>
       </c>
       <c r="W3">
-        <v>-0.05587975243147657</v>
+        <v>-0.05384615384615385</v>
       </c>
       <c r="X3">
-        <v>0.1929485102198176</v>
+        <v>0.2295495300811207</v>
       </c>
       <c r="Y3">
-        <v>-0.2488282626512942</v>
+        <v>-0.2833956839272745</v>
       </c>
       <c r="Z3">
-        <v>0.4902210884353742</v>
+        <v>1.156834532374101</v>
       </c>
       <c r="AA3">
-        <v>-0.03630952380952381</v>
+        <v>-0.04892086330935252</v>
       </c>
       <c r="AB3">
-        <v>0.05997016651696749</v>
+        <v>0.1069395171358437</v>
       </c>
       <c r="AC3">
-        <v>-0.09627969032649131</v>
+        <v>-0.1558603804451962</v>
       </c>
       <c r="AD3">
-        <v>165.1</v>
+        <v>34.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>165.1</v>
+        <v>34.1</v>
       </c>
       <c r="AG3">
-        <v>150.6</v>
+        <v>18.1</v>
       </c>
       <c r="AH3">
-        <v>0.7914669223394055</v>
+        <v>0.6987704918032788</v>
       </c>
       <c r="AI3">
-        <v>0.5955988455988456</v>
+        <v>0.5182370820668694</v>
       </c>
       <c r="AJ3">
-        <v>0.7758887171561051</v>
+        <v>0.551829268292683</v>
       </c>
       <c r="AK3">
-        <v>0.5732775028549677</v>
+        <v>0.3634538152610442</v>
       </c>
       <c r="AL3">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="AM3">
-        <v>1.597</v>
+        <v>1.144</v>
       </c>
       <c r="AN3">
-        <v>13</v>
+        <v>-84.61538461538461</v>
       </c>
       <c r="AO3">
-        <v>-5.175757575757576</v>
+        <v>-1.349206349206349</v>
       </c>
       <c r="AP3">
-        <v>11.85826771653543</v>
+        <v>-44.91315136476427</v>
       </c>
       <c r="AQ3">
-        <v>-5.347526612398246</v>
+        <v>-1.486013986013986</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Metal and Recycling Company K.S.C. (Public) (KWSE:MRC)</t>
+          <t>National Cleaning Co. (K.S.C.P) (KWSE:CLEANING)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0518</v>
+        <v>-0.0432</v>
       </c>
       <c r="G4">
-        <v>-0.009946332737030413</v>
+        <v>0.1113089937666964</v>
       </c>
       <c r="H4">
-        <v>-0.009946332737030413</v>
+        <v>0.1113089937666964</v>
       </c>
       <c r="I4">
-        <v>-0.04704830053667263</v>
+        <v>-0.1193232413178985</v>
       </c>
       <c r="J4">
-        <v>-0.04704830053667263</v>
+        <v>-0.1193232413178985</v>
       </c>
       <c r="K4">
-        <v>-8.52</v>
+        <v>-12.4</v>
       </c>
       <c r="L4">
-        <v>-0.1524150268336315</v>
+        <v>-0.1104185218165628</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,73 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>14.9</v>
+        <v>5.55</v>
       </c>
       <c r="V4">
-        <v>0.5265017667844523</v>
+        <v>0.2228915662650602</v>
       </c>
       <c r="W4">
-        <v>-0.2613496932515337</v>
+        <v>-0.1143911439114391</v>
       </c>
       <c r="X4">
-        <v>0.09042639326295952</v>
+        <v>0.4678102711343324</v>
       </c>
       <c r="Y4">
-        <v>-0.3517760865144933</v>
+        <v>-0.5822014150457715</v>
       </c>
       <c r="Z4">
-        <v>1.922944616443068</v>
+        <v>0.4638579099545642</v>
       </c>
       <c r="AA4">
-        <v>-0.09047127622979016</v>
+        <v>-0.0553490293267245</v>
       </c>
       <c r="AB4">
-        <v>0.06201754952643276</v>
+        <v>0.1079074753091989</v>
       </c>
       <c r="AC4">
-        <v>-0.1524888257562229</v>
+        <v>-0.1632565046359234</v>
       </c>
       <c r="AD4">
-        <v>26.3</v>
+        <v>166.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>26.3</v>
+        <v>166.5</v>
       </c>
       <c r="AG4">
-        <v>11.4</v>
+        <v>160.95</v>
       </c>
       <c r="AH4">
-        <v>0.4816849816849817</v>
+        <v>0.8699059561128526</v>
       </c>
       <c r="AI4">
-        <v>0.4457627118644068</v>
+        <v>0.6333206542411564</v>
       </c>
       <c r="AJ4">
-        <v>0.2871536523929471</v>
+        <v>0.8660209846650524</v>
       </c>
       <c r="AK4">
-        <v>0.2585034013605442</v>
+        <v>0.6254128618612783</v>
       </c>
       <c r="AL4">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="AM4">
-        <v>1.244</v>
+        <v>1.814</v>
       </c>
       <c r="AN4">
-        <v>-19.62686567164179</v>
+        <v>18.54120267260579</v>
       </c>
       <c r="AO4">
-        <v>-2.007633587786259</v>
+        <v>-7.3224043715847</v>
       </c>
       <c r="AP4">
-        <v>-8.507462686567164</v>
+        <v>17.92316258351893</v>
       </c>
       <c r="AQ4">
-        <v>-2.114147909967846</v>
+        <v>-7.386990077177508</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_environmental_waste_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kwse_mrc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.04935</v>
+        <v>-0.0507</v>
       </c>
       <c r="G2">
-        <v>0.05836065573770492</v>
+        <v>0.07989521938441388</v>
       </c>
       <c r="H2">
-        <v>0.05836065573770492</v>
+        <v>0.07989521938441388</v>
       </c>
       <c r="I2">
-        <v>-0.09901639344262295</v>
+        <v>-0.02429600523903078</v>
       </c>
       <c r="J2">
-        <v>-0.09901639344262295</v>
+        <v>-0.02422476695206448</v>
       </c>
       <c r="K2">
-        <v>-13.73</v>
+        <v>-0.6499999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.09003278688524591</v>
+        <v>-0.004256712508185986</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>21.55</v>
+        <v>16.03</v>
       </c>
       <c r="V2">
-        <v>0.5441919191919193</v>
+        <v>0.2985102420856611</v>
       </c>
       <c r="W2">
-        <v>-0.08411864887879647</v>
+        <v>0.03098964535088638</v>
       </c>
       <c r="X2">
-        <v>0.3486799006077266</v>
+        <v>0.1985256849087155</v>
       </c>
       <c r="Y2">
-        <v>-0.4327985494865231</v>
+        <v>-0.1675360395578291</v>
       </c>
       <c r="Z2">
-        <v>0.550839804948528</v>
+        <v>0.5513829710406587</v>
       </c>
       <c r="AA2">
-        <v>-0.05213494631803851</v>
+        <v>0.006490592001186839</v>
       </c>
       <c r="AB2">
-        <v>0.1074234962225213</v>
+        <v>0.08700211160563345</v>
       </c>
       <c r="AC2">
-        <v>-0.1595584425405598</v>
+        <v>-0.08051151960444662</v>
       </c>
       <c r="AD2">
-        <v>200.6</v>
+        <v>167.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>200.6</v>
+        <v>167.8</v>
       </c>
       <c r="AG2">
-        <v>179.05</v>
+        <v>151.77</v>
       </c>
       <c r="AH2">
-        <v>0.8351373855120733</v>
+        <v>0.7575620767494358</v>
       </c>
       <c r="AI2">
-        <v>0.6102829327654397</v>
+        <v>0.5877408056042032</v>
       </c>
       <c r="AJ2">
-        <v>0.818888634804482</v>
+        <v>0.7386479778069791</v>
       </c>
       <c r="AK2">
-        <v>0.582939931629497</v>
+        <v>0.5632166846031098</v>
       </c>
       <c r="AL2">
-        <v>3.09</v>
+        <v>4.15</v>
       </c>
       <c r="AM2">
-        <v>2.958</v>
+        <v>3.664000000000001</v>
       </c>
       <c r="AN2">
-        <v>23.38813104815203</v>
+        <v>8.522092432706957</v>
       </c>
       <c r="AO2">
-        <v>-4.88673139158576</v>
+        <v>-0.8939759036144578</v>
       </c>
       <c r="AP2">
-        <v>20.87559752827329</v>
+        <v>7.707973590655155</v>
       </c>
       <c r="AQ2">
-        <v>-5.104800540906018</v>
+        <v>-1.012554585152838</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0555</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.08955223880597014</v>
+        <v>0.03640776699029126</v>
       </c>
       <c r="H3">
-        <v>-0.08955223880597014</v>
+        <v>0.03640776699029126</v>
       </c>
       <c r="I3">
-        <v>-0.04228855721393034</v>
+        <v>0.03300970873786408</v>
       </c>
       <c r="J3">
-        <v>-0.04228855721393034</v>
+        <v>0.03281613328538895</v>
       </c>
       <c r="K3">
-        <v>-1.33</v>
+        <v>2.06</v>
       </c>
       <c r="L3">
-        <v>-0.03308457711442786</v>
+        <v>0.05</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>16</v>
+        <v>4.73</v>
       </c>
       <c r="V3">
-        <v>1.08843537414966</v>
+        <v>0.1946502057613169</v>
       </c>
       <c r="W3">
-        <v>-0.05384615384615385</v>
+        <v>0.0911504424778761</v>
       </c>
       <c r="X3">
-        <v>0.2295495300811207</v>
+        <v>0.1368450664779488</v>
       </c>
       <c r="Y3">
-        <v>-0.2833956839272745</v>
+        <v>-0.04569462400007274</v>
       </c>
       <c r="Z3">
-        <v>1.156834532374101</v>
+        <v>1.045950748921046</v>
       </c>
       <c r="AA3">
-        <v>-0.04892086330935252</v>
+        <v>0.03432405918654544</v>
       </c>
       <c r="AB3">
-        <v>0.1069395171358437</v>
+        <v>0.08649729442296494</v>
       </c>
       <c r="AC3">
-        <v>-0.1558603804451962</v>
+        <v>-0.05217323523641951</v>
       </c>
       <c r="AD3">
-        <v>34.1</v>
+        <v>33.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>34.1</v>
+        <v>33.3</v>
       </c>
       <c r="AG3">
-        <v>18.1</v>
+        <v>28.57</v>
       </c>
       <c r="AH3">
-        <v>0.6987704918032788</v>
+        <v>0.578125</v>
       </c>
       <c r="AI3">
-        <v>0.5182370820668694</v>
+        <v>0.502262443438914</v>
       </c>
       <c r="AJ3">
-        <v>0.551829268292683</v>
+        <v>0.5403820692264043</v>
       </c>
       <c r="AK3">
-        <v>0.3634538152610442</v>
+        <v>0.4640246873477343</v>
       </c>
       <c r="AL3">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="AM3">
-        <v>1.144</v>
+        <v>1.58</v>
       </c>
       <c r="AN3">
-        <v>-84.61538461538461</v>
+        <v>11.52249134948097</v>
       </c>
       <c r="AO3">
-        <v>-1.349206349206349</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="AP3">
-        <v>-44.91315136476427</v>
+        <v>9.885813148788925</v>
       </c>
       <c r="AQ3">
-        <v>-1.486013986013986</v>
+        <v>0.8607594936708862</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +837,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Cleaning Co. (K.S.C.P) (KWSE:CLEANING)</t>
+          <t>National Cleaning Company K.P.S.C. (KWSE:CLEANING)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +846,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0432</v>
+        <v>-0.0246</v>
       </c>
       <c r="G4">
-        <v>0.1113089937666964</v>
+        <v>0.09596412556053811</v>
       </c>
       <c r="H4">
-        <v>0.1113089937666964</v>
+        <v>0.09596412556053811</v>
       </c>
       <c r="I4">
-        <v>-0.1193232413178985</v>
+        <v>-0.04547085201793722</v>
       </c>
       <c r="J4">
-        <v>-0.1193232413178985</v>
+        <v>-0.04547085201793722</v>
       </c>
       <c r="K4">
-        <v>-12.4</v>
+        <v>-2.71</v>
       </c>
       <c r="L4">
-        <v>-0.1104185218165628</v>
+        <v>-0.02430493273542601</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,73 +888,8845 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.55</v>
+        <v>11.3</v>
       </c>
       <c r="V4">
-        <v>0.2228915662650602</v>
+        <v>0.3843537414965987</v>
       </c>
       <c r="W4">
-        <v>-0.1143911439114391</v>
+        <v>-0.02917115177610333</v>
       </c>
       <c r="X4">
-        <v>0.4678102711343324</v>
+        <v>0.2602063033394821</v>
       </c>
       <c r="Y4">
-        <v>-0.5822014150457715</v>
+        <v>-0.2893774551155855</v>
       </c>
       <c r="Z4">
-        <v>0.4638579099545642</v>
+        <v>0.4693748684487477</v>
       </c>
       <c r="AA4">
-        <v>-0.0553490293267245</v>
+        <v>-0.02134287518417176</v>
       </c>
       <c r="AB4">
-        <v>0.1079074753091989</v>
+        <v>0.08750692878830198</v>
       </c>
       <c r="AC4">
-        <v>-0.1632565046359234</v>
+        <v>-0.1088498039724737</v>
       </c>
       <c r="AD4">
-        <v>166.5</v>
+        <v>134.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>166.5</v>
+        <v>134.5</v>
       </c>
       <c r="AG4">
-        <v>160.95</v>
+        <v>123.2</v>
       </c>
       <c r="AH4">
-        <v>0.8699059561128526</v>
+        <v>0.8206223306894448</v>
       </c>
       <c r="AI4">
-        <v>0.6333206542411564</v>
+        <v>0.613594890510949</v>
       </c>
       <c r="AJ4">
-        <v>0.8660209846650524</v>
+        <v>0.8073394495412844</v>
       </c>
       <c r="AK4">
-        <v>0.6254128618612783</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="AL4">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AM4">
-        <v>1.814</v>
+        <v>2.084</v>
       </c>
       <c r="AN4">
-        <v>18.54120267260579</v>
+        <v>8.005952380952381</v>
       </c>
       <c r="AO4">
-        <v>-7.3224043715847</v>
+        <v>-2.273542600896861</v>
       </c>
       <c r="AP4">
-        <v>17.92316258351893</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="AQ4">
-        <v>-7.386990077177508</v>
+        <v>-2.432821497120921</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Metal and Recycling Company K.S.C. (Public) (KWSE:MRC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KWSE:MRC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Waste Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-0.0885416666666666</v>
+      </c>
+      <c r="F2">
+        <v>11.0981387136773</v>
+      </c>
+      <c r="G2">
+        <v>11.522491349481</v>
+      </c>
+      <c r="H2">
+        <v>1.19584775086505</v>
+      </c>
+      <c r="I2">
+        <v>0.578125</v>
+      </c>
+      <c r="J2">
+        <v>0.06</v>
+      </c>
+      <c r="K2">
+        <v>24.3</v>
+      </c>
+      <c r="L2">
+        <v>57.4497576924283</v>
+      </c>
+      <c r="M2">
+        <v>52.87</v>
+      </c>
+      <c r="N2">
+        <v>56.1757576924283</v>
+      </c>
+      <c r="O2">
+        <v>33.3</v>
+      </c>
+      <c r="P2">
+        <v>3.456</v>
+      </c>
+      <c r="Q2">
+        <v>0.0864972944229649</v>
+      </c>
+      <c r="R2">
+        <v>0.0836904662746018</v>
+      </c>
+      <c r="S2">
+        <v>0.0497570283287875</v>
+      </c>
+      <c r="T2">
+        <v>0.03893</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.136845066477949</v>
+      </c>
+      <c r="X2">
+        <v>0.08654751731340619</v>
+      </c>
+      <c r="Y2">
+        <v>1.74105688309587</v>
+      </c>
+      <c r="Z2">
+        <v>0.84788706515837</v>
+      </c>
+      <c r="AA2">
+        <v>33.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.05853768038680883</v>
+      </c>
+      <c r="AC2">
+        <v>-0.08854166666666663</v>
+      </c>
+      <c r="AD2">
+        <v>33.3</v>
+      </c>
+      <c r="AE2">
+        <v>1.92</v>
+      </c>
+      <c r="AF2">
+        <v>3.06</v>
+      </c>
+      <c r="AG2">
+        <v>2.89</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>24.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.05631353428476683</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.15</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>1.92</v>
+      </c>
+      <c r="AS2">
+        <v>33.3</v>
+      </c>
+      <c r="AT2">
+        <v>4.73</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08409027878365473</v>
+      </c>
+      <c r="C2">
+        <v>60.40985059637696</v>
+      </c>
+      <c r="D2">
+        <v>55.67985059637695</v>
+      </c>
+      <c r="E2">
+        <v>-33.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.73</v>
+      </c>
+      <c r="H2">
+        <v>24.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K2">
+        <v>3.06</v>
+      </c>
+      <c r="L2">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="O2">
+        <v>0.2635000000000001</v>
+      </c>
+      <c r="P2">
+        <v>1.493166666666667</v>
+      </c>
+      <c r="Q2">
+        <v>4.553166666666668</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08409027878365473</v>
+      </c>
+      <c r="T2">
+        <v>0.8042521102410373</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.037995</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08401429336547925</v>
+      </c>
+      <c r="C3">
+        <v>59.92742403116039</v>
+      </c>
+      <c r="D3">
+        <v>55.7734240311604</v>
+      </c>
+      <c r="E3">
+        <v>-32.724</v>
+      </c>
+      <c r="F3">
+        <v>0.576</v>
+      </c>
+      <c r="G3">
+        <v>4.73</v>
+      </c>
+      <c r="H3">
+        <v>24.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K3">
+        <v>3.06</v>
+      </c>
+      <c r="L3">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M3">
+        <v>0.0257472</v>
+      </c>
+      <c r="N3">
+        <v>1.730919466666667</v>
+      </c>
+      <c r="O3">
+        <v>0.2596379200000001</v>
+      </c>
+      <c r="P3">
+        <v>1.471281546666667</v>
+      </c>
+      <c r="Q3">
+        <v>4.531281546666667</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08447913471260529</v>
+      </c>
+      <c r="T3">
+        <v>0.8111573051269451</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.037995</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>68.22748363576106</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08393830794730377</v>
+      </c>
+      <c r="C4">
+        <v>59.44531250728656</v>
+      </c>
+      <c r="D4">
+        <v>55.86731250728656</v>
+      </c>
+      <c r="E4">
+        <v>-32.148</v>
+      </c>
+      <c r="F4">
+        <v>1.152</v>
+      </c>
+      <c r="G4">
+        <v>4.73</v>
+      </c>
+      <c r="H4">
+        <v>24.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K4">
+        <v>3.06</v>
+      </c>
+      <c r="L4">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M4">
+        <v>0.0514944</v>
+      </c>
+      <c r="N4">
+        <v>1.705172266666667</v>
+      </c>
+      <c r="O4">
+        <v>0.2557758400000001</v>
+      </c>
+      <c r="P4">
+        <v>1.449396426666667</v>
+      </c>
+      <c r="Q4">
+        <v>4.509396426666667</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08487592647684059</v>
+      </c>
+      <c r="T4">
+        <v>0.8182034223574635</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.037995</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>34.11374181788053</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08386232252912829</v>
+      </c>
+      <c r="C5">
+        <v>58.9635176184515</v>
+      </c>
+      <c r="D5">
+        <v>55.9615176184515</v>
+      </c>
+      <c r="E5">
+        <v>-31.572</v>
+      </c>
+      <c r="F5">
+        <v>1.728</v>
+      </c>
+      <c r="G5">
+        <v>4.73</v>
+      </c>
+      <c r="H5">
+        <v>24.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K5">
+        <v>3.06</v>
+      </c>
+      <c r="L5">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M5">
+        <v>0.07724159999999999</v>
+      </c>
+      <c r="N5">
+        <v>1.679425066666667</v>
+      </c>
+      <c r="O5">
+        <v>0.2519137600000001</v>
+      </c>
+      <c r="P5">
+        <v>1.427511306666667</v>
+      </c>
+      <c r="Q5">
+        <v>4.487511306666667</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08528089951456524</v>
+      </c>
+      <c r="T5">
+        <v>0.8253948203556212</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.037995</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>22.74249454525369</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08378633711095279</v>
+      </c>
+      <c r="C6">
+        <v>58.48204096911873</v>
+      </c>
+      <c r="D6">
+        <v>56.05604096911873</v>
+      </c>
+      <c r="E6">
+        <v>-30.996</v>
+      </c>
+      <c r="F6">
+        <v>2.304</v>
+      </c>
+      <c r="G6">
+        <v>4.73</v>
+      </c>
+      <c r="H6">
+        <v>24.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K6">
+        <v>3.06</v>
+      </c>
+      <c r="L6">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M6">
+        <v>0.1029888</v>
+      </c>
+      <c r="N6">
+        <v>1.653677866666667</v>
+      </c>
+      <c r="O6">
+        <v>0.2480516800000001</v>
+      </c>
+      <c r="P6">
+        <v>1.405626186666667</v>
+      </c>
+      <c r="Q6">
+        <v>4.465626186666667</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08569430949057583</v>
+      </c>
+      <c r="T6">
+        <v>0.8327360391454073</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.037995</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>17.05687090894027</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08371035169277732</v>
+      </c>
+      <c r="C7">
+        <v>58.00088417461036</v>
+      </c>
+      <c r="D7">
+        <v>56.15088417461036</v>
+      </c>
+      <c r="E7">
+        <v>-30.42</v>
+      </c>
+      <c r="F7">
+        <v>2.88</v>
+      </c>
+      <c r="G7">
+        <v>4.73</v>
+      </c>
+      <c r="H7">
+        <v>24.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K7">
+        <v>3.06</v>
+      </c>
+      <c r="L7">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M7">
+        <v>0.128736</v>
+      </c>
+      <c r="N7">
+        <v>1.627930666666667</v>
+      </c>
+      <c r="O7">
+        <v>0.2441896000000001</v>
+      </c>
+      <c r="P7">
+        <v>1.383741066666667</v>
+      </c>
+      <c r="Q7">
+        <v>4.443741066666667</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08611642283450244</v>
+      </c>
+      <c r="T7">
+        <v>0.8402318099097152</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.037995</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>13.64549672715221</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08369046627460183</v>
+      </c>
+      <c r="C8">
+        <v>57.44975769242826</v>
+      </c>
+      <c r="D8">
+        <v>56.17575769242827</v>
+      </c>
+      <c r="E8">
+        <v>-29.844</v>
+      </c>
+      <c r="F8">
+        <v>3.456</v>
+      </c>
+      <c r="G8">
+        <v>4.73</v>
+      </c>
+      <c r="H8">
+        <v>24.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K8">
+        <v>3.06</v>
+      </c>
+      <c r="L8">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M8">
+        <v>0.1582848</v>
+      </c>
+      <c r="N8">
+        <v>1.598381866666667</v>
+      </c>
+      <c r="O8">
+        <v>0.2397572800000001</v>
+      </c>
+      <c r="P8">
+        <v>1.358624586666667</v>
+      </c>
+      <c r="Q8">
+        <v>4.418624586666668</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08654751731340621</v>
+      </c>
+      <c r="T8">
+        <v>0.8478870651583701</v>
+      </c>
+      <c r="U8">
+        <v>0.0458</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.03893</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>11.09813871367729</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08375473085642635</v>
+      </c>
+      <c r="C9">
+        <v>56.79345220493001</v>
+      </c>
+      <c r="D9">
+        <v>56.09545220493001</v>
+      </c>
+      <c r="E9">
+        <v>-29.268</v>
+      </c>
+      <c r="F9">
+        <v>4.032</v>
+      </c>
+      <c r="G9">
+        <v>4.73</v>
+      </c>
+      <c r="H9">
+        <v>24.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K9">
+        <v>3.06</v>
+      </c>
+      <c r="L9">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M9">
+        <v>0.193536</v>
+      </c>
+      <c r="N9">
+        <v>1.563130666666667</v>
+      </c>
+      <c r="O9">
+        <v>0.2344696000000001</v>
+      </c>
+      <c r="P9">
+        <v>1.328661066666667</v>
+      </c>
+      <c r="Q9">
+        <v>4.388661066666668</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08698788264131865</v>
+      </c>
+      <c r="T9">
+        <v>0.8557069495521574</v>
+      </c>
+      <c r="U9">
+        <v>0.048</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.0408</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>9.076692019400356</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08370679543825088</v>
+      </c>
+      <c r="C10">
+        <v>56.27733086990583</v>
+      </c>
+      <c r="D10">
+        <v>56.15533086990583</v>
+      </c>
+      <c r="E10">
+        <v>-28.692</v>
+      </c>
+      <c r="F10">
+        <v>4.608</v>
+      </c>
+      <c r="G10">
+        <v>4.73</v>
+      </c>
+      <c r="H10">
+        <v>24.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K10">
+        <v>3.06</v>
+      </c>
+      <c r="L10">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M10">
+        <v>0.221184</v>
+      </c>
+      <c r="N10">
+        <v>1.535482666666667</v>
+      </c>
+      <c r="O10">
+        <v>0.2303224000000001</v>
+      </c>
+      <c r="P10">
+        <v>1.305160266666667</v>
+      </c>
+      <c r="Q10">
+        <v>4.365160266666667</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08743782112853356</v>
+      </c>
+      <c r="T10">
+        <v>0.8636968314327661</v>
+      </c>
+      <c r="U10">
+        <v>0.048</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.0408</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>7.942105516975311</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08377361002007538</v>
+      </c>
+      <c r="C11">
+        <v>55.61790427934272</v>
+      </c>
+      <c r="D11">
+        <v>56.07190427934272</v>
+      </c>
+      <c r="E11">
+        <v>-28.116</v>
+      </c>
+      <c r="F11">
+        <v>5.183999999999999</v>
+      </c>
+      <c r="G11">
+        <v>4.73</v>
+      </c>
+      <c r="H11">
+        <v>24.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K11">
+        <v>3.06</v>
+      </c>
+      <c r="L11">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M11">
+        <v>0.256608</v>
+      </c>
+      <c r="N11">
+        <v>1.500058666666667</v>
+      </c>
+      <c r="O11">
+        <v>0.2250088000000001</v>
+      </c>
+      <c r="P11">
+        <v>1.275049866666667</v>
+      </c>
+      <c r="Q11">
+        <v>4.335049866666667</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08789764837370921</v>
+      </c>
+      <c r="T11">
+        <v>0.8718623151129485</v>
+      </c>
+      <c r="U11">
+        <v>0.0495</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.042075</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>6.845720580288484</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08385742460189992</v>
+      </c>
+      <c r="C12">
+        <v>54.9376008654037</v>
+      </c>
+      <c r="D12">
+        <v>55.9676008654037</v>
+      </c>
+      <c r="E12">
+        <v>-27.54</v>
+      </c>
+      <c r="F12">
+        <v>5.76</v>
+      </c>
+      <c r="G12">
+        <v>4.73</v>
+      </c>
+      <c r="H12">
+        <v>24.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K12">
+        <v>3.06</v>
+      </c>
+      <c r="L12">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M12">
+        <v>0.293184</v>
+      </c>
+      <c r="N12">
+        <v>1.463482666666667</v>
+      </c>
+      <c r="O12">
+        <v>0.2195224000000001</v>
+      </c>
+      <c r="P12">
+        <v>1.243960266666667</v>
+      </c>
+      <c r="Q12">
+        <v>4.303960266666667</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08836769400211102</v>
+      </c>
+      <c r="T12">
+        <v>0.8802092539860242</v>
+      </c>
+      <c r="U12">
+        <v>0.0509</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.043265</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>5.991686676853672</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08383413918372443</v>
+      </c>
+      <c r="C13">
+        <v>54.39053955534098</v>
+      </c>
+      <c r="D13">
+        <v>55.99653955534098</v>
+      </c>
+      <c r="E13">
+        <v>-26.964</v>
+      </c>
+      <c r="F13">
+        <v>6.335999999999999</v>
+      </c>
+      <c r="G13">
+        <v>4.73</v>
+      </c>
+      <c r="H13">
+        <v>24.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K13">
+        <v>3.06</v>
+      </c>
+      <c r="L13">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M13">
+        <v>0.3225024</v>
+      </c>
+      <c r="N13">
+        <v>1.434164266666667</v>
+      </c>
+      <c r="O13">
+        <v>0.2151246400000001</v>
+      </c>
+      <c r="P13">
+        <v>1.219039626666667</v>
+      </c>
+      <c r="Q13">
+        <v>4.279039626666667</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08884830245362295</v>
+      </c>
+      <c r="T13">
+        <v>0.8887437645191687</v>
+      </c>
+      <c r="U13">
+        <v>0.0509</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.043265</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.446987888048795</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08381085376554893</v>
+      </c>
+      <c r="C14">
+        <v>53.84350818692301</v>
+      </c>
+      <c r="D14">
+        <v>56.02550818692301</v>
+      </c>
+      <c r="E14">
+        <v>-26.388</v>
+      </c>
+      <c r="F14">
+        <v>6.911999999999999</v>
+      </c>
+      <c r="G14">
+        <v>4.73</v>
+      </c>
+      <c r="H14">
+        <v>24.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K14">
+        <v>3.06</v>
+      </c>
+      <c r="L14">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M14">
+        <v>0.3518207999999999</v>
+      </c>
+      <c r="N14">
+        <v>1.404845866666667</v>
+      </c>
+      <c r="O14">
+        <v>0.2107268800000001</v>
+      </c>
+      <c r="P14">
+        <v>1.194118986666667</v>
+      </c>
+      <c r="Q14">
+        <v>4.254118986666667</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08933983382448743</v>
+      </c>
+      <c r="T14">
+        <v>0.8974722412007939</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.043265</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>4.993072230711395</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08378756834737346</v>
+      </c>
+      <c r="C15">
+        <v>53.29650680664285</v>
+      </c>
+      <c r="D15">
+        <v>56.05450680664286</v>
+      </c>
+      <c r="E15">
+        <v>-25.812</v>
+      </c>
+      <c r="F15">
+        <v>7.488</v>
+      </c>
+      <c r="G15">
+        <v>4.73</v>
+      </c>
+      <c r="H15">
+        <v>24.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K15">
+        <v>3.06</v>
+      </c>
+      <c r="L15">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M15">
+        <v>0.3811392</v>
+      </c>
+      <c r="N15">
+        <v>1.375527466666667</v>
+      </c>
+      <c r="O15">
+        <v>0.2063291200000001</v>
+      </c>
+      <c r="P15">
+        <v>1.169198346666667</v>
+      </c>
+      <c r="Q15">
+        <v>4.229198346666667</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08984266476709593</v>
+      </c>
+      <c r="T15">
+        <v>0.9064013725187782</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.043265</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.608989751425902</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08407368292919797</v>
+      </c>
+      <c r="C16">
+        <v>52.3662610122496</v>
+      </c>
+      <c r="D16">
+        <v>55.70026101224961</v>
+      </c>
+      <c r="E16">
+        <v>-25.236</v>
+      </c>
+      <c r="F16">
+        <v>8.064</v>
+      </c>
+      <c r="G16">
+        <v>4.73</v>
+      </c>
+      <c r="H16">
+        <v>24.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K16">
+        <v>3.06</v>
+      </c>
+      <c r="L16">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M16">
+        <v>0.431424</v>
+      </c>
+      <c r="N16">
+        <v>1.325242666666667</v>
+      </c>
+      <c r="O16">
+        <v>0.1987864000000001</v>
+      </c>
+      <c r="P16">
+        <v>1.126456266666667</v>
+      </c>
+      <c r="Q16">
+        <v>4.186456266666667</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09035718945255578</v>
+      </c>
+      <c r="T16">
+        <v>0.9155381580534597</v>
+      </c>
+      <c r="U16">
+        <v>0.0535</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.071787074123524</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.0844167475110225</v>
+      </c>
+      <c r="C17">
+        <v>51.37136252004413</v>
+      </c>
+      <c r="D17">
+        <v>55.28136252004413</v>
+      </c>
+      <c r="E17">
+        <v>-24.66</v>
+      </c>
+      <c r="F17">
+        <v>8.639999999999999</v>
+      </c>
+      <c r="G17">
+        <v>4.73</v>
+      </c>
+      <c r="H17">
+        <v>24.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K17">
+        <v>3.06</v>
+      </c>
+      <c r="L17">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M17">
+        <v>0.4855679999999999</v>
+      </c>
+      <c r="N17">
+        <v>1.271098666666667</v>
+      </c>
+      <c r="O17">
+        <v>0.1906648000000001</v>
+      </c>
+      <c r="P17">
+        <v>1.080433866666667</v>
+      </c>
+      <c r="Q17">
+        <v>4.140433866666667</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09088382060120294</v>
+      </c>
+      <c r="T17">
+        <v>0.9248899267771928</v>
+      </c>
+      <c r="U17">
+        <v>0.0562</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.04777</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>3.617756249725409</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08507771209284701</v>
+      </c>
+      <c r="C18">
+        <v>50.00580268641533</v>
+      </c>
+      <c r="D18">
+        <v>54.49180268641533</v>
+      </c>
+      <c r="E18">
+        <v>-24.084</v>
+      </c>
+      <c r="F18">
+        <v>9.215999999999999</v>
+      </c>
+      <c r="G18">
+        <v>4.73</v>
+      </c>
+      <c r="H18">
+        <v>24.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K18">
+        <v>3.06</v>
+      </c>
+      <c r="L18">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M18">
+        <v>0.5612543999999999</v>
+      </c>
+      <c r="N18">
+        <v>1.195412266666667</v>
+      </c>
+      <c r="O18">
+        <v>0.1793118400000001</v>
+      </c>
+      <c r="P18">
+        <v>1.016100426666667</v>
+      </c>
+      <c r="Q18">
+        <v>4.076100426666668</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09142299058672264</v>
+      </c>
+      <c r="T18">
+        <v>0.9344643566610148</v>
+      </c>
+      <c r="U18">
+        <v>0.0609</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.051765</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>3.129893799793226</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08648327667467152</v>
+      </c>
+      <c r="C19">
+        <v>47.8235425214867</v>
+      </c>
+      <c r="D19">
+        <v>52.88554252148671</v>
+      </c>
+      <c r="E19">
+        <v>-23.508</v>
+      </c>
+      <c r="F19">
+        <v>9.792</v>
+      </c>
+      <c r="G19">
+        <v>4.73</v>
+      </c>
+      <c r="H19">
+        <v>24.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K19">
+        <v>3.06</v>
+      </c>
+      <c r="L19">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M19">
+        <v>0.6873984</v>
+      </c>
+      <c r="N19">
+        <v>1.069268266666667</v>
+      </c>
+      <c r="O19">
+        <v>0.1603902400000001</v>
+      </c>
+      <c r="P19">
+        <v>0.9088780266666672</v>
+      </c>
+      <c r="Q19">
+        <v>3.968878026666667</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09197515262008618</v>
+      </c>
+      <c r="T19">
+        <v>0.9442694956986636</v>
+      </c>
+      <c r="U19">
+        <v>0.0702</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.05966999999999999</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>2.555529175899547</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08734314125649606</v>
+      </c>
+      <c r="C20">
+        <v>46.3107592040553</v>
+      </c>
+      <c r="D20">
+        <v>51.9487592040553</v>
+      </c>
+      <c r="E20">
+        <v>-22.932</v>
+      </c>
+      <c r="F20">
+        <v>10.368</v>
+      </c>
+      <c r="G20">
+        <v>4.73</v>
+      </c>
+      <c r="H20">
+        <v>24.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K20">
+        <v>3.06</v>
+      </c>
+      <c r="L20">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M20">
+        <v>0.7765631999999998</v>
+      </c>
+      <c r="N20">
+        <v>0.9801034666666675</v>
+      </c>
+      <c r="O20">
+        <v>0.1470155200000001</v>
+      </c>
+      <c r="P20">
+        <v>0.8330879466666674</v>
+      </c>
+      <c r="Q20">
+        <v>3.893087946666667</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09254078202011713</v>
+      </c>
+      <c r="T20">
+        <v>0.9543137844689381</v>
+      </c>
+      <c r="U20">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.063665</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>2.262103930068625</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08752385583832058</v>
+      </c>
+      <c r="C21">
+        <v>45.54208360122503</v>
+      </c>
+      <c r="D21">
+        <v>51.75608360122504</v>
+      </c>
+      <c r="E21">
+        <v>-22.356</v>
+      </c>
+      <c r="F21">
+        <v>10.944</v>
+      </c>
+      <c r="G21">
+        <v>4.73</v>
+      </c>
+      <c r="H21">
+        <v>24.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K21">
+        <v>3.06</v>
+      </c>
+      <c r="L21">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M21">
+        <v>0.8197055999999999</v>
+      </c>
+      <c r="N21">
+        <v>0.9369610666666673</v>
+      </c>
+      <c r="O21">
+        <v>0.1405441600000001</v>
+      </c>
+      <c r="P21">
+        <v>0.7964169066666673</v>
+      </c>
+      <c r="Q21">
+        <v>3.856416906666667</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09312037757817354</v>
+      </c>
+      <c r="T21">
+        <v>0.9646060803693428</v>
+      </c>
+      <c r="U21">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.063665</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.143045828486065</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08770457042014509</v>
+      </c>
+      <c r="C22">
+        <v>44.77483196718518</v>
+      </c>
+      <c r="D22">
+        <v>51.56483196718517</v>
+      </c>
+      <c r="E22">
+        <v>-21.78</v>
+      </c>
+      <c r="F22">
+        <v>11.52</v>
+      </c>
+      <c r="G22">
+        <v>4.73</v>
+      </c>
+      <c r="H22">
+        <v>24.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K22">
+        <v>3.06</v>
+      </c>
+      <c r="L22">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M22">
+        <v>0.8628479999999999</v>
+      </c>
+      <c r="N22">
+        <v>0.8938186666666673</v>
+      </c>
+      <c r="O22">
+        <v>0.1340728000000001</v>
+      </c>
+      <c r="P22">
+        <v>0.7597458666666672</v>
+      </c>
+      <c r="Q22">
+        <v>3.819745866666667</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09371446302518135</v>
+      </c>
+      <c r="T22">
+        <v>0.9751556836672576</v>
+      </c>
+      <c r="U22">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.063665</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.035893537061762</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09079483500196961</v>
+      </c>
+      <c r="C23">
+        <v>41.13412421515772</v>
+      </c>
+      <c r="D23">
+        <v>48.50012421515771</v>
+      </c>
+      <c r="E23">
+        <v>-21.204</v>
+      </c>
+      <c r="F23">
+        <v>12.096</v>
+      </c>
+      <c r="G23">
+        <v>4.73</v>
+      </c>
+      <c r="H23">
+        <v>24.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K23">
+        <v>3.06</v>
+      </c>
+      <c r="L23">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M23">
+        <v>1.1031552</v>
+      </c>
+      <c r="N23">
+        <v>0.6535114666666675</v>
+      </c>
+      <c r="O23">
+        <v>0.09802672000000012</v>
+      </c>
+      <c r="P23">
+        <v>0.5554847466666674</v>
+      </c>
+      <c r="Q23">
+        <v>3.615484746666668</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.0943235886100881</v>
+      </c>
+      <c r="T23">
+        <v>0.9859723655296766</v>
+      </c>
+      <c r="U23">
+        <v>0.0912</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>1.592402108666729</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09111409958379411</v>
+      </c>
+      <c r="C24">
+        <v>40.26213571494112</v>
+      </c>
+      <c r="D24">
+        <v>48.20413571494112</v>
+      </c>
+      <c r="E24">
+        <v>-20.628</v>
+      </c>
+      <c r="F24">
+        <v>12.672</v>
+      </c>
+      <c r="G24">
+        <v>4.73</v>
+      </c>
+      <c r="H24">
+        <v>24.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K24">
+        <v>3.06</v>
+      </c>
+      <c r="L24">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M24">
+        <v>1.1556864</v>
+      </c>
+      <c r="N24">
+        <v>0.6009802666666673</v>
+      </c>
+      <c r="O24">
+        <v>0.09014704000000008</v>
+      </c>
+      <c r="P24">
+        <v>0.5108332266666672</v>
+      </c>
+      <c r="Q24">
+        <v>3.570833226666667</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09494833279973605</v>
+      </c>
+      <c r="T24">
+        <v>0.9970663982090808</v>
+      </c>
+      <c r="U24">
+        <v>0.0912</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>1.520020194636423</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1052865908868222</v>
+      </c>
+      <c r="C25">
+        <v>29.41079018921054</v>
+      </c>
+      <c r="D25">
+        <v>37.92879018921054</v>
+      </c>
+      <c r="E25">
+        <v>-20.052</v>
+      </c>
+      <c r="F25">
+        <v>13.248</v>
+      </c>
+      <c r="G25">
+        <v>4.73</v>
+      </c>
+      <c r="H25">
+        <v>24.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K25">
+        <v>3.06</v>
+      </c>
+      <c r="L25">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M25">
+        <v>2.0746368</v>
+      </c>
+      <c r="N25">
+        <v>-0.3179701333333327</v>
+      </c>
+      <c r="O25">
+        <v>-0.0476955199999999</v>
+      </c>
+      <c r="P25">
+        <v>-0.2702746133333328</v>
+      </c>
+      <c r="Q25">
+        <v>2.789725386666667</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09590031644753241</v>
+      </c>
+      <c r="T25">
+        <v>1.013971457710095</v>
+      </c>
+      <c r="U25">
+        <v>0.1566</v>
+      </c>
+      <c r="V25">
+        <v>0.127010183180015</v>
+      </c>
+      <c r="W25">
+        <v>0.1367102053140097</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.8467345545334332</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1064645908868222</v>
+      </c>
+      <c r="C26">
+        <v>28.17447266925947</v>
+      </c>
+      <c r="D26">
+        <v>37.26847266925947</v>
+      </c>
+      <c r="E26">
+        <v>-19.476</v>
+      </c>
+      <c r="F26">
+        <v>13.824</v>
+      </c>
+      <c r="G26">
+        <v>4.73</v>
+      </c>
+      <c r="H26">
+        <v>24.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K26">
+        <v>3.06</v>
+      </c>
+      <c r="L26">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M26">
+        <v>2.1648384</v>
+      </c>
+      <c r="N26">
+        <v>-0.4081717333333326</v>
+      </c>
+      <c r="O26">
+        <v>-0.06122575999999988</v>
+      </c>
+      <c r="P26">
+        <v>-0.3469459733333327</v>
+      </c>
+      <c r="Q26">
+        <v>2.713054026666668</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09665163640078943</v>
+      </c>
+      <c r="T26">
+        <v>1.027313187416806</v>
+      </c>
+      <c r="U26">
+        <v>0.1566</v>
+      </c>
+      <c r="V26">
+        <v>0.121718092214181</v>
+      </c>
+      <c r="W26">
+        <v>0.1375389467592593</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.8114539480945402</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1210233496665859</v>
+      </c>
+      <c r="C27">
+        <v>20.99958432571561</v>
+      </c>
+      <c r="D27">
+        <v>30.66958432571561</v>
+      </c>
+      <c r="E27">
+        <v>-18.9</v>
+      </c>
+      <c r="F27">
+        <v>14.4</v>
+      </c>
+      <c r="G27">
+        <v>4.73</v>
+      </c>
+      <c r="H27">
+        <v>24.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K27">
+        <v>3.06</v>
+      </c>
+      <c r="L27">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M27">
+        <v>3.00672</v>
+      </c>
+      <c r="N27">
+        <v>-1.250053333333333</v>
+      </c>
+      <c r="O27">
+        <v>-0.1875079999999999</v>
+      </c>
+      <c r="P27">
+        <v>-1.062545333333333</v>
+      </c>
+      <c r="Q27">
+        <v>1.997454666666667</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09786400325915154</v>
+      </c>
+      <c r="T27">
+        <v>1.048842059183785</v>
+      </c>
+      <c r="U27">
+        <v>0.2088</v>
+      </c>
+      <c r="V27">
+        <v>0.08763702639421034</v>
+      </c>
+      <c r="W27">
+        <v>0.1905013888888889</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.5842468426280689</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1227233496665859</v>
+      </c>
+      <c r="C28">
+        <v>19.80232345420782</v>
+      </c>
+      <c r="D28">
+        <v>30.04832345420782</v>
+      </c>
+      <c r="E28">
+        <v>-18.324</v>
+      </c>
+      <c r="F28">
+        <v>14.976</v>
+      </c>
+      <c r="G28">
+        <v>4.73</v>
+      </c>
+      <c r="H28">
+        <v>24.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K28">
+        <v>3.06</v>
+      </c>
+      <c r="L28">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M28">
+        <v>3.1269888</v>
+      </c>
+      <c r="N28">
+        <v>-1.370322133333333</v>
+      </c>
+      <c r="O28">
+        <v>-0.2055483199999999</v>
+      </c>
+      <c r="P28">
+        <v>-1.164773813333333</v>
+      </c>
+      <c r="Q28">
+        <v>1.895226186666667</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09866216546535629</v>
+      </c>
+      <c r="T28">
+        <v>1.063015600524107</v>
+      </c>
+      <c r="U28">
+        <v>0.2088</v>
+      </c>
+      <c r="V28">
+        <v>0.08426637153289455</v>
+      </c>
+      <c r="W28">
+        <v>0.1912051816239316</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.561775810219297</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1244233496665859</v>
+      </c>
+      <c r="C29">
+        <v>18.62973210300437</v>
+      </c>
+      <c r="D29">
+        <v>29.45173210300437</v>
+      </c>
+      <c r="E29">
+        <v>-17.748</v>
+      </c>
+      <c r="F29">
+        <v>15.552</v>
+      </c>
+      <c r="G29">
+        <v>4.73</v>
+      </c>
+      <c r="H29">
+        <v>24.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K29">
+        <v>3.06</v>
+      </c>
+      <c r="L29">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M29">
+        <v>3.2472576</v>
+      </c>
+      <c r="N29">
+        <v>-1.490590933333333</v>
+      </c>
+      <c r="O29">
+        <v>-0.2235886399999999</v>
+      </c>
+      <c r="P29">
+        <v>-1.267002293333333</v>
+      </c>
+      <c r="Q29">
+        <v>1.792997706666667</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09948219512926529</v>
+      </c>
+      <c r="T29">
+        <v>1.077577458065533</v>
+      </c>
+      <c r="U29">
+        <v>0.2088</v>
+      </c>
+      <c r="V29">
+        <v>0.081145394809454</v>
+      </c>
+      <c r="W29">
+        <v>0.191856841563786</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.5409692987296935</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1261233496665859</v>
+      </c>
+      <c r="C30">
+        <v>17.48036948273986</v>
+      </c>
+      <c r="D30">
+        <v>28.87836948273986</v>
+      </c>
+      <c r="E30">
+        <v>-17.172</v>
+      </c>
+      <c r="F30">
+        <v>16.128</v>
+      </c>
+      <c r="G30">
+        <v>4.73</v>
+      </c>
+      <c r="H30">
+        <v>24.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K30">
+        <v>3.06</v>
+      </c>
+      <c r="L30">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M30">
+        <v>3.3675264</v>
+      </c>
+      <c r="N30">
+        <v>-1.610859733333333</v>
+      </c>
+      <c r="O30">
+        <v>-0.2416289599999999</v>
+      </c>
+      <c r="P30">
+        <v>-1.369230773333333</v>
+      </c>
+      <c r="Q30">
+        <v>1.690769226666667</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1003250033949495</v>
+      </c>
+      <c r="T30">
+        <v>1.092543811649776</v>
+      </c>
+      <c r="U30">
+        <v>0.2088</v>
+      </c>
+      <c r="V30">
+        <v>0.07824734499483066</v>
+      </c>
+      <c r="W30">
+        <v>0.1924619543650794</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.5216489666322044</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1278233496665859</v>
+      </c>
+      <c r="C31">
+        <v>16.35290485795857</v>
+      </c>
+      <c r="D31">
+        <v>28.32690485795857</v>
+      </c>
+      <c r="E31">
+        <v>-16.596</v>
+      </c>
+      <c r="F31">
+        <v>16.704</v>
+      </c>
+      <c r="G31">
+        <v>4.73</v>
+      </c>
+      <c r="H31">
+        <v>24.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K31">
+        <v>3.06</v>
+      </c>
+      <c r="L31">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M31">
+        <v>3.487795199999999</v>
+      </c>
+      <c r="N31">
+        <v>-1.731128533333332</v>
+      </c>
+      <c r="O31">
+        <v>-0.2596692799999998</v>
+      </c>
+      <c r="P31">
+        <v>-1.471459253333332</v>
+      </c>
+      <c r="Q31">
+        <v>1.588540746666668</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1011915527385404</v>
+      </c>
+      <c r="T31">
+        <v>1.107931752658928</v>
+      </c>
+      <c r="U31">
+        <v>0.2088</v>
+      </c>
+      <c r="V31">
+        <v>0.07554916068466409</v>
+      </c>
+      <c r="W31">
+        <v>0.1930253352490421</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5036610712310939</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1386480074981551</v>
+      </c>
+      <c r="C32">
+        <v>12.70594670668568</v>
+      </c>
+      <c r="D32">
+        <v>25.25594670668567</v>
+      </c>
+      <c r="E32">
+        <v>-16.02</v>
+      </c>
+      <c r="F32">
+        <v>17.28</v>
+      </c>
+      <c r="G32">
+        <v>4.73</v>
+      </c>
+      <c r="H32">
+        <v>24.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K32">
+        <v>3.06</v>
+      </c>
+      <c r="L32">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M32">
+        <v>4.126463999999999</v>
+      </c>
+      <c r="N32">
+        <v>-2.369797333333332</v>
+      </c>
+      <c r="O32">
+        <v>-0.3554695999999998</v>
+      </c>
+      <c r="P32">
+        <v>-2.014327733333332</v>
+      </c>
+      <c r="Q32">
+        <v>1.045672266666668</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1022609432513327</v>
+      </c>
+      <c r="T32">
+        <v>1.126921690448743</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.06385612475960049</v>
+      </c>
+      <c r="W32">
+        <v>0.2235511574074074</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.4257074983973367</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1406480074981551</v>
+      </c>
+      <c r="C33">
+        <v>11.63399303361763</v>
+      </c>
+      <c r="D33">
+        <v>24.75999303361763</v>
+      </c>
+      <c r="E33">
+        <v>-15.444</v>
+      </c>
+      <c r="F33">
+        <v>17.856</v>
+      </c>
+      <c r="G33">
+        <v>4.73</v>
+      </c>
+      <c r="H33">
+        <v>24.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K33">
+        <v>3.06</v>
+      </c>
+      <c r="L33">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M33">
+        <v>4.2640128</v>
+      </c>
+      <c r="N33">
+        <v>-2.507346133333332</v>
+      </c>
+      <c r="O33">
+        <v>-0.3761019199999999</v>
+      </c>
+      <c r="P33">
+        <v>-2.131244213333332</v>
+      </c>
+      <c r="Q33">
+        <v>0.9287557866666676</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1031806670665694</v>
+      </c>
+      <c r="T33">
+        <v>1.143253888861044</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.06179624976735532</v>
+      </c>
+      <c r="W33">
+        <v>0.2240430555555556</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.4119749984490355</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1426480074981551</v>
+      </c>
+      <c r="C34">
+        <v>10.58114242030071</v>
+      </c>
+      <c r="D34">
+        <v>24.28314242030071</v>
+      </c>
+      <c r="E34">
+        <v>-14.868</v>
+      </c>
+      <c r="F34">
+        <v>18.432</v>
+      </c>
+      <c r="G34">
+        <v>4.73</v>
+      </c>
+      <c r="H34">
+        <v>24.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K34">
+        <v>3.06</v>
+      </c>
+      <c r="L34">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M34">
+        <v>4.4015616</v>
+      </c>
+      <c r="N34">
+        <v>-2.644894933333333</v>
+      </c>
+      <c r="O34">
+        <v>-0.3967342399999999</v>
+      </c>
+      <c r="P34">
+        <v>-2.248160693333333</v>
+      </c>
+      <c r="Q34">
+        <v>0.8118393066666671</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1041274415822542</v>
+      </c>
+      <c r="T34">
+        <v>1.160066446050177</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05986511696212546</v>
+      </c>
+      <c r="W34">
+        <v>0.2245042100694444</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.3991007797475031</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1446480074981551</v>
+      </c>
+      <c r="C35">
+        <v>9.54631200876511</v>
+      </c>
+      <c r="D35">
+        <v>23.82431200876511</v>
+      </c>
+      <c r="E35">
+        <v>-14.292</v>
+      </c>
+      <c r="F35">
+        <v>19.008</v>
+      </c>
+      <c r="G35">
+        <v>4.73</v>
+      </c>
+      <c r="H35">
+        <v>24.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K35">
+        <v>3.06</v>
+      </c>
+      <c r="L35">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M35">
+        <v>4.5391104</v>
+      </c>
+      <c r="N35">
+        <v>-2.782443733333333</v>
+      </c>
+      <c r="O35">
+        <v>-0.4173665599999999</v>
+      </c>
+      <c r="P35">
+        <v>-2.365077173333333</v>
+      </c>
+      <c r="Q35">
+        <v>0.6949228266666672</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1051024780237804</v>
+      </c>
+      <c r="T35">
+        <v>1.17738087061809</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.05805102250872771</v>
+      </c>
+      <c r="W35">
+        <v>0.2249374158249158</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.3870068167248515</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1466480074981551</v>
+      </c>
+      <c r="C36">
+        <v>8.528499265786571</v>
+      </c>
+      <c r="D36">
+        <v>23.38249926578657</v>
+      </c>
+      <c r="E36">
+        <v>-13.716</v>
+      </c>
+      <c r="F36">
+        <v>19.584</v>
+      </c>
+      <c r="G36">
+        <v>4.73</v>
+      </c>
+      <c r="H36">
+        <v>24.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K36">
+        <v>3.06</v>
+      </c>
+      <c r="L36">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M36">
+        <v>4.6766592</v>
+      </c>
+      <c r="N36">
+        <v>-2.919992533333333</v>
+      </c>
+      <c r="O36">
+        <v>-0.43799888</v>
+      </c>
+      <c r="P36">
+        <v>-2.481993653333333</v>
+      </c>
+      <c r="Q36">
+        <v>0.5780063466666667</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1061070610241407</v>
+      </c>
+      <c r="T36">
+        <v>1.195219974718364</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.05634363949376513</v>
+      </c>
+      <c r="W36">
+        <v>0.2253451388888889</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3756242632917676</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1486480074981551</v>
+      </c>
+      <c r="C37">
+        <v>7.526774670532905</v>
+      </c>
+      <c r="D37">
+        <v>22.9567746705329</v>
+      </c>
+      <c r="E37">
+        <v>-13.14</v>
+      </c>
+      <c r="F37">
+        <v>20.16</v>
+      </c>
+      <c r="G37">
+        <v>4.73</v>
+      </c>
+      <c r="H37">
+        <v>24.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K37">
+        <v>3.06</v>
+      </c>
+      <c r="L37">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M37">
+        <v>4.814208000000001</v>
+      </c>
+      <c r="N37">
+        <v>-3.057541333333333</v>
+      </c>
+      <c r="O37">
+        <v>-0.4586312</v>
+      </c>
+      <c r="P37">
+        <v>-2.598910133333333</v>
+      </c>
+      <c r="Q37">
+        <v>0.4610898666666667</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.107142554270666</v>
+      </c>
+      <c r="T37">
+        <v>1.213607974329416</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.0547338212225147</v>
+      </c>
+      <c r="W37">
+        <v>0.2257295634920635</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3648921414834313</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1506480074981551</v>
+      </c>
+      <c r="C38">
+        <v>6.54027518674172</v>
+      </c>
+      <c r="D38">
+        <v>22.54627518674172</v>
+      </c>
+      <c r="E38">
+        <v>-12.564</v>
+      </c>
+      <c r="F38">
+        <v>20.736</v>
+      </c>
+      <c r="G38">
+        <v>4.73</v>
+      </c>
+      <c r="H38">
+        <v>24.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K38">
+        <v>3.06</v>
+      </c>
+      <c r="L38">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M38">
+        <v>4.951756799999999</v>
+      </c>
+      <c r="N38">
+        <v>-3.195090133333332</v>
+      </c>
+      <c r="O38">
+        <v>-0.4792635199999998</v>
+      </c>
+      <c r="P38">
+        <v>-2.715826613333332</v>
+      </c>
+      <c r="Q38">
+        <v>0.3441733866666681</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1082104066811451</v>
+      </c>
+      <c r="T38">
+        <v>1.232570598928313</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.05321343729966708</v>
+      </c>
+      <c r="W38">
+        <v>0.2260926311728395</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3547562486644472</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1526480074981551</v>
+      </c>
+      <c r="C39">
+        <v>5.568198422954584</v>
+      </c>
+      <c r="D39">
+        <v>22.15019842295458</v>
+      </c>
+      <c r="E39">
+        <v>-11.988</v>
+      </c>
+      <c r="F39">
+        <v>21.312</v>
+      </c>
+      <c r="G39">
+        <v>4.73</v>
+      </c>
+      <c r="H39">
+        <v>24.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K39">
+        <v>3.06</v>
+      </c>
+      <c r="L39">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M39">
+        <v>5.089305599999999</v>
+      </c>
+      <c r="N39">
+        <v>-3.332638933333332</v>
+      </c>
+      <c r="O39">
+        <v>-0.4998958399999998</v>
+      </c>
+      <c r="P39">
+        <v>-2.832743093333332</v>
+      </c>
+      <c r="Q39">
+        <v>0.2272569066666676</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1093121591681474</v>
+      </c>
+      <c r="T39">
+        <v>1.252135211609715</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.05177523629156797</v>
+      </c>
+      <c r="W39">
+        <v>0.2264360735735736</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3451682419437865</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1546480074981551</v>
+      </c>
+      <c r="C40">
+        <v>4.609797397657577</v>
+      </c>
+      <c r="D40">
+        <v>21.76779739765757</v>
+      </c>
+      <c r="E40">
+        <v>-11.412</v>
+      </c>
+      <c r="F40">
+        <v>21.888</v>
+      </c>
+      <c r="G40">
+        <v>4.73</v>
+      </c>
+      <c r="H40">
+        <v>24.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K40">
+        <v>3.06</v>
+      </c>
+      <c r="L40">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M40">
+        <v>5.2268544</v>
+      </c>
+      <c r="N40">
+        <v>-3.470187733333332</v>
+      </c>
+      <c r="O40">
+        <v>-0.5205281599999998</v>
+      </c>
+      <c r="P40">
+        <v>-2.949659573333332</v>
+      </c>
+      <c r="Q40">
+        <v>0.1103404266666677</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1104494520579563</v>
+      </c>
+      <c r="T40">
+        <v>1.272330940829226</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.05041273007336881</v>
+      </c>
+      <c r="W40">
+        <v>0.2267614400584795</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3360848671557921</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1566480074981551</v>
+      </c>
+      <c r="C41">
+        <v>3.664375837467038</v>
+      </c>
+      <c r="D41">
+        <v>21.39837583746704</v>
+      </c>
+      <c r="E41">
+        <v>-10.836</v>
+      </c>
+      <c r="F41">
+        <v>22.464</v>
+      </c>
+      <c r="G41">
+        <v>4.73</v>
+      </c>
+      <c r="H41">
+        <v>24.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K41">
+        <v>3.06</v>
+      </c>
+      <c r="L41">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M41">
+        <v>5.3644032</v>
+      </c>
+      <c r="N41">
+        <v>-3.607736533333333</v>
+      </c>
+      <c r="O41">
+        <v>-0.5411604799999998</v>
+      </c>
+      <c r="P41">
+        <v>-3.066576053333333</v>
+      </c>
+      <c r="Q41">
+        <v>-0.006576053333332776</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1116240332392342</v>
+      </c>
+      <c r="T41">
+        <v>1.293188825105115</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04912009596892346</v>
+      </c>
+      <c r="W41">
+        <v>0.2270701210826211</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3274673064594897</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1586480074981551</v>
+      </c>
+      <c r="C42">
+        <v>2.731283946092926</v>
+      </c>
+      <c r="D42">
+        <v>21.04128394609292</v>
+      </c>
+      <c r="E42">
+        <v>-10.26</v>
+      </c>
+      <c r="F42">
+        <v>23.04</v>
+      </c>
+      <c r="G42">
+        <v>4.73</v>
+      </c>
+      <c r="H42">
+        <v>24.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K42">
+        <v>3.06</v>
+      </c>
+      <c r="L42">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M42">
+        <v>5.501952</v>
+      </c>
+      <c r="N42">
+        <v>-3.745285333333333</v>
+      </c>
+      <c r="O42">
+        <v>-0.5617927999999999</v>
+      </c>
+      <c r="P42">
+        <v>-3.183492533333333</v>
+      </c>
+      <c r="Q42">
+        <v>-0.1234925333333332</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1128377671265548</v>
+      </c>
+      <c r="T42">
+        <v>1.3147419721902</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04789209356970037</v>
+      </c>
+      <c r="W42">
+        <v>0.2273633680555556</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3192806237980025</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1606480074981551</v>
+      </c>
+      <c r="C43">
+        <v>1.809914589988988</v>
+      </c>
+      <c r="D43">
+        <v>20.69591458998899</v>
+      </c>
+      <c r="E43">
+        <v>-9.683999999999997</v>
+      </c>
+      <c r="F43">
+        <v>23.616</v>
+      </c>
+      <c r="G43">
+        <v>4.73</v>
+      </c>
+      <c r="H43">
+        <v>24.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K43">
+        <v>3.06</v>
+      </c>
+      <c r="L43">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M43">
+        <v>5.6395008</v>
+      </c>
+      <c r="N43">
+        <v>-3.882834133333333</v>
+      </c>
+      <c r="O43">
+        <v>-0.5824251199999999</v>
+      </c>
+      <c r="P43">
+        <v>-3.300409013333333</v>
+      </c>
+      <c r="Q43">
+        <v>-0.2404090133333332</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1140926445354795</v>
+      </c>
+      <c r="T43">
+        <v>1.337025734430712</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.04672399372653694</v>
+      </c>
+      <c r="W43">
+        <v>0.227642310298103</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3114932915102463</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1626480074981551</v>
+      </c>
+      <c r="C44">
+        <v>0.8996998535864336</v>
+      </c>
+      <c r="D44">
+        <v>20.36169985358643</v>
+      </c>
+      <c r="E44">
+        <v>-9.108000000000001</v>
+      </c>
+      <c r="F44">
+        <v>24.192</v>
+      </c>
+      <c r="G44">
+        <v>4.73</v>
+      </c>
+      <c r="H44">
+        <v>24.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K44">
+        <v>3.06</v>
+      </c>
+      <c r="L44">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M44">
+        <v>5.7770496</v>
+      </c>
+      <c r="N44">
+        <v>-4.020382933333332</v>
+      </c>
+      <c r="O44">
+        <v>-0.6030574399999998</v>
+      </c>
+      <c r="P44">
+        <v>-3.417325493333332</v>
+      </c>
+      <c r="Q44">
+        <v>-0.3573254933333323</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1153907935791946</v>
+      </c>
+      <c r="T44">
+        <v>1.360077902265724</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.04561151768542893</v>
+      </c>
+      <c r="W44">
+        <v>0.2279079695767196</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3040767845695262</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1646480074981551</v>
+      </c>
+      <c r="C45">
+        <v>0.000107922996907206</v>
+      </c>
+      <c r="D45">
+        <v>20.0381079229969</v>
+      </c>
+      <c r="E45">
+        <v>-8.532</v>
+      </c>
+      <c r="F45">
+        <v>24.768</v>
+      </c>
+      <c r="G45">
+        <v>4.73</v>
+      </c>
+      <c r="H45">
+        <v>24.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K45">
+        <v>3.06</v>
+      </c>
+      <c r="L45">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M45">
+        <v>5.9145984</v>
+      </c>
+      <c r="N45">
+        <v>-4.157931733333333</v>
+      </c>
+      <c r="O45">
+        <v>-0.62368976</v>
+      </c>
+      <c r="P45">
+        <v>-3.534241973333333</v>
+      </c>
+      <c r="Q45">
+        <v>-0.4742419733333332</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1167344917121629</v>
+      </c>
+      <c r="T45">
+        <v>1.383938918094948</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.04455078471600035</v>
+      </c>
+      <c r="W45">
+        <v>0.2281612726098191</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2970052314400022</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1666480074981551</v>
+      </c>
+      <c r="C46">
+        <v>-0.8893597377843641</v>
+      </c>
+      <c r="D46">
+        <v>19.72464026221563</v>
+      </c>
+      <c r="E46">
+        <v>-7.956</v>
+      </c>
+      <c r="F46">
+        <v>25.344</v>
+      </c>
+      <c r="G46">
+        <v>4.73</v>
+      </c>
+      <c r="H46">
+        <v>24.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K46">
+        <v>3.06</v>
+      </c>
+      <c r="L46">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M46">
+        <v>6.052147199999999</v>
+      </c>
+      <c r="N46">
+        <v>-4.295480533333333</v>
+      </c>
+      <c r="O46">
+        <v>-0.6443220799999999</v>
+      </c>
+      <c r="P46">
+        <v>-3.651158453333333</v>
+      </c>
+      <c r="Q46">
+        <v>-0.5911584533333327</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1181261790641659</v>
+      </c>
+      <c r="T46">
+        <v>1.408652113060929</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.04353826688154579</v>
+      </c>
+      <c r="W46">
+        <v>0.2284030618686869</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2902551125436386</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1686480074981551</v>
+      </c>
+      <c r="C47">
+        <v>-1.769170949712223</v>
+      </c>
+      <c r="D47">
+        <v>19.42082905028778</v>
+      </c>
+      <c r="E47">
+        <v>-7.379999999999999</v>
+      </c>
+      <c r="F47">
+        <v>25.92</v>
+      </c>
+      <c r="G47">
+        <v>4.73</v>
+      </c>
+      <c r="H47">
+        <v>24.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K47">
+        <v>3.06</v>
+      </c>
+      <c r="L47">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M47">
+        <v>6.189696</v>
+      </c>
+      <c r="N47">
+        <v>-4.433029333333332</v>
+      </c>
+      <c r="O47">
+        <v>-0.6649543999999997</v>
+      </c>
+      <c r="P47">
+        <v>-3.768074933333332</v>
+      </c>
+      <c r="Q47">
+        <v>-0.7080749333333323</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1195684732289689</v>
+      </c>
+      <c r="T47">
+        <v>1.434263969662037</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.04257074983973366</v>
+      </c>
+      <c r="W47">
+        <v>0.2286341049382716</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2838049989315579</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1706480074981551</v>
+      </c>
+      <c r="C48">
+        <v>-2.639765148271643</v>
+      </c>
+      <c r="D48">
+        <v>19.12623485172836</v>
+      </c>
+      <c r="E48">
+        <v>-6.803999999999998</v>
+      </c>
+      <c r="F48">
+        <v>26.496</v>
+      </c>
+      <c r="G48">
+        <v>4.73</v>
+      </c>
+      <c r="H48">
+        <v>24.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K48">
+        <v>3.06</v>
+      </c>
+      <c r="L48">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M48">
+        <v>6.3272448</v>
+      </c>
+      <c r="N48">
+        <v>-4.570578133333333</v>
+      </c>
+      <c r="O48">
+        <v>-0.68558672</v>
+      </c>
+      <c r="P48">
+        <v>-3.884991413333333</v>
+      </c>
+      <c r="Q48">
+        <v>-0.8249914133333331</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.121064185696172</v>
+      </c>
+      <c r="T48">
+        <v>1.460824413544667</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.04164529875626119</v>
+      </c>
+      <c r="W48">
+        <v>0.2288551026570048</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2776353250417412</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1726480074981551</v>
+      </c>
+      <c r="C49">
+        <v>-3.501555504201921</v>
+      </c>
+      <c r="D49">
+        <v>18.84044449579808</v>
+      </c>
+      <c r="E49">
+        <v>-6.227999999999998</v>
+      </c>
+      <c r="F49">
+        <v>27.072</v>
+      </c>
+      <c r="G49">
+        <v>4.73</v>
+      </c>
+      <c r="H49">
+        <v>24.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K49">
+        <v>3.06</v>
+      </c>
+      <c r="L49">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M49">
+        <v>6.4647936</v>
+      </c>
+      <c r="N49">
+        <v>-4.708126933333332</v>
+      </c>
+      <c r="O49">
+        <v>-0.7062190399999998</v>
+      </c>
+      <c r="P49">
+        <v>-4.001907893333333</v>
+      </c>
+      <c r="Q49">
+        <v>-0.9419078933333327</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1226163401432696</v>
+      </c>
+      <c r="T49">
+        <v>1.488387138328529</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.04075922856995776</v>
+      </c>
+      <c r="W49">
+        <v>0.2290666962174941</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2717281904663852</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1746480074981551</v>
+      </c>
+      <c r="C50">
+        <v>-4.354930856888693</v>
+      </c>
+      <c r="D50">
+        <v>18.5630691431113</v>
+      </c>
+      <c r="E50">
+        <v>-5.652000000000001</v>
+      </c>
+      <c r="F50">
+        <v>27.648</v>
+      </c>
+      <c r="G50">
+        <v>4.73</v>
+      </c>
+      <c r="H50">
+        <v>24.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K50">
+        <v>3.06</v>
+      </c>
+      <c r="L50">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M50">
+        <v>6.6023424</v>
+      </c>
+      <c r="N50">
+        <v>-4.845675733333332</v>
+      </c>
+      <c r="O50">
+        <v>-0.7268513599999997</v>
+      </c>
+      <c r="P50">
+        <v>-4.118824373333332</v>
+      </c>
+      <c r="Q50">
+        <v>-1.058824373333332</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1242281928383325</v>
+      </c>
+      <c r="T50">
+        <v>1.51700996791177</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.0399100779747503</v>
+      </c>
+      <c r="W50">
+        <v>0.2292694733796296</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2660671864983355</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1766480074981551</v>
+      </c>
+      <c r="C51">
+        <v>-5.200257479449554</v>
+      </c>
+      <c r="D51">
+        <v>18.29374252055044</v>
+      </c>
+      <c r="E51">
+        <v>-5.076000000000001</v>
+      </c>
+      <c r="F51">
+        <v>28.224</v>
+      </c>
+      <c r="G51">
+        <v>4.73</v>
+      </c>
+      <c r="H51">
+        <v>24.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K51">
+        <v>3.06</v>
+      </c>
+      <c r="L51">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M51">
+        <v>6.7398912</v>
+      </c>
+      <c r="N51">
+        <v>-4.983224533333333</v>
+      </c>
+      <c r="O51">
+        <v>-0.7474836799999999</v>
+      </c>
+      <c r="P51">
+        <v>-4.235740853333333</v>
+      </c>
+      <c r="Q51">
+        <v>-1.175740853333333</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1259032554430056</v>
+      </c>
+      <c r="T51">
+        <v>1.546755261400235</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03909558658751051</v>
+      </c>
+      <c r="W51">
+        <v>0.2294639739229025</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2606372439167367</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1786480074981551</v>
+      </c>
+      <c r="C52">
+        <v>-6.037880692362215</v>
+      </c>
+      <c r="D52">
+        <v>18.03211930763778</v>
+      </c>
+      <c r="E52">
+        <v>-4.5</v>
+      </c>
+      <c r="F52">
+        <v>28.8</v>
+      </c>
+      <c r="G52">
+        <v>4.73</v>
+      </c>
+      <c r="H52">
+        <v>24.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K52">
+        <v>3.06</v>
+      </c>
+      <c r="L52">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M52">
+        <v>6.87744</v>
+      </c>
+      <c r="N52">
+        <v>-5.120773333333332</v>
+      </c>
+      <c r="O52">
+        <v>-0.7681159999999998</v>
+      </c>
+      <c r="P52">
+        <v>-4.352657333333332</v>
+      </c>
+      <c r="Q52">
+        <v>-1.292657333333332</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1276453205518658</v>
+      </c>
+      <c r="T52">
+        <v>1.57769036662824</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03831367485576029</v>
+      </c>
+      <c r="W52">
+        <v>0.2296506944444444</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.255424499038402</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1806480074981551</v>
+      </c>
+      <c r="C53">
+        <v>-6.868126340583569</v>
+      </c>
+      <c r="D53">
+        <v>17.77787365941643</v>
+      </c>
+      <c r="E53">
+        <v>-3.923999999999999</v>
+      </c>
+      <c r="F53">
+        <v>29.376</v>
+      </c>
+      <c r="G53">
+        <v>4.73</v>
+      </c>
+      <c r="H53">
+        <v>24.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K53">
+        <v>3.06</v>
+      </c>
+      <c r="L53">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M53">
+        <v>7.0149888</v>
+      </c>
+      <c r="N53">
+        <v>-5.258322133333333</v>
+      </c>
+      <c r="O53">
+        <v>-0.7887483199999999</v>
+      </c>
+      <c r="P53">
+        <v>-4.469573813333334</v>
+      </c>
+      <c r="Q53">
+        <v>-1.409573813333334</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1294584903590467</v>
+      </c>
+      <c r="T53">
+        <v>1.60988812921249</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03756242632917676</v>
+      </c>
+      <c r="W53">
+        <v>0.2298300925925926</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.250416175527845</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1826480074981551</v>
+      </c>
+      <c r="C54">
+        <v>-7.691302147445466</v>
+      </c>
+      <c r="D54">
+        <v>17.53069785255453</v>
+      </c>
+      <c r="E54">
+        <v>-3.347999999999999</v>
+      </c>
+      <c r="F54">
+        <v>29.952</v>
+      </c>
+      <c r="G54">
+        <v>4.73</v>
+      </c>
+      <c r="H54">
+        <v>24.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K54">
+        <v>3.06</v>
+      </c>
+      <c r="L54">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M54">
+        <v>7.1525376</v>
+      </c>
+      <c r="N54">
+        <v>-5.395870933333333</v>
+      </c>
+      <c r="O54">
+        <v>-0.8093806399999999</v>
+      </c>
+      <c r="P54">
+        <v>-4.586490293333333</v>
+      </c>
+      <c r="Q54">
+        <v>-1.526490293333333</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1313472089081935</v>
+      </c>
+      <c r="T54">
+        <v>1.64342746523775</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.0368400719766926</v>
+      </c>
+      <c r="W54">
+        <v>0.2300025908119658</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2456004798446172</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1846480074981551</v>
+      </c>
+      <c r="C55">
+        <v>-8.507698957155419</v>
+      </c>
+      <c r="D55">
+        <v>17.29030104284458</v>
+      </c>
+      <c r="E55">
+        <v>-2.771999999999998</v>
+      </c>
+      <c r="F55">
+        <v>30.528</v>
+      </c>
+      <c r="G55">
+        <v>4.73</v>
+      </c>
+      <c r="H55">
+        <v>24.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K55">
+        <v>3.06</v>
+      </c>
+      <c r="L55">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M55">
+        <v>7.2900864</v>
+      </c>
+      <c r="N55">
+        <v>-5.533419733333332</v>
+      </c>
+      <c r="O55">
+        <v>-0.8300129599999998</v>
+      </c>
+      <c r="P55">
+        <v>-4.703406773333333</v>
+      </c>
+      <c r="Q55">
+        <v>-1.643406773333333</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1333162984594317</v>
+      </c>
+      <c r="T55">
+        <v>1.67839400705132</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03614497627901915</v>
+      </c>
+      <c r="W55">
+        <v>0.2301685796645702</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2409665085267944</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1866480074981551</v>
+      </c>
+      <c r="C56">
+        <v>-9.31759187645039</v>
+      </c>
+      <c r="D56">
+        <v>17.05640812354961</v>
+      </c>
+      <c r="E56">
+        <v>-2.195999999999998</v>
+      </c>
+      <c r="F56">
+        <v>31.104</v>
+      </c>
+      <c r="G56">
+        <v>4.73</v>
+      </c>
+      <c r="H56">
+        <v>24.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K56">
+        <v>3.06</v>
+      </c>
+      <c r="L56">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M56">
+        <v>7.4276352</v>
+      </c>
+      <c r="N56">
+        <v>-5.670968533333333</v>
+      </c>
+      <c r="O56">
+        <v>-0.8506452799999999</v>
+      </c>
+      <c r="P56">
+        <v>-4.820323253333333</v>
+      </c>
+      <c r="Q56">
+        <v>-1.760323253333333</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1353710005998541</v>
+      </c>
+      <c r="T56">
+        <v>1.714880833291566</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03547562486644472</v>
+      </c>
+      <c r="W56">
+        <v>0.230328420781893</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2365041657762981</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1886480074981551</v>
+      </c>
+      <c r="C57">
+        <v>-10.12124132482574</v>
+      </c>
+      <c r="D57">
+        <v>16.82875867517426</v>
+      </c>
+      <c r="E57">
+        <v>-1.619999999999997</v>
+      </c>
+      <c r="F57">
+        <v>31.68</v>
+      </c>
+      <c r="G57">
+        <v>4.73</v>
+      </c>
+      <c r="H57">
+        <v>24.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K57">
+        <v>3.06</v>
+      </c>
+      <c r="L57">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M57">
+        <v>7.565184</v>
+      </c>
+      <c r="N57">
+        <v>-5.808517333333333</v>
+      </c>
+      <c r="O57">
+        <v>-0.8712775999999999</v>
+      </c>
+      <c r="P57">
+        <v>-4.937239733333333</v>
+      </c>
+      <c r="Q57">
+        <v>-1.877239733333333</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1375170228354064</v>
+      </c>
+      <c r="T57">
+        <v>1.752989296253601</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.03483061350523663</v>
+      </c>
+      <c r="W57">
+        <v>0.2304824494949495</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2322040900349109</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1906480074981551</v>
+      </c>
+      <c r="C58">
+        <v>-10.91889400176822</v>
+      </c>
+      <c r="D58">
+        <v>16.60710599823178</v>
+      </c>
+      <c r="E58">
+        <v>-1.043999999999997</v>
+      </c>
+      <c r="F58">
+        <v>32.256</v>
+      </c>
+      <c r="G58">
+        <v>4.73</v>
+      </c>
+      <c r="H58">
+        <v>24.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K58">
+        <v>3.06</v>
+      </c>
+      <c r="L58">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M58">
+        <v>7.702732800000001</v>
+      </c>
+      <c r="N58">
+        <v>-5.946066133333334</v>
+      </c>
+      <c r="O58">
+        <v>-0.89190992</v>
+      </c>
+      <c r="P58">
+        <v>-5.054156213333334</v>
+      </c>
+      <c r="Q58">
+        <v>-1.994156213333334</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1397605915362111</v>
+      </c>
+      <c r="T58">
+        <v>1.792829962077546</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.03420863826407169</v>
+      </c>
+      <c r="W58">
+        <v>0.2306309771825397</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2280575884271445</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1926480074981551</v>
+      </c>
+      <c r="C59">
+        <v>-11.71078377854587</v>
+      </c>
+      <c r="D59">
+        <v>16.39121622145413</v>
+      </c>
+      <c r="E59">
+        <v>-0.4679999999999964</v>
+      </c>
+      <c r="F59">
+        <v>32.832</v>
+      </c>
+      <c r="G59">
+        <v>4.73</v>
+      </c>
+      <c r="H59">
+        <v>24.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K59">
+        <v>3.06</v>
+      </c>
+      <c r="L59">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M59">
+        <v>7.840281600000001</v>
+      </c>
+      <c r="N59">
+        <v>-6.083614933333333</v>
+      </c>
+      <c r="O59">
+        <v>-0.9125422399999999</v>
+      </c>
+      <c r="P59">
+        <v>-5.171072693333334</v>
+      </c>
+      <c r="Q59">
+        <v>-2.111072693333333</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1421085122696114</v>
+      </c>
+      <c r="T59">
+        <v>1.834523682125861</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.0336084867155792</v>
+      </c>
+      <c r="W59">
+        <v>0.2307742933723197</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2240565781038614</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1946480074981551</v>
+      </c>
+      <c r="C60">
+        <v>-12.49713252133166</v>
+      </c>
+      <c r="D60">
+        <v>16.18086747866833</v>
+      </c>
+      <c r="E60">
+        <v>0.107999999999997</v>
+      </c>
+      <c r="F60">
+        <v>33.40799999999999</v>
+      </c>
+      <c r="G60">
+        <v>4.73</v>
+      </c>
+      <c r="H60">
+        <v>24.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K60">
+        <v>3.06</v>
+      </c>
+      <c r="L60">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M60">
+        <v>7.977830399999999</v>
+      </c>
+      <c r="N60">
+        <v>-6.221163733333333</v>
+      </c>
+      <c r="O60">
+        <v>-0.9331745599999999</v>
+      </c>
+      <c r="P60">
+        <v>-5.287989173333333</v>
+      </c>
+      <c r="Q60">
+        <v>-2.227989173333333</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1445682387522211</v>
+      </c>
+      <c r="T60">
+        <v>1.878202817414572</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.03302903004806922</v>
+      </c>
+      <c r="W60">
+        <v>0.2309126676245211</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2201935336537948</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1966480074981551</v>
+      </c>
+      <c r="C61">
+        <v>-13.27815085175129</v>
+      </c>
+      <c r="D61">
+        <v>15.9758491482487</v>
+      </c>
+      <c r="E61">
+        <v>0.6839999999999975</v>
+      </c>
+      <c r="F61">
+        <v>33.98399999999999</v>
+      </c>
+      <c r="G61">
+        <v>4.73</v>
+      </c>
+      <c r="H61">
+        <v>24.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K61">
+        <v>3.06</v>
+      </c>
+      <c r="L61">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M61">
+        <v>8.1153792</v>
+      </c>
+      <c r="N61">
+        <v>-6.358712533333332</v>
+      </c>
+      <c r="O61">
+        <v>-0.9538068799999997</v>
+      </c>
+      <c r="P61">
+        <v>-5.404905653333332</v>
+      </c>
+      <c r="Q61">
+        <v>-2.344905653333332</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1471479518925192</v>
+      </c>
+      <c r="T61">
+        <v>1.924012642229561</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.03246921597945788</v>
+      </c>
+      <c r="W61">
+        <v>0.2310463512241055</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2164614398630526</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1986480074981551</v>
+      </c>
+      <c r="C62">
+        <v>-14.05403885033561</v>
+      </c>
+      <c r="D62">
+        <v>15.77596114966438</v>
+      </c>
+      <c r="E62">
+        <v>1.259999999999998</v>
+      </c>
+      <c r="F62">
+        <v>34.56</v>
+      </c>
+      <c r="G62">
+        <v>4.73</v>
+      </c>
+      <c r="H62">
+        <v>24.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K62">
+        <v>3.06</v>
+      </c>
+      <c r="L62">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M62">
+        <v>8.252927999999999</v>
+      </c>
+      <c r="N62">
+        <v>-6.496261333333331</v>
+      </c>
+      <c r="O62">
+        <v>-0.9744391999999996</v>
+      </c>
+      <c r="P62">
+        <v>-5.521822133333331</v>
+      </c>
+      <c r="Q62">
+        <v>-2.461822133333331</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1498566506898322</v>
+      </c>
+      <c r="T62">
+        <v>1.9721129582853</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.03192806237980025</v>
+      </c>
+      <c r="W62">
+        <v>0.2311755787037037</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2128537491986684</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2006480074981551</v>
+      </c>
+      <c r="C63">
+        <v>-14.82498670781658</v>
+      </c>
+      <c r="D63">
+        <v>15.58101329218342</v>
+      </c>
+      <c r="E63">
+        <v>1.835999999999999</v>
+      </c>
+      <c r="F63">
+        <v>35.136</v>
+      </c>
+      <c r="G63">
+        <v>4.73</v>
+      </c>
+      <c r="H63">
+        <v>24.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K63">
+        <v>3.06</v>
+      </c>
+      <c r="L63">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M63">
+        <v>8.3904768</v>
+      </c>
+      <c r="N63">
+        <v>-6.633810133333332</v>
+      </c>
+      <c r="O63">
+        <v>-0.9950715199999998</v>
+      </c>
+      <c r="P63">
+        <v>-5.638738613333333</v>
+      </c>
+      <c r="Q63">
+        <v>-2.578738613333333</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1527042571177766</v>
+      </c>
+      <c r="T63">
+        <v>2.022679957215693</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.031404651521115</v>
+      </c>
+      <c r="W63">
+        <v>0.2313005692167577</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2093643434741</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2026480074981551</v>
+      </c>
+      <c r="C64">
+        <v>-15.59117532872317</v>
+      </c>
+      <c r="D64">
+        <v>15.39082467127683</v>
+      </c>
+      <c r="E64">
+        <v>2.411999999999999</v>
+      </c>
+      <c r="F64">
+        <v>35.712</v>
+      </c>
+      <c r="G64">
+        <v>4.73</v>
+      </c>
+      <c r="H64">
+        <v>24.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K64">
+        <v>3.06</v>
+      </c>
+      <c r="L64">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M64">
+        <v>8.528025599999999</v>
+      </c>
+      <c r="N64">
+        <v>-6.771358933333332</v>
+      </c>
+      <c r="O64">
+        <v>-1.01570384</v>
+      </c>
+      <c r="P64">
+        <v>-5.755655093333332</v>
+      </c>
+      <c r="Q64">
+        <v>-2.695655093333332</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1557017375682444</v>
+      </c>
+      <c r="T64">
+        <v>2.075908377142421</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03089812488367766</v>
+      </c>
+      <c r="W64">
+        <v>0.2314215277777778</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2059874992245178</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2046480074981551</v>
+      </c>
+      <c r="C65">
+        <v>-16.35277689130388</v>
+      </c>
+      <c r="D65">
+        <v>15.20522310869612</v>
+      </c>
+      <c r="E65">
+        <v>2.988</v>
+      </c>
+      <c r="F65">
+        <v>36.288</v>
+      </c>
+      <c r="G65">
+        <v>4.73</v>
+      </c>
+      <c r="H65">
+        <v>24.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K65">
+        <v>3.06</v>
+      </c>
+      <c r="L65">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M65">
+        <v>8.665574399999999</v>
+      </c>
+      <c r="N65">
+        <v>-6.908907733333331</v>
+      </c>
+      <c r="O65">
+        <v>-1.03633616</v>
+      </c>
+      <c r="P65">
+        <v>-5.872571573333332</v>
+      </c>
+      <c r="Q65">
+        <v>-2.812571573333332</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1588612439890078</v>
+      </c>
+      <c r="T65">
+        <v>2.132014008957082</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03040767845695262</v>
+      </c>
+      <c r="W65">
+        <v>0.2315386463844797</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2027178563796842</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2066480074981551</v>
+      </c>
+      <c r="C66">
+        <v>-17.1099553674185</v>
+      </c>
+      <c r="D66">
+        <v>15.02404463258149</v>
+      </c>
+      <c r="E66">
+        <v>3.564</v>
+      </c>
+      <c r="F66">
+        <v>36.864</v>
+      </c>
+      <c r="G66">
+        <v>4.73</v>
+      </c>
+      <c r="H66">
+        <v>24.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K66">
+        <v>3.06</v>
+      </c>
+      <c r="L66">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M66">
+        <v>8.8031232</v>
+      </c>
+      <c r="N66">
+        <v>-7.046456533333332</v>
+      </c>
+      <c r="O66">
+        <v>-1.05696848</v>
+      </c>
+      <c r="P66">
+        <v>-5.989488053333332</v>
+      </c>
+      <c r="Q66">
+        <v>-2.929488053333332</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.162196278544258</v>
+      </c>
+      <c r="T66">
+        <v>2.191236620317</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02993255848106273</v>
+      </c>
+      <c r="W66">
+        <v>0.2316521050347222</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1995503898737516</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2086480074981551</v>
+      </c>
+      <c r="C67">
+        <v>-17.86286700569892</v>
+      </c>
+      <c r="D67">
+        <v>14.84713299430108</v>
+      </c>
+      <c r="E67">
+        <v>4.140000000000001</v>
+      </c>
+      <c r="F67">
+        <v>37.44</v>
+      </c>
+      <c r="G67">
+        <v>4.73</v>
+      </c>
+      <c r="H67">
+        <v>24.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K67">
+        <v>3.06</v>
+      </c>
+      <c r="L67">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M67">
+        <v>8.940671999999999</v>
+      </c>
+      <c r="N67">
+        <v>-7.184005333333332</v>
+      </c>
+      <c r="O67">
+        <v>-1.0776008</v>
+      </c>
+      <c r="P67">
+        <v>-6.106404533333332</v>
+      </c>
+      <c r="Q67">
+        <v>-3.046404533333332</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1657218865026654</v>
+      </c>
+      <c r="T67">
+        <v>2.253843380897486</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02947205758135407</v>
+      </c>
+      <c r="W67">
+        <v>0.2317620726495727</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1964803838756939</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2106480074981551</v>
+      </c>
+      <c r="C68">
+        <v>-18.61166078097106</v>
+      </c>
+      <c r="D68">
+        <v>14.67433921902894</v>
+      </c>
+      <c r="E68">
+        <v>4.716000000000001</v>
+      </c>
+      <c r="F68">
+        <v>38.016</v>
+      </c>
+      <c r="G68">
+        <v>4.73</v>
+      </c>
+      <c r="H68">
+        <v>24.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K68">
+        <v>3.06</v>
+      </c>
+      <c r="L68">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M68">
+        <v>9.0782208</v>
+      </c>
+      <c r="N68">
+        <v>-7.321554133333333</v>
+      </c>
+      <c r="O68">
+        <v>-1.09823312</v>
+      </c>
+      <c r="P68">
+        <v>-6.223321013333333</v>
+      </c>
+      <c r="Q68">
+        <v>-3.163321013333333</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1694548831645085</v>
+      </c>
+      <c r="T68">
+        <v>2.320132892100354</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02902551125436386</v>
+      </c>
+      <c r="W68">
+        <v>0.2318687079124579</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1935034083624257</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2126480074981551</v>
+      </c>
+      <c r="C69">
+        <v>-19.35647881265525</v>
+      </c>
+      <c r="D69">
+        <v>14.50552118734474</v>
+      </c>
+      <c r="E69">
+        <v>5.292000000000002</v>
+      </c>
+      <c r="F69">
+        <v>38.592</v>
+      </c>
+      <c r="G69">
+        <v>4.73</v>
+      </c>
+      <c r="H69">
+        <v>24.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K69">
+        <v>3.06</v>
+      </c>
+      <c r="L69">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M69">
+        <v>9.2157696</v>
+      </c>
+      <c r="N69">
+        <v>-7.459102933333332</v>
+      </c>
+      <c r="O69">
+        <v>-1.11886544</v>
+      </c>
+      <c r="P69">
+        <v>-6.340237493333333</v>
+      </c>
+      <c r="Q69">
+        <v>-3.280237493333332</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1734141220482815</v>
+      </c>
+      <c r="T69">
+        <v>2.390439949436728</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02859229466847783</v>
+      </c>
+      <c r="W69">
+        <v>0.2319721600331675</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1906152977898523</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2146480074981551</v>
+      </c>
+      <c r="C70">
+        <v>-20.09745675461456</v>
+      </c>
+      <c r="D70">
+        <v>14.34054324538544</v>
+      </c>
+      <c r="E70">
+        <v>5.868000000000002</v>
+      </c>
+      <c r="F70">
+        <v>39.168</v>
+      </c>
+      <c r="G70">
+        <v>4.73</v>
+      </c>
+      <c r="H70">
+        <v>24.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K70">
+        <v>3.06</v>
+      </c>
+      <c r="L70">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M70">
+        <v>9.353318400000001</v>
+      </c>
+      <c r="N70">
+        <v>-7.596651733333333</v>
+      </c>
+      <c r="O70">
+        <v>-1.13949776</v>
+      </c>
+      <c r="P70">
+        <v>-6.457153973333333</v>
+      </c>
+      <c r="Q70">
+        <v>-3.397153973333333</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1776208133622903</v>
+      </c>
+      <c r="T70">
+        <v>2.465141197856626</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02817181974688257</v>
+      </c>
+      <c r="W70">
+        <v>0.2320725694444445</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1878121316458838</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2166480074981552</v>
+      </c>
+      <c r="C71">
+        <v>-20.83472415869874</v>
+      </c>
+      <c r="D71">
+        <v>14.17927584130125</v>
+      </c>
+      <c r="E71">
+        <v>6.444000000000003</v>
+      </c>
+      <c r="F71">
+        <v>39.744</v>
+      </c>
+      <c r="G71">
+        <v>4.73</v>
+      </c>
+      <c r="H71">
+        <v>24.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K71">
+        <v>3.06</v>
+      </c>
+      <c r="L71">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M71">
+        <v>9.4908672</v>
+      </c>
+      <c r="N71">
+        <v>-7.734200533333333</v>
+      </c>
+      <c r="O71">
+        <v>-1.16013008</v>
+      </c>
+      <c r="P71">
+        <v>-6.574070453333333</v>
+      </c>
+      <c r="Q71">
+        <v>-3.514070453333332</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1820989041159126</v>
+      </c>
+      <c r="T71">
+        <v>2.544661881658453</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02776353250417413</v>
+      </c>
+      <c r="W71">
+        <v>0.2321700684380033</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1850902166944942</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2186480074981551</v>
+      </c>
+      <c r="C72">
+        <v>-21.56840481403151</v>
+      </c>
+      <c r="D72">
+        <v>14.02159518596849</v>
+      </c>
+      <c r="E72">
+        <v>7.020000000000003</v>
+      </c>
+      <c r="F72">
+        <v>40.32</v>
+      </c>
+      <c r="G72">
+        <v>4.73</v>
+      </c>
+      <c r="H72">
+        <v>24.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K72">
+        <v>3.06</v>
+      </c>
+      <c r="L72">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M72">
+        <v>9.628416000000001</v>
+      </c>
+      <c r="N72">
+        <v>-7.871749333333334</v>
+      </c>
+      <c r="O72">
+        <v>-1.1807624</v>
+      </c>
+      <c r="P72">
+        <v>-6.690986933333334</v>
+      </c>
+      <c r="Q72">
+        <v>-3.630986933333334</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1868755342531096</v>
+      </c>
+      <c r="T72">
+        <v>2.629483944380401</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02736691061125735</v>
+      </c>
+      <c r="W72">
+        <v>0.2322647817460317</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1824460707417157</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2206480074981551</v>
+      </c>
+      <c r="C73">
+        <v>-22.29861706390849</v>
+      </c>
+      <c r="D73">
+        <v>13.86738293609151</v>
+      </c>
+      <c r="E73">
+        <v>7.595999999999997</v>
+      </c>
+      <c r="F73">
+        <v>40.89599999999999</v>
+      </c>
+      <c r="G73">
+        <v>4.73</v>
+      </c>
+      <c r="H73">
+        <v>24.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K73">
+        <v>3.06</v>
+      </c>
+      <c r="L73">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M73">
+        <v>9.765964799999999</v>
+      </c>
+      <c r="N73">
+        <v>-8.009298133333331</v>
+      </c>
+      <c r="O73">
+        <v>-1.20139472</v>
+      </c>
+      <c r="P73">
+        <v>-6.807903413333332</v>
+      </c>
+      <c r="Q73">
+        <v>-3.747903413333332</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1919815871583893</v>
+      </c>
+      <c r="T73">
+        <v>2.720155804531449</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02698146116602838</v>
+      </c>
+      <c r="W73">
+        <v>0.2323568270735524</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1798764077735225</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2226480074981551</v>
+      </c>
+      <c r="C74">
+        <v>-23.0254741020108</v>
+      </c>
+      <c r="D74">
+        <v>13.71652589798919</v>
+      </c>
+      <c r="E74">
+        <v>8.171999999999997</v>
+      </c>
+      <c r="F74">
+        <v>41.47199999999999</v>
+      </c>
+      <c r="G74">
+        <v>4.73</v>
+      </c>
+      <c r="H74">
+        <v>24.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K74">
+        <v>3.06</v>
+      </c>
+      <c r="L74">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M74">
+        <v>9.903513599999998</v>
+      </c>
+      <c r="N74">
+        <v>-8.146846933333331</v>
+      </c>
+      <c r="O74">
+        <v>-1.22202704</v>
+      </c>
+      <c r="P74">
+        <v>-6.924819893333331</v>
+      </c>
+      <c r="Q74">
+        <v>-3.864819893333331</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1974523581283317</v>
+      </c>
+      <c r="T74">
+        <v>2.817304226121858</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02660671864983354</v>
+      </c>
+      <c r="W74">
+        <v>0.2324463155864198</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1773781243322237</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2246480074981551</v>
+      </c>
+      <c r="C75">
+        <v>-23.74908424949248</v>
+      </c>
+      <c r="D75">
+        <v>13.56891575050752</v>
+      </c>
+      <c r="E75">
+        <v>8.747999999999998</v>
+      </c>
+      <c r="F75">
+        <v>42.04799999999999</v>
+      </c>
+      <c r="G75">
+        <v>4.73</v>
+      </c>
+      <c r="H75">
+        <v>24.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K75">
+        <v>3.06</v>
+      </c>
+      <c r="L75">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M75">
+        <v>10.0410624</v>
+      </c>
+      <c r="N75">
+        <v>-8.284395733333332</v>
+      </c>
+      <c r="O75">
+        <v>-1.24265936</v>
+      </c>
+      <c r="P75">
+        <v>-7.041736373333332</v>
+      </c>
+      <c r="Q75">
+        <v>-3.981736373333332</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.203328371392344</v>
+      </c>
+      <c r="T75">
+        <v>2.921648827089334</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02624224305189061</v>
+      </c>
+      <c r="W75">
+        <v>0.2325333523592085</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1749482870126041</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2266480074981551</v>
+      </c>
+      <c r="C76">
+        <v>-24.46955121436716</v>
+      </c>
+      <c r="D76">
+        <v>13.42444878563284</v>
+      </c>
+      <c r="E76">
+        <v>9.323999999999998</v>
+      </c>
+      <c r="F76">
+        <v>42.624</v>
+      </c>
+      <c r="G76">
+        <v>4.73</v>
+      </c>
+      <c r="H76">
+        <v>24.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K76">
+        <v>3.06</v>
+      </c>
+      <c r="L76">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M76">
+        <v>10.1786112</v>
+      </c>
+      <c r="N76">
+        <v>-8.421944533333331</v>
+      </c>
+      <c r="O76">
+        <v>-1.26329168</v>
+      </c>
+      <c r="P76">
+        <v>-7.158652853333331</v>
+      </c>
+      <c r="Q76">
+        <v>-4.098652853333331</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2096563856766649</v>
+      </c>
+      <c r="T76">
+        <v>3.034019935823539</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02588761814578399</v>
+      </c>
+      <c r="W76">
+        <v>0.2326180367867868</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1725841209718932</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2286480074981551</v>
+      </c>
+      <c r="C77">
+        <v>-25.18697433449933</v>
+      </c>
+      <c r="D77">
+        <v>13.28302566550066</v>
+      </c>
+      <c r="E77">
+        <v>9.899999999999999</v>
+      </c>
+      <c r="F77">
+        <v>43.2</v>
+      </c>
+      <c r="G77">
+        <v>4.73</v>
+      </c>
+      <c r="H77">
+        <v>24.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K77">
+        <v>3.06</v>
+      </c>
+      <c r="L77">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M77">
+        <v>10.31616</v>
+      </c>
+      <c r="N77">
+        <v>-8.559493333333332</v>
+      </c>
+      <c r="O77">
+        <v>-1.283924</v>
+      </c>
+      <c r="P77">
+        <v>-7.275569333333332</v>
+      </c>
+      <c r="Q77">
+        <v>-4.215569333333333</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2164906411037315</v>
+      </c>
+      <c r="T77">
+        <v>3.15538073325648</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0255424499038402</v>
+      </c>
+      <c r="W77">
+        <v>0.232700462962963</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1702829993589347</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2306480074981551</v>
+      </c>
+      <c r="C78">
+        <v>-25.9014488053966</v>
+      </c>
+      <c r="D78">
+        <v>13.1445511946034</v>
+      </c>
+      <c r="E78">
+        <v>10.476</v>
+      </c>
+      <c r="F78">
+        <v>43.776</v>
+      </c>
+      <c r="G78">
+        <v>4.73</v>
+      </c>
+      <c r="H78">
+        <v>24.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K78">
+        <v>3.06</v>
+      </c>
+      <c r="L78">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M78">
+        <v>10.4537088</v>
+      </c>
+      <c r="N78">
+        <v>-8.697042133333332</v>
+      </c>
+      <c r="O78">
+        <v>-1.30455632</v>
+      </c>
+      <c r="P78">
+        <v>-7.392485813333332</v>
+      </c>
+      <c r="Q78">
+        <v>-4.332485813333331</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.223894417816387</v>
+      </c>
+      <c r="T78">
+        <v>3.286854930475501</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02520636503668441</v>
+      </c>
+      <c r="W78">
+        <v>0.2327807200292398</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1680424335778961</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2326480074981551</v>
+      </c>
+      <c r="C79">
+        <v>-26.61306589390063</v>
+      </c>
+      <c r="D79">
+        <v>13.00893410609937</v>
+      </c>
+      <c r="E79">
+        <v>11.052</v>
+      </c>
+      <c r="F79">
+        <v>44.352</v>
+      </c>
+      <c r="G79">
+        <v>4.73</v>
+      </c>
+      <c r="H79">
+        <v>24.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K79">
+        <v>3.06</v>
+      </c>
+      <c r="L79">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M79">
+        <v>10.5912576</v>
+      </c>
+      <c r="N79">
+        <v>-8.834590933333333</v>
+      </c>
+      <c r="O79">
+        <v>-1.32518864</v>
+      </c>
+      <c r="P79">
+        <v>-7.509402293333332</v>
+      </c>
+      <c r="Q79">
+        <v>-4.449402293333332</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2319420011997082</v>
+      </c>
+      <c r="T79">
+        <v>3.429761666583131</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02487900964659759</v>
+      </c>
+      <c r="W79">
+        <v>0.2328588924963925</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1658600643106507</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2346480074981551</v>
+      </c>
+      <c r="C80">
+        <v>-27.32191313878487</v>
+      </c>
+      <c r="D80">
+        <v>12.87608686121512</v>
+      </c>
+      <c r="E80">
+        <v>11.628</v>
+      </c>
+      <c r="F80">
+        <v>44.928</v>
+      </c>
+      <c r="G80">
+        <v>4.73</v>
+      </c>
+      <c r="H80">
+        <v>24.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K80">
+        <v>3.06</v>
+      </c>
+      <c r="L80">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M80">
+        <v>10.7288064</v>
+      </c>
+      <c r="N80">
+        <v>-8.972139733333332</v>
+      </c>
+      <c r="O80">
+        <v>-1.34582096</v>
+      </c>
+      <c r="P80">
+        <v>-7.626318773333333</v>
+      </c>
+      <c r="Q80">
+        <v>-4.566318773333332</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2407211830724222</v>
+      </c>
+      <c r="T80">
+        <v>3.585659924155092</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02456004798446173</v>
+      </c>
+      <c r="W80">
+        <v>0.2329350605413106</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1637336532297449</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2366480074981551</v>
+      </c>
+      <c r="C81">
+        <v>-28.02807453918549</v>
+      </c>
+      <c r="D81">
+        <v>12.74592546081451</v>
+      </c>
+      <c r="E81">
+        <v>12.204</v>
+      </c>
+      <c r="F81">
+        <v>45.504</v>
+      </c>
+      <c r="G81">
+        <v>4.73</v>
+      </c>
+      <c r="H81">
+        <v>24.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K81">
+        <v>3.06</v>
+      </c>
+      <c r="L81">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M81">
+        <v>10.8663552</v>
+      </c>
+      <c r="N81">
+        <v>-9.109688533333332</v>
+      </c>
+      <c r="O81">
+        <v>-1.36645328</v>
+      </c>
+      <c r="P81">
+        <v>-7.743235253333332</v>
+      </c>
+      <c r="Q81">
+        <v>-4.683235253333331</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2503364775044423</v>
+      </c>
+      <c r="T81">
+        <v>3.756405634829144</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02424916130111411</v>
+      </c>
+      <c r="W81">
+        <v>0.233009300281294</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1616610753407608</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2386480074981551</v>
+      </c>
+      <c r="C82">
+        <v>-28.73163073171778</v>
+      </c>
+      <c r="D82">
+        <v>12.61836926828222</v>
+      </c>
+      <c r="E82">
+        <v>12.78</v>
+      </c>
+      <c r="F82">
+        <v>46.08</v>
+      </c>
+      <c r="G82">
+        <v>4.73</v>
+      </c>
+      <c r="H82">
+        <v>24.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K82">
+        <v>3.06</v>
+      </c>
+      <c r="L82">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M82">
+        <v>11.003904</v>
+      </c>
+      <c r="N82">
+        <v>-9.247237333333333</v>
+      </c>
+      <c r="O82">
+        <v>-1.3870856</v>
+      </c>
+      <c r="P82">
+        <v>-7.860151733333333</v>
+      </c>
+      <c r="Q82">
+        <v>-4.800151733333333</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2609133013796645</v>
+      </c>
+      <c r="T82">
+        <v>3.944225916570602</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02394604678485019</v>
+      </c>
+      <c r="W82">
+        <v>0.2330816840277778</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1596403118990013</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2406480074981551</v>
+      </c>
+      <c r="C83">
+        <v>-29.432659157063</v>
+      </c>
+      <c r="D83">
+        <v>12.493340842937</v>
+      </c>
+      <c r="E83">
+        <v>13.356</v>
+      </c>
+      <c r="F83">
+        <v>46.656</v>
+      </c>
+      <c r="G83">
+        <v>4.73</v>
+      </c>
+      <c r="H83">
+        <v>24.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K83">
+        <v>3.06</v>
+      </c>
+      <c r="L83">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M83">
+        <v>11.1414528</v>
+      </c>
+      <c r="N83">
+        <v>-9.384786133333332</v>
+      </c>
+      <c r="O83">
+        <v>-1.40771792</v>
+      </c>
+      <c r="P83">
+        <v>-7.977068213333332</v>
+      </c>
+      <c r="Q83">
+        <v>-4.917068213333332</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.272603475136489</v>
+      </c>
+      <c r="T83">
+        <v>4.151816754284845</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02365041657762981</v>
+      </c>
+      <c r="W83">
+        <v>0.233152280521262</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1576694438508655</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2426480074981551</v>
+      </c>
+      <c r="C84">
+        <v>-30.13123421674858</v>
+      </c>
+      <c r="D84">
+        <v>12.37076578325142</v>
+      </c>
+      <c r="E84">
+        <v>13.932</v>
+      </c>
+      <c r="F84">
+        <v>47.232</v>
+      </c>
+      <c r="G84">
+        <v>4.73</v>
+      </c>
+      <c r="H84">
+        <v>24.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K84">
+        <v>3.06</v>
+      </c>
+      <c r="L84">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M84">
+        <v>11.2790016</v>
+      </c>
+      <c r="N84">
+        <v>-9.522334933333333</v>
+      </c>
+      <c r="O84">
+        <v>-1.42835024</v>
+      </c>
+      <c r="P84">
+        <v>-8.093984693333333</v>
+      </c>
+      <c r="Q84">
+        <v>-5.033984693333332</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2855925570885161</v>
+      </c>
+      <c r="T84">
+        <v>4.382473240634003</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02336199686326847</v>
+      </c>
+      <c r="W84">
+        <v>0.2332211551490515</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1557466457551232</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2446480074981551</v>
+      </c>
+      <c r="C85">
+        <v>-30.82742742078882</v>
+      </c>
+      <c r="D85">
+        <v>12.25057257921118</v>
+      </c>
+      <c r="E85">
+        <v>14.508</v>
+      </c>
+      <c r="F85">
+        <v>47.808</v>
+      </c>
+      <c r="G85">
+        <v>4.73</v>
+      </c>
+      <c r="H85">
+        <v>24.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K85">
+        <v>3.06</v>
+      </c>
+      <c r="L85">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M85">
+        <v>11.4165504</v>
+      </c>
+      <c r="N85">
+        <v>-9.659883733333333</v>
+      </c>
+      <c r="O85">
+        <v>-1.44898256</v>
+      </c>
+      <c r="P85">
+        <v>-8.210901173333333</v>
+      </c>
+      <c r="Q85">
+        <v>-5.150901173333333</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3001097663290171</v>
+      </c>
+      <c r="T85">
+        <v>4.640265784200709</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02308052702154234</v>
+      </c>
+      <c r="W85">
+        <v>0.2332883701472557</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1538701801436156</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2466480074981551</v>
+      </c>
+      <c r="C86">
+        <v>-31.52130752680157</v>
+      </c>
+      <c r="D86">
+        <v>12.13269247319842</v>
+      </c>
+      <c r="E86">
+        <v>15.084</v>
+      </c>
+      <c r="F86">
+        <v>48.38399999999999</v>
+      </c>
+      <c r="G86">
+        <v>4.73</v>
+      </c>
+      <c r="H86">
+        <v>24.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K86">
+        <v>3.06</v>
+      </c>
+      <c r="L86">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M86">
+        <v>11.5540992</v>
+      </c>
+      <c r="N86">
+        <v>-9.797432533333332</v>
+      </c>
+      <c r="O86">
+        <v>-1.46961488</v>
+      </c>
+      <c r="P86">
+        <v>-8.327817653333332</v>
+      </c>
+      <c r="Q86">
+        <v>-5.267817653333331</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3164416267245805</v>
+      </c>
+      <c r="T86">
+        <v>4.930282395713251</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02280575884271446</v>
+      </c>
+      <c r="W86">
+        <v>0.2333539847883598</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1520383922847631</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2486480074981551</v>
+      </c>
+      <c r="C87">
+        <v>-32.21294067116969</v>
+      </c>
+      <c r="D87">
+        <v>12.0170593288303</v>
+      </c>
+      <c r="E87">
+        <v>15.66</v>
+      </c>
+      <c r="F87">
+        <v>48.95999999999999</v>
+      </c>
+      <c r="G87">
+        <v>4.73</v>
+      </c>
+      <c r="H87">
+        <v>24.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K87">
+        <v>3.06</v>
+      </c>
+      <c r="L87">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M87">
+        <v>11.691648</v>
+      </c>
+      <c r="N87">
+        <v>-9.934981333333331</v>
+      </c>
+      <c r="O87">
+        <v>-1.4902472</v>
+      </c>
+      <c r="P87">
+        <v>-8.444734133333332</v>
+      </c>
+      <c r="Q87">
+        <v>-5.384734133333332</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3349510685062192</v>
+      </c>
+      <c r="T87">
+        <v>5.2589678887608</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02253745579750606</v>
+      </c>
+      <c r="W87">
+        <v>0.2334180555555556</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1502497053167071</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2506480074981551</v>
+      </c>
+      <c r="C88">
+        <v>-32.9023904927729</v>
+      </c>
+      <c r="D88">
+        <v>11.90360950722709</v>
+      </c>
+      <c r="E88">
+        <v>16.236</v>
+      </c>
+      <c r="F88">
+        <v>49.53599999999999</v>
+      </c>
+      <c r="G88">
+        <v>4.73</v>
+      </c>
+      <c r="H88">
+        <v>24.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K88">
+        <v>3.06</v>
+      </c>
+      <c r="L88">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M88">
+        <v>11.8291968</v>
+      </c>
+      <c r="N88">
+        <v>-10.07253013333333</v>
+      </c>
+      <c r="O88">
+        <v>-1.51087952</v>
+      </c>
+      <c r="P88">
+        <v>-8.561650613333333</v>
+      </c>
+      <c r="Q88">
+        <v>-5.501650613333332</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3561047162566635</v>
+      </c>
+      <c r="T88">
+        <v>5.634608452243715</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02227539235800017</v>
+      </c>
+      <c r="W88">
+        <v>0.2334806363049096</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1485026157200012</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2526480074981551</v>
+      </c>
+      <c r="C89">
+        <v>-33.58971824977648</v>
+      </c>
+      <c r="D89">
+        <v>11.79228175022351</v>
+      </c>
+      <c r="E89">
+        <v>16.812</v>
+      </c>
+      <c r="F89">
+        <v>50.11199999999999</v>
+      </c>
+      <c r="G89">
+        <v>4.73</v>
+      </c>
+      <c r="H89">
+        <v>24.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K89">
+        <v>3.06</v>
+      </c>
+      <c r="L89">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M89">
+        <v>11.9667456</v>
+      </c>
+      <c r="N89">
+        <v>-10.21007893333333</v>
+      </c>
+      <c r="O89">
+        <v>-1.53151184</v>
+      </c>
+      <c r="P89">
+        <v>-8.678567093333331</v>
+      </c>
+      <c r="Q89">
+        <v>-5.618567093333331</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3805127713533298</v>
+      </c>
+      <c r="T89">
+        <v>6.068039871647078</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02201935336537948</v>
+      </c>
+      <c r="W89">
+        <v>0.2335417784163474</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1467956891025299</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2546480074981551</v>
+      </c>
+      <c r="C90">
+        <v>-34.27498292992716</v>
+      </c>
+      <c r="D90">
+        <v>11.68301707007284</v>
+      </c>
+      <c r="E90">
+        <v>17.388</v>
+      </c>
+      <c r="F90">
+        <v>50.688</v>
+      </c>
+      <c r="G90">
+        <v>4.73</v>
+      </c>
+      <c r="H90">
+        <v>24.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K90">
+        <v>3.06</v>
+      </c>
+      <c r="L90">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M90">
+        <v>12.1042944</v>
+      </c>
+      <c r="N90">
+        <v>-10.34762773333333</v>
+      </c>
+      <c r="O90">
+        <v>-1.55214416</v>
+      </c>
+      <c r="P90">
+        <v>-8.795483573333332</v>
+      </c>
+      <c r="Q90">
+        <v>-5.735483573333331</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.408988835632774</v>
+      </c>
+      <c r="T90">
+        <v>6.573709860951001</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0217691334407729</v>
+      </c>
+      <c r="W90">
+        <v>0.2336015309343434</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1451275562718194</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2566480074981551</v>
+      </c>
+      <c r="C91">
+        <v>-34.95824135477341</v>
+      </c>
+      <c r="D91">
+        <v>11.57575864522659</v>
+      </c>
+      <c r="E91">
+        <v>17.964</v>
+      </c>
+      <c r="F91">
+        <v>51.264</v>
+      </c>
+      <c r="G91">
+        <v>4.73</v>
+      </c>
+      <c r="H91">
+        <v>24.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K91">
+        <v>3.06</v>
+      </c>
+      <c r="L91">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M91">
+        <v>12.2418432</v>
+      </c>
+      <c r="N91">
+        <v>-10.48517653333333</v>
+      </c>
+      <c r="O91">
+        <v>-1.57277648</v>
+      </c>
+      <c r="P91">
+        <v>-8.912400053333332</v>
+      </c>
+      <c r="Q91">
+        <v>-5.852400053333332</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4426423661448445</v>
+      </c>
+      <c r="T91">
+        <v>7.171319848310184</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02152453643582039</v>
+      </c>
+      <c r="W91">
+        <v>0.2336599406991261</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.143496909572136</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2586480074981551</v>
+      </c>
+      <c r="C92">
+        <v>-35.63954827819708</v>
+      </c>
+      <c r="D92">
+        <v>11.47045172180292</v>
+      </c>
+      <c r="E92">
+        <v>18.54</v>
+      </c>
+      <c r="F92">
+        <v>51.84</v>
+      </c>
+      <c r="G92">
+        <v>4.73</v>
+      </c>
+      <c r="H92">
+        <v>24.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K92">
+        <v>3.06</v>
+      </c>
+      <c r="L92">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M92">
+        <v>12.379392</v>
+      </c>
+      <c r="N92">
+        <v>-10.62272533333333</v>
+      </c>
+      <c r="O92">
+        <v>-1.5934088</v>
+      </c>
+      <c r="P92">
+        <v>-9.029316533333333</v>
+      </c>
+      <c r="Q92">
+        <v>-5.969316533333332</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4830266027593289</v>
+      </c>
+      <c r="T92">
+        <v>7.888451833141203</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02128537491986683</v>
+      </c>
+      <c r="W92">
+        <v>0.2337170524691358</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1419024994657789</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2606480074981551</v>
+      </c>
+      <c r="C93">
+        <v>-36.31895647961532</v>
+      </c>
+      <c r="D93">
+        <v>11.36704352038468</v>
+      </c>
+      <c r="E93">
+        <v>19.116</v>
+      </c>
+      <c r="F93">
+        <v>52.416</v>
+      </c>
+      <c r="G93">
+        <v>4.73</v>
+      </c>
+      <c r="H93">
+        <v>24.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K93">
+        <v>3.06</v>
+      </c>
+      <c r="L93">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M93">
+        <v>12.5169408</v>
+      </c>
+      <c r="N93">
+        <v>-10.76027413333333</v>
+      </c>
+      <c r="O93">
+        <v>-1.61404112</v>
+      </c>
+      <c r="P93">
+        <v>-9.146233013333333</v>
+      </c>
+      <c r="Q93">
+        <v>-6.086233013333333</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5323851141770322</v>
+      </c>
+      <c r="T93">
+        <v>8.764946481268005</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02105146970096719</v>
+      </c>
+      <c r="W93">
+        <v>0.2337729090354091</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1403431313397814</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2626480074981551</v>
+      </c>
+      <c r="C94">
+        <v>-36.99651685218623</v>
+      </c>
+      <c r="D94">
+        <v>11.26548314781377</v>
+      </c>
+      <c r="E94">
+        <v>19.692</v>
+      </c>
+      <c r="F94">
+        <v>52.992</v>
+      </c>
+      <c r="G94">
+        <v>4.73</v>
+      </c>
+      <c r="H94">
+        <v>24.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K94">
+        <v>3.06</v>
+      </c>
+      <c r="L94">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M94">
+        <v>12.6544896</v>
+      </c>
+      <c r="N94">
+        <v>-10.89782293333333</v>
+      </c>
+      <c r="O94">
+        <v>-1.63467344</v>
+      </c>
+      <c r="P94">
+        <v>-9.263149493333332</v>
+      </c>
+      <c r="Q94">
+        <v>-6.203149493333331</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5940832534491614</v>
+      </c>
+      <c r="T94">
+        <v>9.860564791426507</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02082264937813059</v>
+      </c>
+      <c r="W94">
+        <v>0.2338275513285024</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1388176625208707</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2646480074981551</v>
+      </c>
+      <c r="C95">
+        <v>-37.67227848632777</v>
+      </c>
+      <c r="D95">
+        <v>11.16572151367223</v>
+      </c>
+      <c r="E95">
+        <v>20.268</v>
+      </c>
+      <c r="F95">
+        <v>53.568</v>
+      </c>
+      <c r="G95">
+        <v>4.73</v>
+      </c>
+      <c r="H95">
+        <v>24.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K95">
+        <v>3.06</v>
+      </c>
+      <c r="L95">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M95">
+        <v>12.7920384</v>
+      </c>
+      <c r="N95">
+        <v>-11.03537173333333</v>
+      </c>
+      <c r="O95">
+        <v>-1.65530576</v>
+      </c>
+      <c r="P95">
+        <v>-9.380065973333334</v>
+      </c>
+      <c r="Q95">
+        <v>-6.320065973333334</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6734094325133273</v>
+      </c>
+      <c r="T95">
+        <v>11.26921690448744</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02059874992245177</v>
+      </c>
+      <c r="W95">
+        <v>0.2338810185185185</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1373249994830118</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2666480074981551</v>
+      </c>
+      <c r="C96">
+        <v>-38.34628874883808</v>
+      </c>
+      <c r="D96">
+        <v>11.06771125116192</v>
+      </c>
+      <c r="E96">
+        <v>20.844</v>
+      </c>
+      <c r="F96">
+        <v>54.144</v>
+      </c>
+      <c r="G96">
+        <v>4.73</v>
+      </c>
+      <c r="H96">
+        <v>24.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K96">
+        <v>3.06</v>
+      </c>
+      <c r="L96">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M96">
+        <v>12.9295872</v>
+      </c>
+      <c r="N96">
+        <v>-11.17292053333333</v>
+      </c>
+      <c r="O96">
+        <v>-1.67593808</v>
+      </c>
+      <c r="P96">
+        <v>-9.496982453333333</v>
+      </c>
+      <c r="Q96">
+        <v>-6.436982453333332</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7791776712655487</v>
+      </c>
+      <c r="T96">
+        <v>13.14741972190201</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02037961428497888</v>
+      </c>
+      <c r="W96">
+        <v>0.2339333481087471</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1358640952331925</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2686480074981551</v>
+      </c>
+      <c r="C97">
+        <v>-39.018593357885</v>
+      </c>
+      <c r="D97">
+        <v>10.971406642115</v>
+      </c>
+      <c r="E97">
+        <v>21.42</v>
+      </c>
+      <c r="F97">
+        <v>54.72</v>
+      </c>
+      <c r="G97">
+        <v>4.73</v>
+      </c>
+      <c r="H97">
+        <v>24.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K97">
+        <v>3.06</v>
+      </c>
+      <c r="L97">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M97">
+        <v>13.067136</v>
+      </c>
+      <c r="N97">
+        <v>-11.31046933333333</v>
+      </c>
+      <c r="O97">
+        <v>-1.6965704</v>
+      </c>
+      <c r="P97">
+        <v>-9.613898933333331</v>
+      </c>
+      <c r="Q97">
+        <v>-6.553898933333331</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9272532055186589</v>
+      </c>
+      <c r="T97">
+        <v>15.77690366628243</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02016509202934752</v>
+      </c>
+      <c r="W97">
+        <v>0.2339845760233918</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1344339468623169</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2706480074981551</v>
+      </c>
+      <c r="C98">
+        <v>-39.68923645411434</v>
+      </c>
+      <c r="D98">
+        <v>10.87676354588565</v>
+      </c>
+      <c r="E98">
+        <v>21.996</v>
+      </c>
+      <c r="F98">
+        <v>55.29599999999999</v>
+      </c>
+      <c r="G98">
+        <v>4.73</v>
+      </c>
+      <c r="H98">
+        <v>24.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K98">
+        <v>3.06</v>
+      </c>
+      <c r="L98">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M98">
+        <v>13.2046848</v>
+      </c>
+      <c r="N98">
+        <v>-11.44801813333333</v>
+      </c>
+      <c r="O98">
+        <v>-1.71720272</v>
+      </c>
+      <c r="P98">
+        <v>-9.730815413333332</v>
+      </c>
+      <c r="Q98">
+        <v>-6.670815413333331</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.149366506898321</v>
+      </c>
+      <c r="T98">
+        <v>19.72112958285298</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01995503898737515</v>
+      </c>
+      <c r="W98">
+        <v>0.2340347366898148</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1330335932491677</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2726480074981551</v>
+      </c>
+      <c r="C99">
+        <v>-40.35826066810917</v>
+      </c>
+      <c r="D99">
+        <v>10.78373933189082</v>
+      </c>
+      <c r="E99">
+        <v>22.572</v>
+      </c>
+      <c r="F99">
+        <v>55.87199999999999</v>
+      </c>
+      <c r="G99">
+        <v>4.73</v>
+      </c>
+      <c r="H99">
+        <v>24.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K99">
+        <v>3.06</v>
+      </c>
+      <c r="L99">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M99">
+        <v>13.3422336</v>
+      </c>
+      <c r="N99">
+        <v>-11.58556693333333</v>
+      </c>
+      <c r="O99">
+        <v>-1.73783504</v>
+      </c>
+      <c r="P99">
+        <v>-9.84773189333333</v>
+      </c>
+      <c r="Q99">
+        <v>-6.78773189333333</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.519555342531095</v>
+      </c>
+      <c r="T99">
+        <v>26.29483944380398</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01974931693595892</v>
+      </c>
+      <c r="W99">
+        <v>0.234083863115693</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1316621129063928</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2746480074981552</v>
+      </c>
+      <c r="C100">
+        <v>-41.02570718441672</v>
+      </c>
+      <c r="D100">
+        <v>10.69229281558328</v>
+      </c>
+      <c r="E100">
+        <v>23.148</v>
+      </c>
+      <c r="F100">
+        <v>56.44799999999999</v>
+      </c>
+      <c r="G100">
+        <v>4.73</v>
+      </c>
+      <c r="H100">
+        <v>24.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K100">
+        <v>3.06</v>
+      </c>
+      <c r="L100">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M100">
+        <v>13.4797824</v>
+      </c>
+      <c r="N100">
+        <v>-11.72311573333333</v>
+      </c>
+      <c r="O100">
+        <v>-1.75846736</v>
+      </c>
+      <c r="P100">
+        <v>-9.964648373333333</v>
+      </c>
+      <c r="Q100">
+        <v>-6.904648373333332</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.259933013796643</v>
+      </c>
+      <c r="T100">
+        <v>39.44225916570598</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01954779329375525</v>
+      </c>
+      <c r="W100">
+        <v>0.2341319869614513</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1303186219583684</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2766480074981551</v>
+      </c>
+      <c r="C101">
+        <v>-41.69161580234504</v>
+      </c>
+      <c r="D101">
+        <v>10.60238419765495</v>
+      </c>
+      <c r="E101">
+        <v>23.724</v>
+      </c>
+      <c r="F101">
+        <v>57.02399999999999</v>
+      </c>
+      <c r="G101">
+        <v>4.73</v>
+      </c>
+      <c r="H101">
+        <v>24.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>4.816666666666667</v>
+      </c>
+      <c r="K101">
+        <v>3.06</v>
+      </c>
+      <c r="L101">
+        <v>1.756666666666667</v>
+      </c>
+      <c r="M101">
+        <v>13.6173312</v>
+      </c>
+      <c r="N101">
+        <v>-11.86066453333333</v>
+      </c>
+      <c r="O101">
+        <v>-1.77909968</v>
+      </c>
+      <c r="P101">
+        <v>-10.08156485333333</v>
+      </c>
+      <c r="Q101">
+        <v>-7.021564853333331</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.481066027593285</v>
+      </c>
+      <c r="T101">
+        <v>78.88451833141195</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01935034083624258</v>
+      </c>
+      <c r="W101">
+        <v>0.2341791386083053</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1290022722416172</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_environmental_waste_services.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08819682534724557</v>
+        <v>0.08810278010922469</v>
       </c>
       <c r="C2">
-        <v>78.43147848200182</v>
+        <v>77.83079196462324</v>
       </c>
       <c r="D2">
-        <v>71.21147848200182</v>
+        <v>71.36979196462325</v>
       </c>
       <c r="E2">
-        <v>-40.8</v>
+        <v>-40.041</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7590000000000001</v>
       </c>
       <c r="G2">
         <v>7.22</v>
@@ -1573,28 +1573,28 @@
         <v>3.49</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0381777</v>
       </c>
       <c r="N2">
-        <v>3.49</v>
+        <v>3.4518223</v>
       </c>
       <c r="O2">
-        <v>0.5235</v>
+        <v>0.5177733450000001</v>
       </c>
       <c r="P2">
-        <v>2.9665</v>
+        <v>2.934048955</v>
       </c>
       <c r="Q2">
-        <v>6.7265</v>
+        <v>6.694048955</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08819682534724557</v>
+        <v>0.08856083849416635</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410372</v>
+        <v>0.8111573051269449</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>91.41462162466571</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08810278010922469</v>
+        <v>0.08800873487120384</v>
       </c>
       <c r="C3">
-        <v>77.83079196462324</v>
+        <v>77.2308109234547</v>
       </c>
       <c r="D3">
-        <v>71.36979196462325</v>
+        <v>71.5288109234547</v>
       </c>
       <c r="E3">
-        <v>-40.041</v>
+        <v>-39.282</v>
       </c>
       <c r="F3">
-        <v>0.7590000000000001</v>
+        <v>1.518</v>
       </c>
       <c r="G3">
         <v>7.22</v>
@@ -1655,28 +1655,28 @@
         <v>3.49</v>
       </c>
       <c r="M3">
-        <v>0.0381777</v>
+        <v>0.0763554</v>
       </c>
       <c r="N3">
-        <v>3.4518223</v>
+        <v>3.4136446</v>
       </c>
       <c r="O3">
-        <v>0.5177733450000001</v>
+        <v>0.51204669</v>
       </c>
       <c r="P3">
-        <v>2.934048955</v>
+        <v>2.90159791</v>
       </c>
       <c r="Q3">
-        <v>6.694048955</v>
+        <v>6.661597909999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08856083849416635</v>
+        <v>0.08893228048082025</v>
       </c>
       <c r="T3">
-        <v>0.8111573051269449</v>
+        <v>0.8182034223574634</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>91.41462162466571</v>
+        <v>45.70731081233285</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08800873487120384</v>
+        <v>0.08791468963318295</v>
       </c>
       <c r="C4">
-        <v>77.2308109234547</v>
+        <v>76.63154008463903</v>
       </c>
       <c r="D4">
-        <v>71.5288109234547</v>
+        <v>71.68854008463903</v>
       </c>
       <c r="E4">
-        <v>-39.282</v>
+        <v>-38.523</v>
       </c>
       <c r="F4">
-        <v>1.518</v>
+        <v>2.277</v>
       </c>
       <c r="G4">
         <v>7.22</v>
@@ -1737,28 +1737,28 @@
         <v>3.49</v>
       </c>
       <c r="M4">
-        <v>0.0763554</v>
+        <v>0.1145331</v>
       </c>
       <c r="N4">
-        <v>3.4136446</v>
+        <v>3.3754669</v>
       </c>
       <c r="O4">
-        <v>0.51204669</v>
+        <v>0.506320035</v>
       </c>
       <c r="P4">
-        <v>2.90159791</v>
+        <v>2.869146865</v>
       </c>
       <c r="Q4">
-        <v>6.661597909999999</v>
+        <v>6.629146865</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08893228048082025</v>
+        <v>0.08931138106513707</v>
       </c>
       <c r="T4">
-        <v>0.8182034223574634</v>
+        <v>0.8253948203556211</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>45.70731081233285</v>
+        <v>30.47154054155524</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08791468963318295</v>
+        <v>0.08782064439516209</v>
       </c>
       <c r="C5">
-        <v>76.63154008463903</v>
+        <v>76.03298421662869</v>
       </c>
       <c r="D5">
-        <v>71.68854008463903</v>
+        <v>71.84898421662869</v>
       </c>
       <c r="E5">
-        <v>-38.523</v>
+        <v>-37.764</v>
       </c>
       <c r="F5">
-        <v>2.277</v>
+        <v>3.036</v>
       </c>
       <c r="G5">
         <v>7.22</v>
@@ -1819,28 +1819,28 @@
         <v>3.49</v>
       </c>
       <c r="M5">
-        <v>0.1145331</v>
+        <v>0.1527108</v>
       </c>
       <c r="N5">
-        <v>3.3754669</v>
+        <v>3.3372892</v>
       </c>
       <c r="O5">
-        <v>0.506320035</v>
+        <v>0.50059338</v>
       </c>
       <c r="P5">
-        <v>2.869146865</v>
+        <v>2.83669582</v>
       </c>
       <c r="Q5">
-        <v>6.629146865</v>
+        <v>6.59669582</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08931138106513707</v>
+        <v>0.08969837957829385</v>
       </c>
       <c r="T5">
-        <v>0.8253948203556211</v>
+        <v>0.8327360391454072</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>30.47154054155524</v>
+        <v>22.85365540616643</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08782064439516209</v>
+        <v>0.08772659915714122</v>
       </c>
       <c r="C6">
-        <v>76.03298421662869</v>
+        <v>75.43514813066058</v>
       </c>
       <c r="D6">
-        <v>71.84898421662869</v>
+        <v>72.01014813066058</v>
       </c>
       <c r="E6">
-        <v>-37.764</v>
+        <v>-37.005</v>
       </c>
       <c r="F6">
-        <v>3.036</v>
+        <v>3.795</v>
       </c>
       <c r="G6">
         <v>7.22</v>
@@ -1901,28 +1901,28 @@
         <v>3.49</v>
       </c>
       <c r="M6">
-        <v>0.1527108</v>
+        <v>0.1908885</v>
       </c>
       <c r="N6">
-        <v>3.3372892</v>
+        <v>3.2991115</v>
       </c>
       <c r="O6">
-        <v>0.50059338</v>
+        <v>0.4948667250000001</v>
       </c>
       <c r="P6">
-        <v>2.83669582</v>
+        <v>2.804244775</v>
       </c>
       <c r="Q6">
-        <v>6.59669582</v>
+        <v>6.564244775000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08969837957829385</v>
+        <v>0.09009352542856972</v>
       </c>
       <c r="T6">
-        <v>0.8327360391454072</v>
+        <v>0.8402318099097151</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>22.85365540616643</v>
+        <v>18.28292432493314</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08772659915714122</v>
+        <v>0.08763255391912037</v>
       </c>
       <c r="C7">
-        <v>75.43514813066058</v>
+        <v>74.83803668123673</v>
       </c>
       <c r="D7">
-        <v>72.01014813066058</v>
+        <v>72.17203668123673</v>
       </c>
       <c r="E7">
-        <v>-37.005</v>
+        <v>-36.246</v>
       </c>
       <c r="F7">
-        <v>3.795</v>
+        <v>4.554</v>
       </c>
       <c r="G7">
         <v>7.22</v>
@@ -1983,28 +1983,28 @@
         <v>3.49</v>
       </c>
       <c r="M7">
-        <v>0.1908885</v>
+        <v>0.2290662</v>
       </c>
       <c r="N7">
-        <v>3.2991115</v>
+        <v>3.2609338</v>
       </c>
       <c r="O7">
-        <v>0.4948667250000001</v>
+        <v>0.48914007</v>
       </c>
       <c r="P7">
-        <v>2.804244775</v>
+        <v>2.77179373</v>
       </c>
       <c r="Q7">
-        <v>6.564244775000001</v>
+        <v>6.53179373</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09009352542856972</v>
+        <v>0.09049707863736209</v>
       </c>
       <c r="T7">
-        <v>0.8402318099097151</v>
+        <v>0.84788706515837</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.28292432493314</v>
+        <v>15.23577027077762</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08763255391912037</v>
+        <v>0.0875385086810995</v>
       </c>
       <c r="C8">
-        <v>74.83803668123673</v>
+        <v>74.24165476661194</v>
       </c>
       <c r="D8">
-        <v>72.17203668123673</v>
+        <v>72.33465476661195</v>
       </c>
       <c r="E8">
-        <v>-36.246</v>
+        <v>-35.48699999999999</v>
       </c>
       <c r="F8">
-        <v>4.554</v>
+        <v>5.313</v>
       </c>
       <c r="G8">
         <v>7.22</v>
@@ -2065,28 +2065,28 @@
         <v>3.49</v>
       </c>
       <c r="M8">
-        <v>0.2290662</v>
+        <v>0.2672439</v>
       </c>
       <c r="N8">
-        <v>3.2609338</v>
+        <v>3.2227561</v>
       </c>
       <c r="O8">
-        <v>0.48914007</v>
+        <v>0.483413415</v>
       </c>
       <c r="P8">
-        <v>2.77179373</v>
+        <v>2.739342685</v>
       </c>
       <c r="Q8">
-        <v>6.53179373</v>
+        <v>6.499342685</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09049707863736209</v>
+        <v>0.09090931040978439</v>
       </c>
       <c r="T8">
-        <v>0.84788706515837</v>
+        <v>0.8557069495521573</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.23577027077762</v>
+        <v>13.05923166066653</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08753850868109948</v>
+        <v>0.08754646344307861</v>
       </c>
       <c r="C9">
-        <v>74.24165476661197</v>
+        <v>73.46887144428827</v>
       </c>
       <c r="D9">
-        <v>72.33465476661198</v>
+        <v>72.32087144428827</v>
       </c>
       <c r="E9">
-        <v>-35.48699999999999</v>
+        <v>-34.72799999999999</v>
       </c>
       <c r="F9">
-        <v>5.313000000000001</v>
+        <v>6.072000000000001</v>
       </c>
       <c r="G9">
         <v>7.22</v>
@@ -2147,45 +2147,45 @@
         <v>3.49</v>
       </c>
       <c r="M9">
-        <v>0.2672439</v>
+        <v>0.3145296</v>
       </c>
       <c r="N9">
-        <v>3.2227561</v>
+        <v>3.1754704</v>
       </c>
       <c r="O9">
-        <v>0.483413415</v>
+        <v>0.47632056</v>
       </c>
       <c r="P9">
-        <v>2.739342685</v>
+        <v>2.69914984</v>
       </c>
       <c r="Q9">
-        <v>6.499342685</v>
+        <v>6.45914984</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09090931040978439</v>
+        <v>0.09133050374247675</v>
       </c>
       <c r="T9">
-        <v>0.8557069495521573</v>
+        <v>0.863696831432766</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.15</v>
       </c>
       <c r="W9">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.05923166066653</v>
+        <v>11.09593500897849</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08754646344307861</v>
+        <v>0.08746516820505776</v>
       </c>
       <c r="C10">
-        <v>73.46887144428827</v>
+        <v>72.85098073800341</v>
       </c>
       <c r="D10">
-        <v>72.32087144428827</v>
+        <v>72.46198073800342</v>
       </c>
       <c r="E10">
-        <v>-34.72799999999999</v>
+        <v>-33.96899999999999</v>
       </c>
       <c r="F10">
-        <v>6.072000000000001</v>
+        <v>6.831</v>
       </c>
       <c r="G10">
         <v>7.22</v>
@@ -2229,28 +2229,28 @@
         <v>3.49</v>
       </c>
       <c r="M10">
-        <v>0.3145296</v>
+        <v>0.3538458</v>
       </c>
       <c r="N10">
-        <v>3.1754704</v>
+        <v>3.1361542</v>
       </c>
       <c r="O10">
-        <v>0.47632056</v>
+        <v>0.47042313</v>
       </c>
       <c r="P10">
-        <v>2.69914984</v>
+        <v>2.66573107</v>
       </c>
       <c r="Q10">
-        <v>6.45914984</v>
+        <v>6.425731069999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09133050374247675</v>
+        <v>0.09176095407149204</v>
       </c>
       <c r="T10">
-        <v>0.863696831432766</v>
+        <v>0.8718623151129484</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.09593500897849</v>
+        <v>9.863053341314211</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08746516820505776</v>
+        <v>0.08752837296703689</v>
       </c>
       <c r="C11">
-        <v>72.85098073800341</v>
+        <v>71.98222466750674</v>
       </c>
       <c r="D11">
-        <v>72.46198073800342</v>
+        <v>72.35222466750675</v>
       </c>
       <c r="E11">
-        <v>-33.96899999999999</v>
+        <v>-33.20999999999999</v>
       </c>
       <c r="F11">
-        <v>6.831</v>
+        <v>7.59</v>
       </c>
       <c r="G11">
         <v>7.22</v>
@@ -2311,45 +2311,45 @@
         <v>3.49</v>
       </c>
       <c r="M11">
-        <v>0.3538458</v>
+        <v>0.406065</v>
       </c>
       <c r="N11">
-        <v>3.1361542</v>
+        <v>3.083935</v>
       </c>
       <c r="O11">
-        <v>0.47042313</v>
+        <v>0.46259025</v>
       </c>
       <c r="P11">
-        <v>2.66573107</v>
+        <v>2.62134475</v>
       </c>
       <c r="Q11">
-        <v>6.425731069999999</v>
+        <v>6.38134475</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09176095407149204</v>
+        <v>0.09220096996337432</v>
       </c>
       <c r="T11">
-        <v>0.8718623151129484</v>
+        <v>0.8802092539860241</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.15</v>
       </c>
       <c r="W11">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.863053341314211</v>
+        <v>8.594683117234926</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08752837296703689</v>
+        <v>0.08746152772901601</v>
       </c>
       <c r="C12">
-        <v>71.98222466750674</v>
+        <v>71.33931262545916</v>
       </c>
       <c r="D12">
-        <v>72.35222466750675</v>
+        <v>72.46831262545916</v>
       </c>
       <c r="E12">
-        <v>-33.20999999999999</v>
+        <v>-32.45099999999999</v>
       </c>
       <c r="F12">
-        <v>7.590000000000001</v>
+        <v>8.349</v>
       </c>
       <c r="G12">
         <v>7.22</v>
@@ -2393,28 +2393,28 @@
         <v>3.49</v>
       </c>
       <c r="M12">
-        <v>0.406065</v>
+        <v>0.4466715</v>
       </c>
       <c r="N12">
-        <v>3.083935</v>
+        <v>3.0433285</v>
       </c>
       <c r="O12">
-        <v>0.46259025</v>
+        <v>0.456499275</v>
       </c>
       <c r="P12">
-        <v>2.62134475</v>
+        <v>2.586829225</v>
       </c>
       <c r="Q12">
-        <v>6.38134475</v>
+        <v>6.346829225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09220096996337432</v>
+        <v>0.09265087385282698</v>
       </c>
       <c r="T12">
-        <v>0.8802092539860241</v>
+        <v>0.8887437645191686</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.594683117234926</v>
+        <v>7.813348288395387</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08746152772901601</v>
+        <v>0.08747628249099515</v>
       </c>
       <c r="C13">
-        <v>71.33931262545916</v>
+        <v>70.55465648148689</v>
       </c>
       <c r="D13">
-        <v>72.46831262545916</v>
+        <v>72.44265648148689</v>
       </c>
       <c r="E13">
-        <v>-32.45099999999999</v>
+        <v>-31.692</v>
       </c>
       <c r="F13">
-        <v>8.349</v>
+        <v>9.108000000000001</v>
       </c>
       <c r="G13">
         <v>7.22</v>
@@ -2475,45 +2475,45 @@
         <v>3.49</v>
       </c>
       <c r="M13">
-        <v>0.4466715</v>
+        <v>0.4945644</v>
       </c>
       <c r="N13">
-        <v>3.0433285</v>
+        <v>2.9954356</v>
       </c>
       <c r="O13">
-        <v>0.456499275</v>
+        <v>0.4493153400000001</v>
       </c>
       <c r="P13">
-        <v>2.586829225</v>
+        <v>2.54612026</v>
       </c>
       <c r="Q13">
-        <v>6.346829225</v>
+        <v>6.30612026</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09265087385282698</v>
+        <v>0.0931110028306763</v>
       </c>
       <c r="T13">
-        <v>0.8887437645191686</v>
+        <v>0.8974722412007938</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.813348288395387</v>
+        <v>7.05671495966956</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08747628249099515</v>
+        <v>0.08741623725297427</v>
       </c>
       <c r="C14">
-        <v>70.55465648148689</v>
+        <v>69.90017906301806</v>
       </c>
       <c r="D14">
-        <v>72.44265648148689</v>
+        <v>72.54717906301806</v>
       </c>
       <c r="E14">
-        <v>-31.692</v>
+        <v>-30.933</v>
       </c>
       <c r="F14">
-        <v>9.108000000000001</v>
+        <v>9.867000000000001</v>
       </c>
       <c r="G14">
         <v>7.22</v>
@@ -2557,28 +2557,28 @@
         <v>3.49</v>
       </c>
       <c r="M14">
-        <v>0.4945644</v>
+        <v>0.5357781</v>
       </c>
       <c r="N14">
-        <v>2.9954356</v>
+        <v>2.9542219</v>
       </c>
       <c r="O14">
-        <v>0.4493153400000001</v>
+        <v>0.443133285</v>
       </c>
       <c r="P14">
-        <v>2.54612026</v>
+        <v>2.511088615</v>
       </c>
       <c r="Q14">
-        <v>6.30612026</v>
+        <v>6.271088615</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0931110028306763</v>
+        <v>0.09358170948617733</v>
       </c>
       <c r="T14">
-        <v>0.8974722412007938</v>
+        <v>0.9064013725187781</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.05671495966956</v>
+        <v>6.513890732002671</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08741623725297427</v>
+        <v>0.08747519201495341</v>
       </c>
       <c r="C15">
-        <v>69.90017906301806</v>
+        <v>69.03855202119465</v>
       </c>
       <c r="D15">
-        <v>72.54717906301806</v>
+        <v>72.44455202119465</v>
       </c>
       <c r="E15">
-        <v>-30.933</v>
+        <v>-30.174</v>
       </c>
       <c r="F15">
-        <v>9.867000000000001</v>
+        <v>10.626</v>
       </c>
       <c r="G15">
         <v>7.22</v>
@@ -2639,45 +2639,45 @@
         <v>3.49</v>
       </c>
       <c r="M15">
-        <v>0.5357781</v>
+        <v>0.5876178000000001</v>
       </c>
       <c r="N15">
-        <v>2.9542219</v>
+        <v>2.9023822</v>
       </c>
       <c r="O15">
-        <v>0.443133285</v>
+        <v>0.43535733</v>
       </c>
       <c r="P15">
-        <v>2.511088615</v>
+        <v>2.46702487</v>
       </c>
       <c r="Q15">
-        <v>6.271088615</v>
+        <v>6.227024869999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09358170948617733</v>
+        <v>0.09406336280808536</v>
       </c>
       <c r="T15">
-        <v>0.9064013725187781</v>
+        <v>0.9155381580534596</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.15</v>
       </c>
       <c r="W15">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.513890732002671</v>
+        <v>5.939234652183782</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08747519201495341</v>
+        <v>0.08742364677693253</v>
       </c>
       <c r="C16">
-        <v>69.03855202119465</v>
+        <v>68.36926476782784</v>
       </c>
       <c r="D16">
-        <v>72.44455202119465</v>
+        <v>72.53426476782785</v>
       </c>
       <c r="E16">
-        <v>-30.174</v>
+        <v>-29.41499999999999</v>
       </c>
       <c r="F16">
-        <v>10.626</v>
+        <v>11.385</v>
       </c>
       <c r="G16">
         <v>7.22</v>
@@ -2721,28 +2721,28 @@
         <v>3.49</v>
       </c>
       <c r="M16">
-        <v>0.5876178000000001</v>
+        <v>0.6295905000000002</v>
       </c>
       <c r="N16">
-        <v>2.9023822</v>
+        <v>2.8604095</v>
       </c>
       <c r="O16">
-        <v>0.43535733</v>
+        <v>0.4290614250000001</v>
       </c>
       <c r="P16">
-        <v>2.46702487</v>
+        <v>2.431348075</v>
       </c>
       <c r="Q16">
-        <v>6.227024869999999</v>
+        <v>6.191348075000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09406336280808536</v>
+        <v>0.09455634914933239</v>
       </c>
       <c r="T16">
-        <v>0.9155381580534596</v>
+        <v>0.9248899267771926</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.939234652183782</v>
+        <v>5.54328567537153</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08742364677693253</v>
+        <v>0.08737210153891167</v>
       </c>
       <c r="C17">
-        <v>68.36926476782784</v>
+        <v>67.70019998408399</v>
       </c>
       <c r="D17">
-        <v>72.53426476782785</v>
+        <v>72.624199984084</v>
       </c>
       <c r="E17">
-        <v>-29.415</v>
+        <v>-28.656</v>
       </c>
       <c r="F17">
-        <v>11.385</v>
+        <v>12.144</v>
       </c>
       <c r="G17">
         <v>7.22</v>
@@ -2803,28 +2803,28 @@
         <v>3.49</v>
       </c>
       <c r="M17">
-        <v>0.6295905000000001</v>
+        <v>0.6715632000000001</v>
       </c>
       <c r="N17">
-        <v>2.8604095</v>
+        <v>2.8184368</v>
       </c>
       <c r="O17">
-        <v>0.4290614250000001</v>
+        <v>0.42276552</v>
       </c>
       <c r="P17">
-        <v>2.431348075</v>
+        <v>2.39567128</v>
       </c>
       <c r="Q17">
-        <v>6.191348075000001</v>
+        <v>6.15567128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09455634914933239</v>
+        <v>0.09506107326060914</v>
       </c>
       <c r="T17">
-        <v>0.9248899267771926</v>
+        <v>0.9344643566610147</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.543285675371531</v>
+        <v>5.19683032066081</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08737210153891167</v>
+        <v>0.08732055630089081</v>
       </c>
       <c r="C18">
-        <v>67.70019998408399</v>
+        <v>67.03135849851061</v>
       </c>
       <c r="D18">
-        <v>72.624199984084</v>
+        <v>72.71435849851062</v>
       </c>
       <c r="E18">
-        <v>-28.656</v>
+        <v>-27.89699999999999</v>
       </c>
       <c r="F18">
-        <v>12.144</v>
+        <v>12.903</v>
       </c>
       <c r="G18">
         <v>7.22</v>
@@ -2885,28 +2885,28 @@
         <v>3.49</v>
       </c>
       <c r="M18">
-        <v>0.6715632000000001</v>
+        <v>0.7135359000000001</v>
       </c>
       <c r="N18">
-        <v>2.8184368</v>
+        <v>2.7764641</v>
       </c>
       <c r="O18">
-        <v>0.42276552</v>
+        <v>0.416469615</v>
       </c>
       <c r="P18">
-        <v>2.39567128</v>
+        <v>2.359994485</v>
       </c>
       <c r="Q18">
-        <v>6.15567128</v>
+        <v>6.119994484999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09506107326060914</v>
+        <v>0.09557795939866362</v>
       </c>
       <c r="T18">
-        <v>0.9344643566610147</v>
+        <v>0.9442694956986635</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.19683032066081</v>
+        <v>4.891134419445468</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08732055630089081</v>
+        <v>0.08726901106286994</v>
       </c>
       <c r="C19">
-        <v>67.03135849851061</v>
+        <v>66.36274114377453</v>
       </c>
       <c r="D19">
-        <v>72.71435849851062</v>
+        <v>72.80474114377454</v>
       </c>
       <c r="E19">
-        <v>-27.89699999999999</v>
+        <v>-27.13799999999999</v>
       </c>
       <c r="F19">
-        <v>12.903</v>
+        <v>13.662</v>
       </c>
       <c r="G19">
         <v>7.22</v>
@@ -2967,28 +2967,28 @@
         <v>3.49</v>
       </c>
       <c r="M19">
-        <v>0.7135359000000001</v>
+        <v>0.7555086000000002</v>
       </c>
       <c r="N19">
-        <v>2.7764641</v>
+        <v>2.7344914</v>
       </c>
       <c r="O19">
-        <v>0.416469615</v>
+        <v>0.41017371</v>
       </c>
       <c r="P19">
-        <v>2.359994485</v>
+        <v>2.32431769</v>
       </c>
       <c r="Q19">
-        <v>6.119994484999999</v>
+        <v>6.08431769</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09557795939866362</v>
+        <v>0.09610745251569505</v>
       </c>
       <c r="T19">
-        <v>0.9442694956986635</v>
+        <v>0.954313784468938</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.891134419445468</v>
+        <v>4.619404729476275</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08726901106286994</v>
+        <v>0.08762121582484908</v>
       </c>
       <c r="C20">
-        <v>66.36274114377453</v>
+        <v>64.99060314623547</v>
       </c>
       <c r="D20">
-        <v>72.80474114377454</v>
+        <v>72.19160314623548</v>
       </c>
       <c r="E20">
-        <v>-27.138</v>
+        <v>-26.379</v>
       </c>
       <c r="F20">
-        <v>13.662</v>
+        <v>14.421</v>
       </c>
       <c r="G20">
         <v>7.22</v>
@@ -3049,45 +3049,45 @@
         <v>3.49</v>
       </c>
       <c r="M20">
-        <v>0.7555086000000001</v>
+        <v>0.8335338000000001</v>
       </c>
       <c r="N20">
-        <v>2.7344914</v>
+        <v>2.6564662</v>
       </c>
       <c r="O20">
-        <v>0.41017371</v>
+        <v>0.39846993</v>
       </c>
       <c r="P20">
-        <v>2.32431769</v>
+        <v>2.25799627</v>
       </c>
       <c r="Q20">
-        <v>6.08431769</v>
+        <v>6.017996269999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09610745251569505</v>
+        <v>0.09665001953685071</v>
       </c>
       <c r="T20">
-        <v>0.954313784468938</v>
+        <v>0.9646060803693426</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.619404729476276</v>
+        <v>4.186992777017561</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08762121582484908</v>
+        <v>0.08818592058682821</v>
       </c>
       <c r="C21">
-        <v>64.99060314623547</v>
+        <v>63.26979928525586</v>
       </c>
       <c r="D21">
-        <v>72.19160314623548</v>
+        <v>71.22979928525587</v>
       </c>
       <c r="E21">
-        <v>-26.379</v>
+        <v>-25.62</v>
       </c>
       <c r="F21">
-        <v>14.421</v>
+        <v>15.18</v>
       </c>
       <c r="G21">
         <v>7.22</v>
@@ -3131,45 +3131,45 @@
         <v>3.49</v>
       </c>
       <c r="M21">
-        <v>0.8335338000000001</v>
+        <v>0.9305340000000001</v>
       </c>
       <c r="N21">
-        <v>2.6564662</v>
+        <v>2.559466</v>
       </c>
       <c r="O21">
-        <v>0.39846993</v>
+        <v>0.3839199</v>
       </c>
       <c r="P21">
-        <v>2.25799627</v>
+        <v>2.1755461</v>
       </c>
       <c r="Q21">
-        <v>6.017996269999999</v>
+        <v>5.9355461</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09665001953685071</v>
+        <v>0.09720615073353525</v>
       </c>
       <c r="T21">
-        <v>0.9646060803693426</v>
+        <v>0.9751556836672575</v>
       </c>
       <c r="U21">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.186992777017561</v>
+        <v>3.750534639250151</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08818592058682821</v>
+        <v>0.08818537534880733</v>
       </c>
       <c r="C22">
-        <v>63.26979928525586</v>
+        <v>62.51171557287797</v>
       </c>
       <c r="D22">
-        <v>71.22979928525587</v>
+        <v>71.23071557287797</v>
       </c>
       <c r="E22">
-        <v>-25.62</v>
+        <v>-24.861</v>
       </c>
       <c r="F22">
-        <v>15.18</v>
+        <v>15.939</v>
       </c>
       <c r="G22">
         <v>7.22</v>
@@ -3213,28 +3213,28 @@
         <v>3.49</v>
       </c>
       <c r="M22">
-        <v>0.9305340000000001</v>
+        <v>0.9770607000000001</v>
       </c>
       <c r="N22">
-        <v>2.559466</v>
+        <v>2.5129393</v>
       </c>
       <c r="O22">
-        <v>0.3839199</v>
+        <v>0.376940895</v>
       </c>
       <c r="P22">
-        <v>2.1755461</v>
+        <v>2.135998405</v>
       </c>
       <c r="Q22">
-        <v>5.9355461</v>
+        <v>5.895998405</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09720615073353525</v>
+        <v>0.09777636120102194</v>
       </c>
       <c r="T22">
-        <v>0.9751556836672575</v>
+        <v>0.9859723655296766</v>
       </c>
       <c r="U22">
         <v>0.0613</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.750534639250151</v>
+        <v>3.57193775166681</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08818537534880733</v>
+        <v>0.08870843011078647</v>
       </c>
       <c r="C23">
-        <v>62.51171557287797</v>
+        <v>60.88441149175966</v>
       </c>
       <c r="D23">
-        <v>71.23071557287797</v>
+        <v>70.36241149175966</v>
       </c>
       <c r="E23">
-        <v>-24.861</v>
+        <v>-24.102</v>
       </c>
       <c r="F23">
-        <v>15.939</v>
+        <v>16.698</v>
       </c>
       <c r="G23">
         <v>7.22</v>
@@ -3295,45 +3295,45 @@
         <v>3.49</v>
       </c>
       <c r="M23">
-        <v>0.9770607</v>
+        <v>1.0703418</v>
       </c>
       <c r="N23">
-        <v>2.5129393</v>
+        <v>2.4196582</v>
       </c>
       <c r="O23">
-        <v>0.376940895</v>
+        <v>0.36294873</v>
       </c>
       <c r="P23">
-        <v>2.135998405</v>
+        <v>2.05670947</v>
       </c>
       <c r="Q23">
-        <v>5.895998405</v>
+        <v>5.81670947</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09777636120102193</v>
+        <v>0.09836119244972624</v>
       </c>
       <c r="T23">
-        <v>0.9859723655296765</v>
+        <v>0.9970663982090807</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.571937751666811</v>
+        <v>3.26064066637405</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08870843011078647</v>
+        <v>0.0887316848727656</v>
       </c>
       <c r="C24">
-        <v>60.88441149175966</v>
+        <v>60.08729835605654</v>
       </c>
       <c r="D24">
-        <v>70.36241149175966</v>
+        <v>70.32429835605654</v>
       </c>
       <c r="E24">
-        <v>-24.102</v>
+        <v>-23.343</v>
       </c>
       <c r="F24">
-        <v>16.698</v>
+        <v>17.457</v>
       </c>
       <c r="G24">
         <v>7.22</v>
@@ -3377,28 +3377,28 @@
         <v>3.49</v>
       </c>
       <c r="M24">
-        <v>1.0703418</v>
+        <v>1.1189937</v>
       </c>
       <c r="N24">
-        <v>2.4196582</v>
+        <v>2.3710063</v>
       </c>
       <c r="O24">
-        <v>0.36294873</v>
+        <v>0.3556509450000001</v>
       </c>
       <c r="P24">
-        <v>2.05670947</v>
+        <v>2.015355355000001</v>
       </c>
       <c r="Q24">
-        <v>5.81670947</v>
+        <v>5.775355355</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09836119244972624</v>
+        <v>0.0989612141204748</v>
       </c>
       <c r="T24">
-        <v>0.9970663982090807</v>
+        <v>1.008448587581456</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.26064066637405</v>
+        <v>3.118873680879526</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0887316848727656</v>
+        <v>0.09034613963474473</v>
       </c>
       <c r="C25">
-        <v>60.08729835605654</v>
+        <v>56.77958371333535</v>
       </c>
       <c r="D25">
-        <v>70.32429835605654</v>
+        <v>67.77558371333535</v>
       </c>
       <c r="E25">
-        <v>-23.343</v>
+        <v>-22.584</v>
       </c>
       <c r="F25">
-        <v>17.457</v>
+        <v>18.216</v>
       </c>
       <c r="G25">
         <v>7.22</v>
@@ -3459,45 +3459,45 @@
         <v>3.49</v>
       </c>
       <c r="M25">
-        <v>1.1189937</v>
+        <v>1.3097304</v>
       </c>
       <c r="N25">
-        <v>2.3710063</v>
+        <v>2.1802696</v>
       </c>
       <c r="O25">
-        <v>0.3556509450000001</v>
+        <v>0.32704044</v>
       </c>
       <c r="P25">
-        <v>2.015355355000001</v>
+        <v>1.85322916</v>
       </c>
       <c r="Q25">
-        <v>5.775355355</v>
+        <v>5.613229159999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0989612141204748</v>
+        <v>0.09957702583519043</v>
       </c>
       <c r="T25">
-        <v>1.008448587581456</v>
+        <v>1.020130308253105</v>
       </c>
       <c r="U25">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.118873680879526</v>
+        <v>2.664670530667991</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09034613963474473</v>
+        <v>0.09043569439672386</v>
       </c>
       <c r="C26">
-        <v>56.77958371333535</v>
+        <v>55.88460226733169</v>
       </c>
       <c r="D26">
-        <v>67.77558371333535</v>
+        <v>67.6396022673317</v>
       </c>
       <c r="E26">
-        <v>-22.584</v>
+        <v>-21.825</v>
       </c>
       <c r="F26">
-        <v>18.216</v>
+        <v>18.975</v>
       </c>
       <c r="G26">
         <v>7.22</v>
@@ -3541,28 +3541,28 @@
         <v>3.49</v>
       </c>
       <c r="M26">
-        <v>1.3097304</v>
+        <v>1.3643025</v>
       </c>
       <c r="N26">
-        <v>2.1802696</v>
+        <v>2.1256975</v>
       </c>
       <c r="O26">
-        <v>0.32704044</v>
+        <v>0.318854625</v>
       </c>
       <c r="P26">
-        <v>1.85322916</v>
+        <v>1.806842875</v>
       </c>
       <c r="Q26">
-        <v>5.613229159999999</v>
+        <v>5.566842875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09957702583519043</v>
+        <v>0.1002092591956318</v>
       </c>
       <c r="T26">
-        <v>1.020130308253105</v>
+        <v>1.032123541475997</v>
       </c>
       <c r="U26">
         <v>0.07190000000000001</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.664670530667991</v>
+        <v>2.558083709441271</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09043569439672386</v>
+        <v>0.09138714915870298</v>
       </c>
       <c r="C27">
-        <v>55.88460226733169</v>
+        <v>53.71388815791057</v>
       </c>
       <c r="D27">
-        <v>67.6396022673317</v>
+        <v>66.22788815791057</v>
       </c>
       <c r="E27">
-        <v>-21.825</v>
+        <v>-21.066</v>
       </c>
       <c r="F27">
-        <v>18.975</v>
+        <v>19.734</v>
       </c>
       <c r="G27">
         <v>7.22</v>
@@ -3623,45 +3623,45 @@
         <v>3.49</v>
       </c>
       <c r="M27">
-        <v>1.3643025</v>
+        <v>1.4958372</v>
       </c>
       <c r="N27">
-        <v>2.1256975</v>
+        <v>1.9941628</v>
       </c>
       <c r="O27">
-        <v>0.318854625</v>
+        <v>0.29912442</v>
       </c>
       <c r="P27">
-        <v>1.806842875</v>
+        <v>1.69503838</v>
       </c>
       <c r="Q27">
-        <v>5.566842875</v>
+        <v>5.45503838</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1002092591956318</v>
+        <v>0.1008585799441932</v>
       </c>
       <c r="T27">
-        <v>1.032123541475997</v>
+        <v>1.044440916137347</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.558083709441271</v>
+        <v>2.333141601238423</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09138714915870298</v>
+        <v>0.09150985392068213</v>
       </c>
       <c r="C28">
-        <v>53.71388815791057</v>
+        <v>52.77710423265673</v>
       </c>
       <c r="D28">
-        <v>66.22788815791057</v>
+        <v>66.05010423265674</v>
       </c>
       <c r="E28">
-        <v>-21.066</v>
+        <v>-20.307</v>
       </c>
       <c r="F28">
-        <v>19.734</v>
+        <v>20.493</v>
       </c>
       <c r="G28">
         <v>7.22</v>
@@ -3705,28 +3705,28 @@
         <v>3.49</v>
       </c>
       <c r="M28">
-        <v>1.4958372</v>
+        <v>1.5533694</v>
       </c>
       <c r="N28">
-        <v>1.9941628</v>
+        <v>1.9366306</v>
       </c>
       <c r="O28">
-        <v>0.29912442</v>
+        <v>0.29049459</v>
       </c>
       <c r="P28">
-        <v>1.69503838</v>
+        <v>1.64613601</v>
       </c>
       <c r="Q28">
-        <v>5.45503838</v>
+        <v>5.40613601</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1008585799441932</v>
+        <v>0.1015256903023043</v>
       </c>
       <c r="T28">
-        <v>1.044440916137347</v>
+        <v>1.057095753118185</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.333141601238423</v>
+        <v>2.246728949340704</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09150985392068213</v>
+        <v>0.09163255868266125</v>
       </c>
       <c r="C29">
-        <v>52.77710423265673</v>
+        <v>51.84127224789498</v>
       </c>
       <c r="D29">
-        <v>66.05010423265674</v>
+        <v>65.87327224789499</v>
       </c>
       <c r="E29">
-        <v>-20.307</v>
+        <v>-19.54799999999999</v>
       </c>
       <c r="F29">
-        <v>20.493</v>
+        <v>21.252</v>
       </c>
       <c r="G29">
         <v>7.22</v>
@@ -3787,28 +3787,28 @@
         <v>3.49</v>
       </c>
       <c r="M29">
-        <v>1.5533694</v>
+        <v>1.6109016</v>
       </c>
       <c r="N29">
-        <v>1.9366306</v>
+        <v>1.8790984</v>
       </c>
       <c r="O29">
-        <v>0.29049459</v>
+        <v>0.28186476</v>
       </c>
       <c r="P29">
-        <v>1.64613601</v>
+        <v>1.59723364</v>
       </c>
       <c r="Q29">
-        <v>5.40613601</v>
+        <v>5.35723364</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1015256903023043</v>
+        <v>0.1022113315036962</v>
       </c>
       <c r="T29">
-        <v>1.057095753118185</v>
+        <v>1.070102113348491</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.246728949340704</v>
+        <v>2.166488629721393</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09163255868266125</v>
+        <v>0.09175526344464038</v>
       </c>
       <c r="C30">
-        <v>51.84127224789498</v>
+        <v>50.90638457832039</v>
       </c>
       <c r="D30">
-        <v>65.87327224789499</v>
+        <v>65.6973845783204</v>
       </c>
       <c r="E30">
-        <v>-19.54799999999999</v>
+        <v>-18.78899999999999</v>
       </c>
       <c r="F30">
-        <v>21.252</v>
+        <v>22.011</v>
       </c>
       <c r="G30">
         <v>7.22</v>
@@ -3869,28 +3869,28 @@
         <v>3.49</v>
       </c>
       <c r="M30">
-        <v>1.6109016</v>
+        <v>1.6684338</v>
       </c>
       <c r="N30">
-        <v>1.8790984</v>
+        <v>1.8215662</v>
       </c>
       <c r="O30">
-        <v>0.28186476</v>
+        <v>0.27323493</v>
       </c>
       <c r="P30">
-        <v>1.59723364</v>
+        <v>1.54833127</v>
       </c>
       <c r="Q30">
-        <v>5.35723364</v>
+        <v>5.30833127</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1022113315036962</v>
+        <v>0.102916286541747</v>
       </c>
       <c r="T30">
-        <v>1.070102113348491</v>
+        <v>1.083474849923313</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.166488629721393</v>
+        <v>2.091782125248241</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09175526344464038</v>
+        <v>0.09187796820661952</v>
       </c>
       <c r="C31">
-        <v>50.9063845783204</v>
+        <v>49.97243367985226</v>
       </c>
       <c r="D31">
-        <v>65.6973845783204</v>
+        <v>65.52243367985226</v>
       </c>
       <c r="E31">
-        <v>-18.789</v>
+        <v>-18.03</v>
       </c>
       <c r="F31">
-        <v>22.011</v>
+        <v>22.77</v>
       </c>
       <c r="G31">
         <v>7.22</v>
@@ -3951,28 +3951,28 @@
         <v>3.49</v>
       </c>
       <c r="M31">
-        <v>1.6684338</v>
+        <v>1.725966</v>
       </c>
       <c r="N31">
-        <v>1.8215662</v>
+        <v>1.764034</v>
       </c>
       <c r="O31">
-        <v>0.27323493</v>
+        <v>0.2646051</v>
       </c>
       <c r="P31">
-        <v>1.54833127</v>
+        <v>1.4994289</v>
       </c>
       <c r="Q31">
-        <v>5.30833127</v>
+        <v>5.2594289</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.102916286541747</v>
+        <v>0.1036413831523136</v>
       </c>
       <c r="T31">
-        <v>1.083474849923313</v>
+        <v>1.097229664685986</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.091782125248242</v>
+        <v>2.022056054406634</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09187796820661952</v>
+        <v>0.09574237296859864</v>
       </c>
       <c r="C32">
-        <v>49.97243367985226</v>
+        <v>44.14348626489692</v>
       </c>
       <c r="D32">
-        <v>65.52243367985226</v>
+        <v>60.45248626489691</v>
       </c>
       <c r="E32">
-        <v>-18.03</v>
+        <v>-17.271</v>
       </c>
       <c r="F32">
-        <v>22.77</v>
+        <v>23.529</v>
       </c>
       <c r="G32">
         <v>7.22</v>
@@ -4033,45 +4033,45 @@
         <v>3.49</v>
       </c>
       <c r="M32">
-        <v>1.725966</v>
+        <v>2.11761</v>
       </c>
       <c r="N32">
-        <v>1.764034</v>
+        <v>1.37239</v>
       </c>
       <c r="O32">
-        <v>0.2646051</v>
+        <v>0.2058585</v>
       </c>
       <c r="P32">
-        <v>1.4994289</v>
+        <v>1.1665315</v>
       </c>
       <c r="Q32">
-        <v>5.2594289</v>
+        <v>4.9265315</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1036413831523136</v>
+        <v>0.1043874970559401</v>
       </c>
       <c r="T32">
-        <v>1.097229664685986</v>
+        <v>1.111383169731636</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.022056054406634</v>
+        <v>1.648084397032504</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09574237296859864</v>
+        <v>0.09598577773057779</v>
       </c>
       <c r="C33">
-        <v>44.14348626489692</v>
+        <v>43.09128720142221</v>
       </c>
       <c r="D33">
-        <v>60.45248626489691</v>
+        <v>60.15928720142221</v>
       </c>
       <c r="E33">
-        <v>-17.271</v>
+        <v>-16.51199999999999</v>
       </c>
       <c r="F33">
-        <v>23.529</v>
+        <v>24.288</v>
       </c>
       <c r="G33">
         <v>7.22</v>
@@ -4115,28 +4115,28 @@
         <v>3.49</v>
       </c>
       <c r="M33">
-        <v>2.11761</v>
+        <v>2.18592</v>
       </c>
       <c r="N33">
-        <v>1.37239</v>
+        <v>1.30408</v>
       </c>
       <c r="O33">
-        <v>0.2058585</v>
+        <v>0.195612</v>
       </c>
       <c r="P33">
-        <v>1.1665315</v>
+        <v>1.108468</v>
       </c>
       <c r="Q33">
-        <v>4.9265315</v>
+        <v>4.868468</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1043874970559401</v>
+        <v>0.1051555554861438</v>
       </c>
       <c r="T33">
-        <v>1.111383169731636</v>
+        <v>1.125952954337452</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.648084397032504</v>
+        <v>1.596581759625238</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09598577773057779</v>
+        <v>0.09622918249255691</v>
       </c>
       <c r="C34">
-        <v>43.09128720142221</v>
+        <v>42.04191848516835</v>
       </c>
       <c r="D34">
-        <v>60.15928720142221</v>
+        <v>59.86891848516834</v>
       </c>
       <c r="E34">
-        <v>-16.51199999999999</v>
+        <v>-15.75299999999999</v>
       </c>
       <c r="F34">
-        <v>24.288</v>
+        <v>25.047</v>
       </c>
       <c r="G34">
         <v>7.22</v>
@@ -4197,28 +4197,28 @@
         <v>3.49</v>
       </c>
       <c r="M34">
-        <v>2.18592</v>
+        <v>2.25423</v>
       </c>
       <c r="N34">
-        <v>1.30408</v>
+        <v>1.23577</v>
       </c>
       <c r="O34">
-        <v>0.195612</v>
+        <v>0.1853655</v>
       </c>
       <c r="P34">
-        <v>1.108468</v>
+        <v>1.0504045</v>
       </c>
       <c r="Q34">
-        <v>4.868468</v>
+        <v>4.8104045</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1051555554861438</v>
+        <v>0.105946541033667</v>
       </c>
       <c r="T34">
-        <v>1.125952954337452</v>
+        <v>1.140957657886725</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.596581759625238</v>
+        <v>1.548200494182049</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09622918249255691</v>
+        <v>0.09647258725453604</v>
       </c>
       <c r="C35">
-        <v>42.04191848516835</v>
+        <v>40.99533932958602</v>
       </c>
       <c r="D35">
-        <v>59.86891848516834</v>
+        <v>59.58133932958602</v>
       </c>
       <c r="E35">
-        <v>-15.75299999999999</v>
+        <v>-14.99399999999999</v>
       </c>
       <c r="F35">
-        <v>25.047</v>
+        <v>25.806</v>
       </c>
       <c r="G35">
         <v>7.22</v>
@@ -4279,28 +4279,28 @@
         <v>3.49</v>
       </c>
       <c r="M35">
-        <v>2.25423</v>
+        <v>2.32254</v>
       </c>
       <c r="N35">
-        <v>1.23577</v>
+        <v>1.16746</v>
       </c>
       <c r="O35">
-        <v>0.1853655</v>
+        <v>0.1751189999999999</v>
       </c>
       <c r="P35">
-        <v>1.0504045</v>
+        <v>0.9923409999999998</v>
       </c>
       <c r="Q35">
-        <v>4.8104045</v>
+        <v>4.752340999999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.105946541033667</v>
+        <v>0.1067614958402061</v>
       </c>
       <c r="T35">
-        <v>1.140957657886725</v>
+        <v>1.15641704942234</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.548200494182049</v>
+        <v>1.502665185529636</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09647258725453604</v>
+        <v>0.1146576249016138</v>
       </c>
       <c r="C36">
-        <v>40.99533932958602</v>
+        <v>24.50113352892179</v>
       </c>
       <c r="D36">
-        <v>59.58133932958602</v>
+        <v>43.8461335289218</v>
       </c>
       <c r="E36">
-        <v>-14.99399999999999</v>
+        <v>-14.23499999999999</v>
       </c>
       <c r="F36">
-        <v>25.806</v>
+        <v>26.565</v>
       </c>
       <c r="G36">
         <v>7.22</v>
@@ -4361,45 +4361,45 @@
         <v>3.49</v>
       </c>
       <c r="M36">
-        <v>2.32254</v>
+        <v>3.899742000000001</v>
       </c>
       <c r="N36">
-        <v>1.16746</v>
+        <v>-0.4097420000000009</v>
       </c>
       <c r="O36">
-        <v>0.1751189999999999</v>
+        <v>-0.06146130000000014</v>
       </c>
       <c r="P36">
-        <v>0.9923409999999998</v>
+        <v>-0.3482807000000008</v>
       </c>
       <c r="Q36">
-        <v>4.752340999999999</v>
+        <v>3.411719299999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1067614958402061</v>
+        <v>0.1079613201587612</v>
       </c>
       <c r="T36">
-        <v>1.15641704942234</v>
+        <v>1.179177273382815</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.15</v>
+        <v>0.1342396496999032</v>
       </c>
       <c r="W36">
-        <v>0.0765</v>
+        <v>0.1270936194240542</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.502665185529636</v>
+        <v>0.8949309979993546</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1146576249016138</v>
+        <v>0.1156676249016138</v>
       </c>
       <c r="C37">
-        <v>24.50113352892179</v>
+        <v>23.10829782996147</v>
       </c>
       <c r="D37">
-        <v>43.8461335289218</v>
+        <v>43.21229782996148</v>
       </c>
       <c r="E37">
-        <v>-14.23499999999999</v>
+        <v>-13.47599999999999</v>
       </c>
       <c r="F37">
-        <v>26.565</v>
+        <v>27.32400000000001</v>
       </c>
       <c r="G37">
         <v>7.22</v>
@@ -4443,37 +4443,37 @@
         <v>3.49</v>
       </c>
       <c r="M37">
-        <v>3.899742000000001</v>
+        <v>4.011163200000001</v>
       </c>
       <c r="N37">
-        <v>-0.4097420000000009</v>
+        <v>-0.521163200000001</v>
       </c>
       <c r="O37">
-        <v>-0.06146130000000014</v>
+        <v>-0.07817448000000016</v>
       </c>
       <c r="P37">
-        <v>-0.3482807000000008</v>
+        <v>-0.4429887200000009</v>
       </c>
       <c r="Q37">
-        <v>3.411719299999999</v>
+        <v>3.317011279999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1079613201587612</v>
+        <v>0.1089325907862419</v>
       </c>
       <c r="T37">
-        <v>1.179177273382815</v>
+        <v>1.197601918279421</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1342396496999032</v>
+        <v>0.1305107705415725</v>
       </c>
       <c r="W37">
-        <v>0.1270936194240542</v>
+        <v>0.1276410188844972</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8949309979993546</v>
+        <v>0.8700718036104836</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1156676249016138</v>
+        <v>0.1166776249016138</v>
       </c>
       <c r="C38">
-        <v>23.10829782996148</v>
+        <v>21.7335263383399</v>
       </c>
       <c r="D38">
-        <v>43.21229782996148</v>
+        <v>42.5965263383399</v>
       </c>
       <c r="E38">
-        <v>-13.476</v>
+        <v>-12.717</v>
       </c>
       <c r="F38">
-        <v>27.324</v>
+        <v>28.083</v>
       </c>
       <c r="G38">
         <v>7.22</v>
@@ -4525,37 +4525,37 @@
         <v>3.49</v>
       </c>
       <c r="M38">
-        <v>4.0111632</v>
+        <v>4.122584400000001</v>
       </c>
       <c r="N38">
-        <v>-0.5211632000000002</v>
+        <v>-0.6325844000000007</v>
       </c>
       <c r="O38">
-        <v>-0.07817448000000002</v>
+        <v>-0.09488766000000011</v>
       </c>
       <c r="P38">
-        <v>-0.4429887200000001</v>
+        <v>-0.5376967400000006</v>
       </c>
       <c r="Q38">
-        <v>3.31701128</v>
+        <v>3.222303259999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1089325907862419</v>
+        <v>0.1099346954018965</v>
       </c>
       <c r="T38">
-        <v>1.197601918279421</v>
+        <v>1.216611472537825</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1305107705415726</v>
+        <v>0.1269834524188274</v>
       </c>
       <c r="W38">
-        <v>0.1276410188844972</v>
+        <v>0.1281588291849162</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8700718036104839</v>
+        <v>0.8465563494588491</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1166776249016138</v>
+        <v>0.1176876249016138</v>
       </c>
       <c r="C39">
-        <v>21.7335263383399</v>
+        <v>20.37605766364653</v>
       </c>
       <c r="D39">
-        <v>42.5965263383399</v>
+        <v>41.99805766364653</v>
       </c>
       <c r="E39">
-        <v>-12.717</v>
+        <v>-11.95799999999999</v>
       </c>
       <c r="F39">
-        <v>28.083</v>
+        <v>28.842</v>
       </c>
       <c r="G39">
         <v>7.22</v>
@@ -4607,37 +4607,37 @@
         <v>3.49</v>
       </c>
       <c r="M39">
-        <v>4.122584400000001</v>
+        <v>4.234005600000001</v>
       </c>
       <c r="N39">
-        <v>-0.6325844000000007</v>
+        <v>-0.7440056000000004</v>
       </c>
       <c r="O39">
-        <v>-0.09488766000000011</v>
+        <v>-0.11160084</v>
       </c>
       <c r="P39">
-        <v>-0.5376967400000006</v>
+        <v>-0.6324047600000003</v>
       </c>
       <c r="Q39">
-        <v>3.222303259999999</v>
+        <v>3.127595239999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1099346954018965</v>
+        <v>0.1109691259728948</v>
       </c>
       <c r="T39">
-        <v>1.216611472537825</v>
+        <v>1.236234238223918</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1269834524188274</v>
+        <v>0.1236417826183319</v>
       </c>
       <c r="W39">
-        <v>0.1281588291849162</v>
+        <v>0.1286493863116289</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8465563494588491</v>
+        <v>0.8242785507888793</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1176876249016138</v>
+        <v>0.1186976249016138</v>
       </c>
       <c r="C40">
-        <v>20.37605766364653</v>
+        <v>19.03517261186969</v>
       </c>
       <c r="D40">
-        <v>41.99805766364653</v>
+        <v>41.4161726118697</v>
       </c>
       <c r="E40">
-        <v>-11.95799999999999</v>
+        <v>-11.19899999999999</v>
       </c>
       <c r="F40">
-        <v>28.842</v>
+        <v>29.601</v>
       </c>
       <c r="G40">
         <v>7.22</v>
@@ -4689,37 +4689,37 @@
         <v>3.49</v>
       </c>
       <c r="M40">
-        <v>4.234005600000001</v>
+        <v>4.345426800000001</v>
       </c>
       <c r="N40">
-        <v>-0.7440056000000004</v>
+        <v>-0.8554268000000009</v>
       </c>
       <c r="O40">
-        <v>-0.11160084</v>
+        <v>-0.1283140200000001</v>
       </c>
       <c r="P40">
-        <v>-0.6324047600000003</v>
+        <v>-0.7271127800000008</v>
       </c>
       <c r="Q40">
-        <v>3.127595239999999</v>
+        <v>3.032887219999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1109691259728948</v>
+        <v>0.1120374723003193</v>
       </c>
       <c r="T40">
-        <v>1.236234238223918</v>
+        <v>1.25650037327677</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1236417826183319</v>
+        <v>0.1204714804999131</v>
       </c>
       <c r="W40">
-        <v>0.1286493863116289</v>
+        <v>0.1291147866626128</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8242785507888793</v>
+        <v>0.8031432033327541</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1186976249016138</v>
+        <v>0.1418433133038984</v>
       </c>
       <c r="C41">
-        <v>19.03517261186969</v>
+        <v>8.295198475165694</v>
       </c>
       <c r="D41">
-        <v>41.4161726118697</v>
+        <v>31.4351984751657</v>
       </c>
       <c r="E41">
-        <v>-11.19899999999999</v>
+        <v>-10.43999999999999</v>
       </c>
       <c r="F41">
-        <v>29.601</v>
+        <v>30.36</v>
       </c>
       <c r="G41">
         <v>7.22</v>
@@ -4771,45 +4771,45 @@
         <v>3.49</v>
       </c>
       <c r="M41">
-        <v>4.345426800000001</v>
+        <v>6.096288</v>
       </c>
       <c r="N41">
-        <v>-0.8554268000000009</v>
+        <v>-2.606288</v>
       </c>
       <c r="O41">
-        <v>-0.1283140200000001</v>
+        <v>-0.3909432</v>
       </c>
       <c r="P41">
-        <v>-0.7271127800000008</v>
+        <v>-2.2153448</v>
       </c>
       <c r="Q41">
-        <v>3.032887219999999</v>
+        <v>1.5446552</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1120374723003193</v>
+        <v>0.114034244175799</v>
       </c>
       <c r="T41">
-        <v>1.25650037327677</v>
+        <v>1.294378397901761</v>
       </c>
       <c r="U41">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1204714804999131</v>
+        <v>0.08587192731052076</v>
       </c>
       <c r="W41">
-        <v>0.1291147866626128</v>
+        <v>0.1835569169960475</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8031432033327541</v>
+        <v>0.5724795154034718</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1418433133038984</v>
+        <v>0.1433933133038983</v>
       </c>
       <c r="C42">
-        <v>8.295198475165694</v>
+        <v>7.036937245200267</v>
       </c>
       <c r="D42">
-        <v>31.4351984751657</v>
+        <v>30.93593724520027</v>
       </c>
       <c r="E42">
-        <v>-10.43999999999999</v>
+        <v>-9.680999999999994</v>
       </c>
       <c r="F42">
-        <v>30.36</v>
+        <v>31.119</v>
       </c>
       <c r="G42">
         <v>7.22</v>
@@ -4853,37 +4853,37 @@
         <v>3.49</v>
       </c>
       <c r="M42">
-        <v>6.096288</v>
+        <v>6.248695200000001</v>
       </c>
       <c r="N42">
-        <v>-2.606288</v>
+        <v>-2.758695200000001</v>
       </c>
       <c r="O42">
-        <v>-0.3909432</v>
+        <v>-0.4138042800000001</v>
       </c>
       <c r="P42">
-        <v>-2.2153448</v>
+        <v>-2.344890920000001</v>
       </c>
       <c r="Q42">
-        <v>1.5446552</v>
+        <v>1.415109079999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.114034244175799</v>
+        <v>0.1151907567889481</v>
       </c>
       <c r="T42">
-        <v>1.294378397901761</v>
+        <v>1.31631701481535</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.08587192731052076</v>
+        <v>0.08377749005904464</v>
       </c>
       <c r="W42">
-        <v>0.1835569169960475</v>
+        <v>0.1839774799961438</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5724795154034718</v>
+        <v>0.5585166003936309</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1433933133038983</v>
+        <v>0.1449433133038983</v>
       </c>
       <c r="C43">
-        <v>7.036937245200267</v>
+        <v>5.794286849302363</v>
       </c>
       <c r="D43">
-        <v>30.93593724520027</v>
+        <v>30.45228684930236</v>
       </c>
       <c r="E43">
-        <v>-9.680999999999994</v>
+        <v>-8.921999999999993</v>
       </c>
       <c r="F43">
-        <v>31.119</v>
+        <v>31.878</v>
       </c>
       <c r="G43">
         <v>7.22</v>
@@ -4935,37 +4935,37 @@
         <v>3.49</v>
       </c>
       <c r="M43">
-        <v>6.248695200000001</v>
+        <v>6.401102400000001</v>
       </c>
       <c r="N43">
-        <v>-2.758695200000001</v>
+        <v>-2.911102400000001</v>
       </c>
       <c r="O43">
-        <v>-0.4138042800000001</v>
+        <v>-0.4366653600000001</v>
       </c>
       <c r="P43">
-        <v>-2.344890920000001</v>
+        <v>-2.474437040000001</v>
       </c>
       <c r="Q43">
-        <v>1.415109079999999</v>
+        <v>1.285562959999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1151907567889481</v>
+        <v>0.1163871491473782</v>
       </c>
       <c r="T43">
-        <v>1.31631701481535</v>
+        <v>1.339012135760443</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.08377749005904464</v>
+        <v>0.08178278791478166</v>
       </c>
       <c r="W43">
-        <v>0.1839774799961438</v>
+        <v>0.1843780161867118</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5585166003936309</v>
+        <v>0.5452185860985445</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1449433133038984</v>
+        <v>0.1464933133038983</v>
       </c>
       <c r="C44">
-        <v>5.79428684930236</v>
+        <v>4.566526381822634</v>
       </c>
       <c r="D44">
-        <v>30.45228684930236</v>
+        <v>29.98352638182263</v>
       </c>
       <c r="E44">
-        <v>-8.921999999999997</v>
+        <v>-8.162999999999997</v>
       </c>
       <c r="F44">
-        <v>31.878</v>
+        <v>32.637</v>
       </c>
       <c r="G44">
         <v>7.22</v>
@@ -5017,37 +5017,37 @@
         <v>3.49</v>
       </c>
       <c r="M44">
-        <v>6.4011024</v>
+        <v>6.5535096</v>
       </c>
       <c r="N44">
-        <v>-2.9111024</v>
+        <v>-3.0635096</v>
       </c>
       <c r="O44">
-        <v>-0.4366653599999999</v>
+        <v>-0.4595264399999999</v>
       </c>
       <c r="P44">
-        <v>-2.47443704</v>
+        <v>-2.60398316</v>
       </c>
       <c r="Q44">
-        <v>1.28556296</v>
+        <v>1.15601684</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1163871491473782</v>
+        <v>0.1176255201850515</v>
       </c>
       <c r="T44">
-        <v>1.339012135760443</v>
+        <v>1.362503576738696</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.08178278791478168</v>
+        <v>0.07988086261443793</v>
       </c>
       <c r="W44">
-        <v>0.1843780161867118</v>
+        <v>0.1847599227870209</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5452185860985446</v>
+        <v>0.5325390840962528</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1464933133038983</v>
+        <v>0.1480433133038983</v>
       </c>
       <c r="C45">
-        <v>4.566526381822634</v>
+        <v>3.352978652586891</v>
       </c>
       <c r="D45">
-        <v>29.98352638182263</v>
+        <v>29.52897865258689</v>
       </c>
       <c r="E45">
-        <v>-8.162999999999997</v>
+        <v>-7.403999999999996</v>
       </c>
       <c r="F45">
-        <v>32.637</v>
+        <v>33.396</v>
       </c>
       <c r="G45">
         <v>7.22</v>
@@ -5099,37 +5099,37 @@
         <v>3.49</v>
       </c>
       <c r="M45">
-        <v>6.5535096</v>
+        <v>6.705916800000001</v>
       </c>
       <c r="N45">
-        <v>-3.0635096</v>
+        <v>-3.2159168</v>
       </c>
       <c r="O45">
-        <v>-0.4595264399999999</v>
+        <v>-0.4823875200000001</v>
       </c>
       <c r="P45">
-        <v>-2.60398316</v>
+        <v>-2.73352928</v>
       </c>
       <c r="Q45">
-        <v>1.15601684</v>
+        <v>1.026470719999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1176255201850515</v>
+        <v>0.1189081187597846</v>
       </c>
       <c r="T45">
-        <v>1.362503576738696</v>
+        <v>1.386833997751887</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.07988086261443793</v>
+        <v>0.07806538846410978</v>
       </c>
       <c r="W45">
-        <v>0.1847599227870209</v>
+        <v>0.1851244699964067</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5325390840962528</v>
+        <v>0.5204359230940652</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1480433133038983</v>
+        <v>0.1495933133038984</v>
       </c>
       <c r="C46">
-        <v>3.352978652586891</v>
+        <v>2.153006922765535</v>
       </c>
       <c r="D46">
-        <v>29.52897865258689</v>
+        <v>29.08800692276554</v>
       </c>
       <c r="E46">
-        <v>-7.403999999999996</v>
+        <v>-6.644999999999996</v>
       </c>
       <c r="F46">
-        <v>33.396</v>
+        <v>34.155</v>
       </c>
       <c r="G46">
         <v>7.22</v>
@@ -5181,37 +5181,37 @@
         <v>3.49</v>
       </c>
       <c r="M46">
-        <v>6.705916800000001</v>
+        <v>6.858324000000001</v>
       </c>
       <c r="N46">
-        <v>-3.2159168</v>
+        <v>-3.368324</v>
       </c>
       <c r="O46">
-        <v>-0.4823875200000001</v>
+        <v>-0.5052486</v>
       </c>
       <c r="P46">
-        <v>-2.73352928</v>
+        <v>-2.8630754</v>
       </c>
       <c r="Q46">
-        <v>1.026470719999999</v>
+        <v>0.8969245999999993</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1189081187597846</v>
+        <v>0.1202373572826897</v>
       </c>
       <c r="T46">
-        <v>1.386833997751887</v>
+        <v>1.412049161347376</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.07806538846410978</v>
+        <v>0.07633060205379623</v>
       </c>
       <c r="W46">
-        <v>0.1851244699964067</v>
+        <v>0.1854728151075977</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5204359230940652</v>
+        <v>0.5088706803586416</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1495933133038984</v>
+        <v>0.1674594700446185</v>
       </c>
       <c r="C47">
-        <v>2.153006922765535</v>
+        <v>-2.877677729211712</v>
       </c>
       <c r="D47">
-        <v>29.08800692276554</v>
+        <v>24.81632227078829</v>
       </c>
       <c r="E47">
-        <v>-6.644999999999996</v>
+        <v>-5.885999999999996</v>
       </c>
       <c r="F47">
-        <v>34.155</v>
+        <v>34.914</v>
       </c>
       <c r="G47">
         <v>7.22</v>
@@ -5263,45 +5263,45 @@
         <v>3.49</v>
       </c>
       <c r="M47">
-        <v>6.858324000000001</v>
+        <v>8.2327212</v>
       </c>
       <c r="N47">
-        <v>-3.368324</v>
+        <v>-4.7427212</v>
       </c>
       <c r="O47">
-        <v>-0.5052486</v>
+        <v>-0.7114081799999999</v>
       </c>
       <c r="P47">
-        <v>-2.8630754</v>
+        <v>-4.03131302</v>
       </c>
       <c r="Q47">
-        <v>0.8969245999999993</v>
+        <v>-0.27131302</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1202373572826897</v>
+        <v>0.1220161171225917</v>
       </c>
       <c r="T47">
-        <v>1.412049161347376</v>
+        <v>1.445791578217891</v>
       </c>
       <c r="U47">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07633060205379623</v>
+        <v>0.06358772358281731</v>
       </c>
       <c r="W47">
-        <v>0.1854728151075977</v>
+        <v>0.2208060147791717</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.5088706803586416</v>
+        <v>0.423918157218782</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1674594700446185</v>
+        <v>0.1693594700446185</v>
       </c>
       <c r="C48">
-        <v>-2.877677729211712</v>
+        <v>-4.018283544593341</v>
       </c>
       <c r="D48">
-        <v>24.81632227078829</v>
+        <v>24.43471645540666</v>
       </c>
       <c r="E48">
-        <v>-5.885999999999996</v>
+        <v>-5.126999999999995</v>
       </c>
       <c r="F48">
-        <v>34.914</v>
+        <v>35.673</v>
       </c>
       <c r="G48">
         <v>7.22</v>
@@ -5345,37 +5345,37 @@
         <v>3.49</v>
       </c>
       <c r="M48">
-        <v>8.2327212</v>
+        <v>8.411693400000001</v>
       </c>
       <c r="N48">
-        <v>-4.7427212</v>
+        <v>-4.921693400000001</v>
       </c>
       <c r="O48">
-        <v>-0.7114081799999999</v>
+        <v>-0.73825401</v>
       </c>
       <c r="P48">
-        <v>-4.03131302</v>
+        <v>-4.18343939</v>
       </c>
       <c r="Q48">
-        <v>-0.27131302</v>
+        <v>-0.4234393900000004</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1220161171225917</v>
+        <v>0.123454157068301</v>
       </c>
       <c r="T48">
-        <v>1.445791578217891</v>
+        <v>1.473070664599361</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06358772358281731</v>
+        <v>0.06223479329382119</v>
       </c>
       <c r="W48">
-        <v>0.2208060147791717</v>
+        <v>0.221125035741317</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.423918157218782</v>
+        <v>0.414898621958808</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1693594700446185</v>
+        <v>0.1712594700446186</v>
       </c>
       <c r="C49">
-        <v>-4.018283544593341</v>
+        <v>-5.147331028842725</v>
       </c>
       <c r="D49">
-        <v>24.43471645540666</v>
+        <v>24.06466897115728</v>
       </c>
       <c r="E49">
-        <v>-5.126999999999995</v>
+        <v>-4.367999999999995</v>
       </c>
       <c r="F49">
-        <v>35.673</v>
+        <v>36.432</v>
       </c>
       <c r="G49">
         <v>7.22</v>
@@ -5427,37 +5427,37 @@
         <v>3.49</v>
       </c>
       <c r="M49">
-        <v>8.411693400000001</v>
+        <v>8.590665600000001</v>
       </c>
       <c r="N49">
-        <v>-4.921693400000001</v>
+        <v>-5.100665600000001</v>
       </c>
       <c r="O49">
-        <v>-0.73825401</v>
+        <v>-0.7650998400000001</v>
       </c>
       <c r="P49">
-        <v>-4.18343939</v>
+        <v>-4.335565760000001</v>
       </c>
       <c r="Q49">
-        <v>-0.4234393900000004</v>
+        <v>-0.5755657600000008</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.123454157068301</v>
+        <v>0.1249475062426914</v>
       </c>
       <c r="T49">
-        <v>1.473070664599361</v>
+        <v>1.501398946610887</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06223479329382119</v>
+        <v>0.06093823510019991</v>
       </c>
       <c r="W49">
-        <v>0.221125035741317</v>
+        <v>0.2214307641633729</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.414898621958808</v>
+        <v>0.4062549006679994</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1712594700446185</v>
+        <v>0.1731594700446185</v>
       </c>
       <c r="C50">
-        <v>-5.147331028842718</v>
+        <v>-6.265337477512624</v>
       </c>
       <c r="D50">
-        <v>24.06466897115729</v>
+        <v>23.70566252248738</v>
       </c>
       <c r="E50">
-        <v>-4.367999999999995</v>
+        <v>-3.608999999999995</v>
       </c>
       <c r="F50">
-        <v>36.432</v>
+        <v>37.191</v>
       </c>
       <c r="G50">
         <v>7.22</v>
@@ -5509,37 +5509,37 @@
         <v>3.49</v>
       </c>
       <c r="M50">
-        <v>8.590665600000001</v>
+        <v>8.769637800000002</v>
       </c>
       <c r="N50">
-        <v>-5.100665600000001</v>
+        <v>-5.279637800000001</v>
       </c>
       <c r="O50">
-        <v>-0.7650998400000001</v>
+        <v>-0.7919456700000002</v>
       </c>
       <c r="P50">
-        <v>-4.335565760000001</v>
+        <v>-4.487692130000001</v>
       </c>
       <c r="Q50">
-        <v>-0.5755657600000008</v>
+        <v>-0.7276921300000012</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1249475062426914</v>
+        <v>0.126499418129803</v>
       </c>
       <c r="T50">
-        <v>1.501398946610887</v>
+        <v>1.530838141642473</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06093823510019991</v>
+        <v>0.05969459764917542</v>
       </c>
       <c r="W50">
-        <v>0.2214307641633729</v>
+        <v>0.2217240138743244</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4062549006679994</v>
+        <v>0.3979639843278362</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1731594700446185</v>
+        <v>0.1750594700446185</v>
       </c>
       <c r="C51">
-        <v>-6.265337477512624</v>
+        <v>-7.372789771005539</v>
       </c>
       <c r="D51">
-        <v>23.70566252248738</v>
+        <v>23.35721022899446</v>
       </c>
       <c r="E51">
-        <v>-3.608999999999995</v>
+        <v>-2.849999999999994</v>
       </c>
       <c r="F51">
-        <v>37.191</v>
+        <v>37.95</v>
       </c>
       <c r="G51">
         <v>7.22</v>
@@ -5591,37 +5591,37 @@
         <v>3.49</v>
       </c>
       <c r="M51">
-        <v>8.769637800000002</v>
+        <v>8.94861</v>
       </c>
       <c r="N51">
-        <v>-5.279637800000001</v>
+        <v>-5.45861</v>
       </c>
       <c r="O51">
-        <v>-0.7919456700000002</v>
+        <v>-0.8187915</v>
       </c>
       <c r="P51">
-        <v>-4.487692130000001</v>
+        <v>-4.639818500000001</v>
       </c>
       <c r="Q51">
-        <v>-0.7276921300000012</v>
+        <v>-0.8798185000000007</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.126499418129803</v>
+        <v>0.1281134064923991</v>
       </c>
       <c r="T51">
-        <v>1.530838141642473</v>
+        <v>1.561454904475322</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05969459764917542</v>
+        <v>0.05850070569619192</v>
       </c>
       <c r="W51">
-        <v>0.2217240138743244</v>
+        <v>0.2220055335968379</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3979639843278362</v>
+        <v>0.3900047046412795</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1750594700446185</v>
+        <v>0.1769594700446185</v>
       </c>
       <c r="C52">
-        <v>-7.372789771005539</v>
+        <v>-8.470146577570809</v>
       </c>
       <c r="D52">
-        <v>23.35721022899446</v>
+        <v>23.0188534224292</v>
       </c>
       <c r="E52">
-        <v>-2.849999999999994</v>
+        <v>-2.090999999999994</v>
       </c>
       <c r="F52">
-        <v>37.95</v>
+        <v>38.709</v>
       </c>
       <c r="G52">
         <v>7.22</v>
@@ -5673,37 +5673,37 @@
         <v>3.49</v>
       </c>
       <c r="M52">
-        <v>8.94861</v>
+        <v>9.127582200000001</v>
       </c>
       <c r="N52">
-        <v>-5.45861</v>
+        <v>-5.637582200000001</v>
       </c>
       <c r="O52">
-        <v>-0.8187915</v>
+        <v>-0.8456373300000001</v>
       </c>
       <c r="P52">
-        <v>-4.639818500000001</v>
+        <v>-4.791944870000001</v>
       </c>
       <c r="Q52">
-        <v>-0.8798185000000007</v>
+        <v>-1.031944870000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1281134064923991</v>
+        <v>0.1297932719310195</v>
       </c>
       <c r="T52">
-        <v>1.561454904475322</v>
+        <v>1.593321331097268</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05850070569619192</v>
+        <v>0.05735363303548227</v>
       </c>
       <c r="W52">
-        <v>0.2220055335968379</v>
+        <v>0.2222760133302333</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3900047046412795</v>
+        <v>0.3823575535698819</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1769594700446185</v>
+        <v>0.1788594700446185</v>
       </c>
       <c r="C53">
-        <v>-8.470146577570809</v>
+        <v>-9.557840367557716</v>
       </c>
       <c r="D53">
-        <v>23.0188534224292</v>
+        <v>22.69015963244229</v>
       </c>
       <c r="E53">
-        <v>-2.090999999999994</v>
+        <v>-1.331999999999994</v>
       </c>
       <c r="F53">
-        <v>38.709</v>
+        <v>39.468</v>
       </c>
       <c r="G53">
         <v>7.22</v>
@@ -5755,37 +5755,37 @@
         <v>3.49</v>
       </c>
       <c r="M53">
-        <v>9.127582200000001</v>
+        <v>9.306554400000001</v>
       </c>
       <c r="N53">
-        <v>-5.637582200000001</v>
+        <v>-5.816554400000001</v>
       </c>
       <c r="O53">
-        <v>-0.8456373300000001</v>
+        <v>-0.8724831600000001</v>
       </c>
       <c r="P53">
-        <v>-4.791944870000001</v>
+        <v>-4.944071240000001</v>
       </c>
       <c r="Q53">
-        <v>-1.031944870000001</v>
+        <v>-1.184071240000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1297932719310195</v>
+        <v>0.1315431317629157</v>
       </c>
       <c r="T53">
-        <v>1.593321331097268</v>
+        <v>1.626515525495127</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05735363303548227</v>
+        <v>0.05625067855403069</v>
       </c>
       <c r="W53">
-        <v>0.2222760133302333</v>
+        <v>0.2225360899969596</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3823575535698819</v>
+        <v>0.375004523693538</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1788594700446185</v>
+        <v>0.1807594700446185</v>
       </c>
       <c r="C54">
-        <v>-9.557840367557716</v>
+        <v>-10.6362792575251</v>
       </c>
       <c r="D54">
-        <v>22.69015963244229</v>
+        <v>22.3707207424749</v>
       </c>
       <c r="E54">
-        <v>-1.331999999999994</v>
+        <v>-0.5729999999999933</v>
       </c>
       <c r="F54">
-        <v>39.468</v>
+        <v>40.227</v>
       </c>
       <c r="G54">
         <v>7.22</v>
@@ -5837,37 +5837,37 @@
         <v>3.49</v>
       </c>
       <c r="M54">
-        <v>9.306554400000001</v>
+        <v>9.485526600000002</v>
       </c>
       <c r="N54">
-        <v>-5.816554400000001</v>
+        <v>-5.995526600000002</v>
       </c>
       <c r="O54">
-        <v>-0.8724831600000001</v>
+        <v>-0.8993289900000002</v>
       </c>
       <c r="P54">
-        <v>-4.944071240000001</v>
+        <v>-5.096197610000002</v>
       </c>
       <c r="Q54">
-        <v>-1.184071240000002</v>
+        <v>-1.336197610000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1315431317629157</v>
+        <v>0.1333674537153182</v>
       </c>
       <c r="T54">
-        <v>1.626515525495127</v>
+        <v>1.661122238803534</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05625067855403069</v>
+        <v>0.05518934499640746</v>
       </c>
       <c r="W54">
-        <v>0.2225360899969596</v>
+        <v>0.2227863524498471</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.375004523693538</v>
+        <v>0.3679289666427165</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1807594700446185</v>
+        <v>0.1826594700446185</v>
       </c>
       <c r="C55">
-        <v>-10.6362792575251</v>
+        <v>-11.7058487007419</v>
       </c>
       <c r="D55">
-        <v>22.3707207424749</v>
+        <v>22.06015129925811</v>
       </c>
       <c r="E55">
-        <v>-0.5729999999999933</v>
+        <v>0.186000000000007</v>
       </c>
       <c r="F55">
-        <v>40.227</v>
+        <v>40.986</v>
       </c>
       <c r="G55">
         <v>7.22</v>
@@ -5919,37 +5919,37 @@
         <v>3.49</v>
       </c>
       <c r="M55">
-        <v>9.485526600000002</v>
+        <v>9.664498800000001</v>
       </c>
       <c r="N55">
-        <v>-5.995526600000002</v>
+        <v>-6.1744988</v>
       </c>
       <c r="O55">
-        <v>-0.8993289900000002</v>
+        <v>-0.92617482</v>
       </c>
       <c r="P55">
-        <v>-5.096197610000002</v>
+        <v>-5.24832398</v>
       </c>
       <c r="Q55">
-        <v>-1.336197610000002</v>
+        <v>-1.488323980000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1333674537153182</v>
+        <v>0.1352710940134773</v>
       </c>
       <c r="T55">
-        <v>1.661122238803534</v>
+        <v>1.697233591821003</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05518934499640746</v>
+        <v>0.05416732008906659</v>
       </c>
       <c r="W55">
-        <v>0.2227863524498471</v>
+        <v>0.2230273459229981</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3679289666427165</v>
+        <v>0.361115467260444</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1826594700446185</v>
+        <v>0.1845594700446185</v>
       </c>
       <c r="C56">
-        <v>-11.7058487007419</v>
+        <v>-12.76691303880194</v>
       </c>
       <c r="D56">
-        <v>22.06015129925811</v>
+        <v>21.75808696119806</v>
       </c>
       <c r="E56">
-        <v>0.186000000000007</v>
+        <v>0.9450000000000074</v>
       </c>
       <c r="F56">
-        <v>40.986</v>
+        <v>41.745</v>
       </c>
       <c r="G56">
         <v>7.22</v>
@@ -6001,37 +6001,37 @@
         <v>3.49</v>
       </c>
       <c r="M56">
-        <v>9.664498800000001</v>
+        <v>9.843471000000001</v>
       </c>
       <c r="N56">
-        <v>-6.1744988</v>
+        <v>-6.353471000000001</v>
       </c>
       <c r="O56">
-        <v>-0.92617482</v>
+        <v>-0.95302065</v>
       </c>
       <c r="P56">
-        <v>-5.24832398</v>
+        <v>-5.400450350000001</v>
       </c>
       <c r="Q56">
-        <v>-1.488323980000001</v>
+        <v>-1.640450350000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1352710940134773</v>
+        <v>0.1372593405471101</v>
       </c>
       <c r="T56">
-        <v>1.697233591821003</v>
+        <v>1.734949893861469</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05416732008906659</v>
+        <v>0.05318245972381084</v>
       </c>
       <c r="W56">
-        <v>0.2230273459229981</v>
+        <v>0.2232595759971254</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.361115467260444</v>
+        <v>0.3545497314920723</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1845594700446185</v>
+        <v>0.1864594700446185</v>
       </c>
       <c r="C57">
-        <v>-12.76691303880194</v>
+        <v>-13.81981692748546</v>
       </c>
       <c r="D57">
-        <v>21.75808696119806</v>
+        <v>21.46418307251455</v>
       </c>
       <c r="E57">
-        <v>0.9450000000000074</v>
+        <v>1.704000000000008</v>
       </c>
       <c r="F57">
-        <v>41.745</v>
+        <v>42.504</v>
       </c>
       <c r="G57">
         <v>7.22</v>
@@ -6083,37 +6083,37 @@
         <v>3.49</v>
       </c>
       <c r="M57">
-        <v>9.843471000000001</v>
+        <v>10.0224432</v>
       </c>
       <c r="N57">
-        <v>-6.353471000000001</v>
+        <v>-6.532443200000001</v>
       </c>
       <c r="O57">
-        <v>-0.95302065</v>
+        <v>-0.9798664800000001</v>
       </c>
       <c r="P57">
-        <v>-5.400450350000001</v>
+        <v>-5.552576720000001</v>
       </c>
       <c r="Q57">
-        <v>-1.640450350000001</v>
+        <v>-1.792576720000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1372593405471101</v>
+        <v>0.1393379619231808</v>
       </c>
       <c r="T57">
-        <v>1.734949893861469</v>
+        <v>1.774380573267411</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05318245972381084</v>
+        <v>0.05223277294302849</v>
       </c>
       <c r="W57">
-        <v>0.2232595759971254</v>
+        <v>0.2234835121400339</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3545497314920723</v>
+        <v>0.3482184862868567</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1864594700446185</v>
+        <v>0.1883594700446185</v>
       </c>
       <c r="C58">
-        <v>-13.81981692748546</v>
+        <v>-14.86488664859914</v>
       </c>
       <c r="D58">
-        <v>21.46418307251455</v>
+        <v>21.17811335140086</v>
       </c>
       <c r="E58">
-        <v>1.704000000000008</v>
+        <v>2.463000000000008</v>
       </c>
       <c r="F58">
-        <v>42.504</v>
+        <v>43.26300000000001</v>
       </c>
       <c r="G58">
         <v>7.22</v>
@@ -6165,37 +6165,37 @@
         <v>3.49</v>
       </c>
       <c r="M58">
-        <v>10.0224432</v>
+        <v>10.2014154</v>
       </c>
       <c r="N58">
-        <v>-6.532443200000001</v>
+        <v>-6.711415400000002</v>
       </c>
       <c r="O58">
-        <v>-0.9798664800000001</v>
+        <v>-1.00671231</v>
       </c>
       <c r="P58">
-        <v>-5.552576720000001</v>
+        <v>-5.704703090000002</v>
       </c>
       <c r="Q58">
-        <v>-1.792576720000001</v>
+        <v>-1.944703090000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1393379619231808</v>
+        <v>0.1415132633632548</v>
       </c>
       <c r="T58">
-        <v>1.774380573267411</v>
+        <v>1.815645237762003</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05223277294302849</v>
+        <v>0.0513164085054315</v>
       </c>
       <c r="W58">
-        <v>0.2234835121400339</v>
+        <v>0.2236995908744193</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3482184862868567</v>
+        <v>0.34210939003621</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1883594700446185</v>
+        <v>0.1902594700446185</v>
       </c>
       <c r="C59">
-        <v>-14.86488664859914</v>
+        <v>-15.90243131829254</v>
       </c>
       <c r="D59">
-        <v>21.17811335140086</v>
+        <v>20.89956868170747</v>
       </c>
       <c r="E59">
-        <v>2.463000000000008</v>
+        <v>3.222000000000008</v>
       </c>
       <c r="F59">
-        <v>43.26300000000001</v>
+        <v>44.02200000000001</v>
       </c>
       <c r="G59">
         <v>7.22</v>
@@ -6247,37 +6247,37 @@
         <v>3.49</v>
       </c>
       <c r="M59">
-        <v>10.2014154</v>
+        <v>10.3803876</v>
       </c>
       <c r="N59">
-        <v>-6.711415400000002</v>
+        <v>-6.890387600000002</v>
       </c>
       <c r="O59">
-        <v>-1.00671231</v>
+        <v>-1.03355814</v>
       </c>
       <c r="P59">
-        <v>-5.704703090000002</v>
+        <v>-5.856829460000002</v>
       </c>
       <c r="Q59">
-        <v>-1.944703090000002</v>
+        <v>-2.096829460000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1415132633632548</v>
+        <v>0.1437921505861894</v>
       </c>
       <c r="T59">
-        <v>1.815645237762003</v>
+        <v>1.858874886280146</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0513164085054315</v>
+        <v>0.05043164284154475</v>
       </c>
       <c r="W59">
-        <v>0.2236995908744193</v>
+        <v>0.2239082186179638</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.34210939003621</v>
+        <v>0.3362109522769651</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1902594700446185</v>
+        <v>0.1921594700446185</v>
       </c>
       <c r="C60">
-        <v>-15.90243131829253</v>
+        <v>-16.93274400125824</v>
       </c>
       <c r="D60">
-        <v>20.89956868170747</v>
+        <v>20.62825599874176</v>
       </c>
       <c r="E60">
-        <v>3.222000000000001</v>
+        <v>3.981000000000002</v>
       </c>
       <c r="F60">
-        <v>44.022</v>
+        <v>44.781</v>
       </c>
       <c r="G60">
         <v>7.22</v>
@@ -6329,37 +6329,37 @@
         <v>3.49</v>
       </c>
       <c r="M60">
-        <v>10.3803876</v>
+        <v>10.5593598</v>
       </c>
       <c r="N60">
-        <v>-6.8903876</v>
+        <v>-7.069359799999999</v>
       </c>
       <c r="O60">
-        <v>-1.03355814</v>
+        <v>-1.06040397</v>
       </c>
       <c r="P60">
-        <v>-5.85682946</v>
+        <v>-6.00895583</v>
       </c>
       <c r="Q60">
-        <v>-2.09682946</v>
+        <v>-2.24895583</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1437921505861894</v>
+        <v>0.1461822030395111</v>
       </c>
       <c r="T60">
-        <v>1.858874886280145</v>
+        <v>1.904213298140637</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05043164284154476</v>
+        <v>0.04957686923406095</v>
       </c>
       <c r="W60">
-        <v>0.2239082186179638</v>
+        <v>0.2241097742346085</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3362109522769651</v>
+        <v>0.3305124615604064</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1921594700446185</v>
+        <v>0.1940594700446185</v>
       </c>
       <c r="C61">
-        <v>-16.93274400125824</v>
+        <v>-17.95610273925867</v>
       </c>
       <c r="D61">
-        <v>20.62825599874176</v>
+        <v>20.36389726074133</v>
       </c>
       <c r="E61">
-        <v>3.981000000000002</v>
+        <v>4.740000000000002</v>
       </c>
       <c r="F61">
-        <v>44.781</v>
+        <v>45.54</v>
       </c>
       <c r="G61">
         <v>7.22</v>
@@ -6411,37 +6411,37 @@
         <v>3.49</v>
       </c>
       <c r="M61">
-        <v>10.5593598</v>
+        <v>10.738332</v>
       </c>
       <c r="N61">
-        <v>-7.069359799999999</v>
+        <v>-7.248332</v>
       </c>
       <c r="O61">
-        <v>-1.06040397</v>
+        <v>-1.0872498</v>
       </c>
       <c r="P61">
-        <v>-6.00895583</v>
+        <v>-6.161082199999999</v>
       </c>
       <c r="Q61">
-        <v>-2.24895583</v>
+        <v>-2.401082199999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1461822030395111</v>
+        <v>0.1486917581154988</v>
       </c>
       <c r="T61">
-        <v>1.904213298140637</v>
+        <v>1.951818630594153</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04957686923406095</v>
+        <v>0.04875058808015994</v>
       </c>
       <c r="W61">
-        <v>0.2241097742346085</v>
+        <v>0.2243046113306983</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3305124615604064</v>
+        <v>0.3250039205343996</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1940594700446185</v>
+        <v>0.1959594700446185</v>
       </c>
       <c r="C62">
-        <v>-17.95610273925867</v>
+        <v>-18.97277150156792</v>
       </c>
       <c r="D62">
-        <v>20.36389726074133</v>
+        <v>20.10622849843208</v>
       </c>
       <c r="E62">
-        <v>4.740000000000002</v>
+        <v>5.499000000000002</v>
       </c>
       <c r="F62">
-        <v>45.54</v>
+        <v>46.299</v>
       </c>
       <c r="G62">
         <v>7.22</v>
@@ -6493,37 +6493,37 @@
         <v>3.49</v>
       </c>
       <c r="M62">
-        <v>10.738332</v>
+        <v>10.9173042</v>
       </c>
       <c r="N62">
-        <v>-7.248332</v>
+        <v>-7.4273042</v>
       </c>
       <c r="O62">
-        <v>-1.0872498</v>
+        <v>-1.11409563</v>
       </c>
       <c r="P62">
-        <v>-6.161082199999999</v>
+        <v>-6.31320857</v>
       </c>
       <c r="Q62">
-        <v>-2.401082199999999</v>
+        <v>-2.553208570000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1486917581154988</v>
+        <v>0.1513300083235886</v>
       </c>
       <c r="T62">
-        <v>1.951818630594153</v>
+        <v>2.001865262147849</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04875058808015994</v>
+        <v>0.04795139811163272</v>
       </c>
       <c r="W62">
-        <v>0.2243046113306983</v>
+        <v>0.224493060325277</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3250039205343996</v>
+        <v>0.3196759874108849</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1959594700446185</v>
+        <v>0.1978594700446185</v>
       </c>
       <c r="C63">
-        <v>-18.97277150156792</v>
+        <v>-19.98300106415821</v>
       </c>
       <c r="D63">
-        <v>20.10622849843208</v>
+        <v>19.85499893584179</v>
       </c>
       <c r="E63">
-        <v>5.499000000000002</v>
+        <v>6.258000000000003</v>
       </c>
       <c r="F63">
-        <v>46.299</v>
+        <v>47.058</v>
       </c>
       <c r="G63">
         <v>7.22</v>
@@ -6575,37 +6575,37 @@
         <v>3.49</v>
       </c>
       <c r="M63">
-        <v>10.9173042</v>
+        <v>11.0962764</v>
       </c>
       <c r="N63">
-        <v>-7.4273042</v>
+        <v>-7.6062764</v>
       </c>
       <c r="O63">
-        <v>-1.11409563</v>
+        <v>-1.14094146</v>
       </c>
       <c r="P63">
-        <v>-6.31320857</v>
+        <v>-6.46533494</v>
       </c>
       <c r="Q63">
-        <v>-2.553208570000001</v>
+        <v>-2.70533494</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1513300083235886</v>
+        <v>0.1541071138057883</v>
       </c>
       <c r="T63">
-        <v>2.001865262147849</v>
+        <v>2.054545926941214</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04795139811163272</v>
+        <v>0.0471779884646709</v>
       </c>
       <c r="W63">
-        <v>0.224493060325277</v>
+        <v>0.2246754303200306</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3196759874108849</v>
+        <v>0.3145199230978061</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1978594700446185</v>
+        <v>0.1997594700446185</v>
       </c>
       <c r="C64">
-        <v>-19.98300106415821</v>
+        <v>-20.98702982378676</v>
       </c>
       <c r="D64">
-        <v>19.85499893584179</v>
+        <v>19.60997017621325</v>
       </c>
       <c r="E64">
-        <v>6.258000000000003</v>
+        <v>7.01700000000001</v>
       </c>
       <c r="F64">
-        <v>47.058</v>
+        <v>47.81700000000001</v>
       </c>
       <c r="G64">
         <v>7.22</v>
@@ -6657,37 +6657,37 @@
         <v>3.49</v>
       </c>
       <c r="M64">
-        <v>11.0962764</v>
+        <v>11.2752486</v>
       </c>
       <c r="N64">
-        <v>-7.6062764</v>
+        <v>-7.785248600000003</v>
       </c>
       <c r="O64">
-        <v>-1.14094146</v>
+        <v>-1.16778729</v>
       </c>
       <c r="P64">
-        <v>-6.46533494</v>
+        <v>-6.617461310000002</v>
       </c>
       <c r="Q64">
-        <v>-2.70533494</v>
+        <v>-2.857461310000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1541071138057883</v>
+        <v>0.1570343330978366</v>
       </c>
       <c r="T64">
-        <v>2.054545926941214</v>
+        <v>2.110074195236922</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0471779884646709</v>
+        <v>0.04642913150491421</v>
       </c>
       <c r="W64">
-        <v>0.2246754303200306</v>
+        <v>0.2248520107911412</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3145199230978061</v>
+        <v>0.3095275433660948</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1997594700446185</v>
+        <v>0.2016594700446185</v>
       </c>
       <c r="C65">
-        <v>-20.98702982378676</v>
+        <v>-21.98508455253785</v>
       </c>
       <c r="D65">
-        <v>19.60997017621325</v>
+        <v>19.37091544746216</v>
       </c>
       <c r="E65">
-        <v>7.01700000000001</v>
+        <v>7.77600000000001</v>
       </c>
       <c r="F65">
-        <v>47.81700000000001</v>
+        <v>48.57600000000001</v>
       </c>
       <c r="G65">
         <v>7.22</v>
@@ -6739,37 +6739,37 @@
         <v>3.49</v>
       </c>
       <c r="M65">
-        <v>11.2752486</v>
+        <v>11.4542208</v>
       </c>
       <c r="N65">
-        <v>-7.785248600000003</v>
+        <v>-7.964220800000001</v>
       </c>
       <c r="O65">
-        <v>-1.16778729</v>
+        <v>-1.19463312</v>
       </c>
       <c r="P65">
-        <v>-6.617461310000002</v>
+        <v>-6.769587680000001</v>
       </c>
       <c r="Q65">
-        <v>-2.857461310000002</v>
+        <v>-3.009587680000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1570343330978366</v>
+        <v>0.1601241756838876</v>
       </c>
       <c r="T65">
-        <v>2.110074195236922</v>
+        <v>2.168687367326836</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04642913150491421</v>
+        <v>0.04570367632514993</v>
       </c>
       <c r="W65">
-        <v>0.2248520107911412</v>
+        <v>0.2250230731225296</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3095275433660948</v>
+        <v>0.3046911755009996</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2016594700446185</v>
+        <v>0.2035594700446185</v>
       </c>
       <c r="C66">
-        <v>-21.98508455253785</v>
+        <v>-22.97738109784044</v>
       </c>
       <c r="D66">
-        <v>19.37091544746216</v>
+        <v>19.13761890215957</v>
       </c>
       <c r="E66">
-        <v>7.77600000000001</v>
+        <v>8.535000000000011</v>
       </c>
       <c r="F66">
-        <v>48.57600000000001</v>
+        <v>49.33500000000001</v>
       </c>
       <c r="G66">
         <v>7.22</v>
@@ -6821,37 +6821,37 @@
         <v>3.49</v>
       </c>
       <c r="M66">
-        <v>11.4542208</v>
+        <v>11.633193</v>
       </c>
       <c r="N66">
-        <v>-7.964220800000001</v>
+        <v>-8.143193000000002</v>
       </c>
       <c r="O66">
-        <v>-1.19463312</v>
+        <v>-1.22147895</v>
       </c>
       <c r="P66">
-        <v>-6.769587680000001</v>
+        <v>-6.921714050000002</v>
       </c>
       <c r="Q66">
-        <v>-3.009587680000001</v>
+        <v>-3.161714050000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1601241756838876</v>
+        <v>0.1633905807034273</v>
       </c>
       <c r="T66">
-        <v>2.168687367326836</v>
+        <v>2.230649863536175</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04570367632514993</v>
+        <v>0.04500054284322455</v>
       </c>
       <c r="W66">
-        <v>0.2250230731225296</v>
+        <v>0.2251888719975677</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3046911755009996</v>
+        <v>0.3000036189548303</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2035594700446185</v>
+        <v>0.2054594700446185</v>
       </c>
       <c r="C67">
-        <v>-22.97738109784044</v>
+        <v>-23.96412503250302</v>
       </c>
       <c r="D67">
-        <v>19.13761890215957</v>
+        <v>18.90987496749699</v>
       </c>
       <c r="E67">
-        <v>8.535000000000011</v>
+        <v>9.294000000000011</v>
       </c>
       <c r="F67">
-        <v>49.33500000000001</v>
+        <v>50.09400000000001</v>
       </c>
       <c r="G67">
         <v>7.22</v>
@@ -6903,37 +6903,37 @@
         <v>3.49</v>
       </c>
       <c r="M67">
-        <v>11.633193</v>
+        <v>11.8121652</v>
       </c>
       <c r="N67">
-        <v>-8.143193000000002</v>
+        <v>-8.322165200000002</v>
       </c>
       <c r="O67">
-        <v>-1.22147895</v>
+        <v>-1.24832478</v>
       </c>
       <c r="P67">
-        <v>-6.921714050000002</v>
+        <v>-7.073840420000002</v>
       </c>
       <c r="Q67">
-        <v>-3.161714050000002</v>
+        <v>-3.313840420000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1633905807034273</v>
+        <v>0.1668491271947045</v>
       </c>
       <c r="T67">
-        <v>2.230649863536175</v>
+        <v>2.29625721246371</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04500054284322455</v>
+        <v>0.04431871643650902</v>
       </c>
       <c r="W67">
-        <v>0.2251888719975677</v>
+        <v>0.2253496466642712</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3000036189548303</v>
+        <v>0.2954581095767268</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2054594700446185</v>
+        <v>0.2073594700446185</v>
       </c>
       <c r="C68">
-        <v>-23.96412503250302</v>
+        <v>-24.94551225888054</v>
       </c>
       <c r="D68">
-        <v>18.90987496749699</v>
+        <v>18.68748774111947</v>
       </c>
       <c r="E68">
-        <v>9.294000000000011</v>
+        <v>10.05300000000001</v>
       </c>
       <c r="F68">
-        <v>50.09400000000001</v>
+        <v>50.85300000000001</v>
       </c>
       <c r="G68">
         <v>7.22</v>
@@ -6985,37 +6985,37 @@
         <v>3.49</v>
       </c>
       <c r="M68">
-        <v>11.8121652</v>
+        <v>11.9911374</v>
       </c>
       <c r="N68">
-        <v>-8.322165200000002</v>
+        <v>-8.501137400000003</v>
       </c>
       <c r="O68">
-        <v>-1.24832478</v>
+        <v>-1.27517061</v>
       </c>
       <c r="P68">
-        <v>-7.073840420000002</v>
+        <v>-7.225966790000003</v>
       </c>
       <c r="Q68">
-        <v>-3.313840420000002</v>
+        <v>-3.465966790000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1668491271947045</v>
+        <v>0.170517282564241</v>
       </c>
       <c r="T68">
-        <v>2.29625721246371</v>
+        <v>2.365840764356549</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04431871643650902</v>
+        <v>0.04365724305685963</v>
       </c>
       <c r="W68">
-        <v>0.2253496466642712</v>
+        <v>0.2255056220871925</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2954581095767268</v>
+        <v>0.2910482870457309</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2073594700446185</v>
+        <v>0.2092594700446185</v>
       </c>
       <c r="C69">
-        <v>-24.94551225888054</v>
+        <v>-25.92172957090557</v>
       </c>
       <c r="D69">
-        <v>18.68748774111947</v>
+        <v>18.47027042909444</v>
       </c>
       <c r="E69">
-        <v>10.05300000000001</v>
+        <v>10.81200000000001</v>
       </c>
       <c r="F69">
-        <v>50.85300000000001</v>
+        <v>51.61200000000001</v>
       </c>
       <c r="G69">
         <v>7.22</v>
@@ -7067,37 +7067,37 @@
         <v>3.49</v>
       </c>
       <c r="M69">
-        <v>11.9911374</v>
+        <v>12.1701096</v>
       </c>
       <c r="N69">
-        <v>-8.501137400000003</v>
+        <v>-8.680109600000002</v>
       </c>
       <c r="O69">
-        <v>-1.27517061</v>
+        <v>-1.30201644</v>
       </c>
       <c r="P69">
-        <v>-7.225966790000003</v>
+        <v>-7.378093160000001</v>
       </c>
       <c r="Q69">
-        <v>-3.465966790000003</v>
+        <v>-3.618093160000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.170517282564241</v>
+        <v>0.1744146976443736</v>
       </c>
       <c r="T69">
-        <v>2.365840764356549</v>
+        <v>2.439773288242691</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04365724305685963</v>
+        <v>0.0430152247766117</v>
       </c>
       <c r="W69">
-        <v>0.2255056220871925</v>
+        <v>0.225657009997675</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2910482870457309</v>
+        <v>0.2867681651774113</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2092594700446185</v>
+        <v>0.2111594700446185</v>
       </c>
       <c r="C70">
-        <v>-25.92172957090557</v>
+        <v>-26.89295517737255</v>
       </c>
       <c r="D70">
-        <v>18.47027042909444</v>
+        <v>18.25804482262746</v>
       </c>
       <c r="E70">
-        <v>10.81200000000001</v>
+        <v>11.57100000000001</v>
       </c>
       <c r="F70">
-        <v>51.61200000000001</v>
+        <v>52.37100000000001</v>
       </c>
       <c r="G70">
         <v>7.22</v>
@@ -7149,37 +7149,37 @@
         <v>3.49</v>
       </c>
       <c r="M70">
-        <v>12.1701096</v>
+        <v>12.3490818</v>
       </c>
       <c r="N70">
-        <v>-8.680109600000002</v>
+        <v>-8.859081800000002</v>
       </c>
       <c r="O70">
-        <v>-1.30201644</v>
+        <v>-1.32886227</v>
       </c>
       <c r="P70">
-        <v>-7.378093160000001</v>
+        <v>-7.530219530000002</v>
       </c>
       <c r="Q70">
-        <v>-3.618093160000002</v>
+        <v>-3.770219530000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1744146976443736</v>
+        <v>0.1785635588587082</v>
       </c>
       <c r="T70">
-        <v>2.439773288242691</v>
+        <v>2.518475652379552</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0430152247766117</v>
+        <v>0.0423918157218782</v>
       </c>
       <c r="W70">
-        <v>0.225657009997675</v>
+        <v>0.2258040098527811</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2867681651774113</v>
+        <v>0.2826121048125213</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2111594700446185</v>
+        <v>0.2130594700446185</v>
       </c>
       <c r="C71">
-        <v>-26.89295517737255</v>
+        <v>-27.85935918955637</v>
       </c>
       <c r="D71">
-        <v>18.25804482262746</v>
+        <v>18.05064081044364</v>
       </c>
       <c r="E71">
-        <v>11.57100000000001</v>
+        <v>12.33000000000001</v>
       </c>
       <c r="F71">
-        <v>52.37100000000001</v>
+        <v>53.13000000000001</v>
       </c>
       <c r="G71">
         <v>7.22</v>
@@ -7231,37 +7231,37 @@
         <v>3.49</v>
       </c>
       <c r="M71">
-        <v>12.3490818</v>
+        <v>12.528054</v>
       </c>
       <c r="N71">
-        <v>-8.859081800000002</v>
+        <v>-9.038054000000002</v>
       </c>
       <c r="O71">
-        <v>-1.32886227</v>
+        <v>-1.3557081</v>
       </c>
       <c r="P71">
-        <v>-7.530219530000002</v>
+        <v>-7.682345900000002</v>
       </c>
       <c r="Q71">
-        <v>-3.770219530000002</v>
+        <v>-3.922345900000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1785635588587082</v>
+        <v>0.1829890108206652</v>
       </c>
       <c r="T71">
-        <v>2.518475652379552</v>
+        <v>2.602424840792204</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0423918157218782</v>
+        <v>0.04178621835442279</v>
       </c>
       <c r="W71">
-        <v>0.2258040098527811</v>
+        <v>0.2259468097120271</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2826121048125213</v>
+        <v>0.2785747890294853</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2130594700446185</v>
+        <v>0.2149594700446185</v>
       </c>
       <c r="C72">
-        <v>-27.85935918955637</v>
+        <v>-28.82110407596915</v>
       </c>
       <c r="D72">
-        <v>18.05064081044364</v>
+        <v>17.84789592403086</v>
       </c>
       <c r="E72">
-        <v>12.33000000000001</v>
+        <v>13.08900000000001</v>
       </c>
       <c r="F72">
-        <v>53.13000000000001</v>
+        <v>53.88900000000001</v>
       </c>
       <c r="G72">
         <v>7.22</v>
@@ -7313,37 +7313,37 @@
         <v>3.49</v>
       </c>
       <c r="M72">
-        <v>12.528054</v>
+        <v>12.7070262</v>
       </c>
       <c r="N72">
-        <v>-9.038054000000002</v>
+        <v>-9.217026200000003</v>
       </c>
       <c r="O72">
-        <v>-1.3557081</v>
+        <v>-1.38255393</v>
       </c>
       <c r="P72">
-        <v>-7.682345900000002</v>
+        <v>-7.834472270000003</v>
       </c>
       <c r="Q72">
-        <v>-3.922345900000002</v>
+        <v>-4.074472270000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1829890108206652</v>
+        <v>0.1877196663662054</v>
       </c>
       <c r="T72">
-        <v>2.602424840792204</v>
+        <v>2.692163628405729</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04178621835442279</v>
+        <v>0.04119768006774079</v>
       </c>
       <c r="W72">
-        <v>0.2259468097120271</v>
+        <v>0.2260855870400267</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2785747890294853</v>
+        <v>0.2746512004516052</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2149594700446185</v>
+        <v>0.2168594700446185</v>
       </c>
       <c r="C73">
-        <v>-28.82110407596914</v>
+        <v>-29.77834508681066</v>
       </c>
       <c r="D73">
-        <v>17.84789592403086</v>
+        <v>17.64965491318935</v>
       </c>
       <c r="E73">
-        <v>13.08900000000001</v>
+        <v>13.84800000000001</v>
       </c>
       <c r="F73">
-        <v>53.889</v>
+        <v>54.648</v>
       </c>
       <c r="G73">
         <v>7.22</v>
@@ -7395,37 +7395,37 @@
         <v>3.49</v>
       </c>
       <c r="M73">
-        <v>12.7070262</v>
+        <v>12.8859984</v>
       </c>
       <c r="N73">
-        <v>-9.217026200000001</v>
+        <v>-9.395998400000002</v>
       </c>
       <c r="O73">
-        <v>-1.38255393</v>
+        <v>-1.40939976</v>
       </c>
       <c r="P73">
-        <v>-7.834472270000001</v>
+        <v>-7.986598640000001</v>
       </c>
       <c r="Q73">
-        <v>-4.074472270000001</v>
+        <v>-4.226598640000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1877196663662053</v>
+        <v>0.192788225879284</v>
       </c>
       <c r="T73">
-        <v>2.692163628405728</v>
+        <v>2.788312329420218</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04119768006774079</v>
+        <v>0.04062549006679995</v>
       </c>
       <c r="W73">
-        <v>0.2260855870400267</v>
+        <v>0.2262205094422486</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2746512004516053</v>
+        <v>0.270836600445333</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2168594700446185</v>
+        <v>0.2187594700446185</v>
       </c>
       <c r="C74">
-        <v>-29.77834508681066</v>
+        <v>-30.73123065044247</v>
       </c>
       <c r="D74">
-        <v>17.64965491318935</v>
+        <v>17.45576934955754</v>
       </c>
       <c r="E74">
-        <v>13.84800000000001</v>
+        <v>14.60700000000001</v>
       </c>
       <c r="F74">
-        <v>54.648</v>
+        <v>55.407</v>
       </c>
       <c r="G74">
         <v>7.22</v>
@@ -7477,37 +7477,37 @@
         <v>3.49</v>
       </c>
       <c r="M74">
-        <v>12.8859984</v>
+        <v>13.0649706</v>
       </c>
       <c r="N74">
-        <v>-9.395998400000002</v>
+        <v>-9.5749706</v>
       </c>
       <c r="O74">
-        <v>-1.40939976</v>
+        <v>-1.43624559</v>
       </c>
       <c r="P74">
-        <v>-7.986598640000001</v>
+        <v>-8.13872501</v>
       </c>
       <c r="Q74">
-        <v>-4.226598640000002</v>
+        <v>-4.37872501</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.192788225879284</v>
+        <v>0.1982322342451835</v>
       </c>
       <c r="T74">
-        <v>2.788312329420218</v>
+        <v>2.891583156435781</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04062549006679995</v>
+        <v>0.04006897650424104</v>
       </c>
       <c r="W74">
-        <v>0.2262205094422486</v>
+        <v>0.2263517353403</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.270836600445333</v>
+        <v>0.2671265100282736</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2187594700446185</v>
+        <v>0.2206594700446185</v>
       </c>
       <c r="C75">
-        <v>-30.73123065044247</v>
+        <v>-31.67990274401392</v>
       </c>
       <c r="D75">
-        <v>17.45576934955754</v>
+        <v>17.26609725598608</v>
       </c>
       <c r="E75">
-        <v>14.60700000000001</v>
+        <v>15.36600000000001</v>
       </c>
       <c r="F75">
-        <v>55.407</v>
+        <v>56.166</v>
       </c>
       <c r="G75">
         <v>7.22</v>
@@ -7559,37 +7559,37 @@
         <v>3.49</v>
       </c>
       <c r="M75">
-        <v>13.0649706</v>
+        <v>13.2439428</v>
       </c>
       <c r="N75">
-        <v>-9.5749706</v>
+        <v>-9.753942800000001</v>
       </c>
       <c r="O75">
-        <v>-1.43624559</v>
+        <v>-1.46309142</v>
       </c>
       <c r="P75">
-        <v>-8.13872501</v>
+        <v>-8.290851380000001</v>
       </c>
       <c r="Q75">
-        <v>-4.37872501</v>
+        <v>-4.530851380000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1982322342451835</v>
+        <v>0.2040950124853828</v>
       </c>
       <c r="T75">
-        <v>2.891583156435781</v>
+        <v>3.002797893221773</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04006897650424104</v>
+        <v>0.03952750384877832</v>
       </c>
       <c r="W75">
-        <v>0.2263517353403</v>
+        <v>0.2264794145924581</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2671265100282736</v>
+        <v>0.2635166923251888</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2206594700446185</v>
+        <v>0.2225594700446185</v>
       </c>
       <c r="C76">
-        <v>-31.67990274401392</v>
+        <v>-32.62449724018487</v>
       </c>
       <c r="D76">
-        <v>17.26609725598608</v>
+        <v>17.08050275981514</v>
       </c>
       <c r="E76">
-        <v>15.36600000000001</v>
+        <v>16.12500000000001</v>
       </c>
       <c r="F76">
-        <v>56.166</v>
+        <v>56.925</v>
       </c>
       <c r="G76">
         <v>7.22</v>
@@ -7641,37 +7641,37 @@
         <v>3.49</v>
       </c>
       <c r="M76">
-        <v>13.2439428</v>
+        <v>13.422915</v>
       </c>
       <c r="N76">
-        <v>-9.753942800000001</v>
+        <v>-9.932915000000001</v>
       </c>
       <c r="O76">
-        <v>-1.46309142</v>
+        <v>-1.48993725</v>
       </c>
       <c r="P76">
-        <v>-8.290851380000001</v>
+        <v>-8.442977750000001</v>
       </c>
       <c r="Q76">
-        <v>-4.530851380000001</v>
+        <v>-4.682977750000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2040950124853828</v>
+        <v>0.2104268129847982</v>
       </c>
       <c r="T76">
-        <v>3.002797893221773</v>
+        <v>3.122909808950644</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03952750384877832</v>
+        <v>0.03900047046412795</v>
       </c>
       <c r="W76">
-        <v>0.2264794145924581</v>
+        <v>0.2266036890645587</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2635166923251888</v>
+        <v>0.2600031364275196</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2225594700446185</v>
+        <v>0.2244594700446185</v>
       </c>
       <c r="C77">
-        <v>-32.62449724018487</v>
+        <v>-33.56514423172437</v>
       </c>
       <c r="D77">
-        <v>17.08050275981514</v>
+        <v>16.89885576827563</v>
       </c>
       <c r="E77">
-        <v>16.12500000000001</v>
+        <v>16.88400000000001</v>
       </c>
       <c r="F77">
-        <v>56.925</v>
+        <v>57.684</v>
       </c>
       <c r="G77">
         <v>7.22</v>
@@ -7723,37 +7723,37 @@
         <v>3.49</v>
       </c>
       <c r="M77">
-        <v>13.422915</v>
+        <v>13.6018872</v>
       </c>
       <c r="N77">
-        <v>-9.932915000000001</v>
+        <v>-10.1118872</v>
       </c>
       <c r="O77">
-        <v>-1.48993725</v>
+        <v>-1.51678308</v>
       </c>
       <c r="P77">
-        <v>-8.442977750000001</v>
+        <v>-8.595104120000002</v>
       </c>
       <c r="Q77">
-        <v>-4.682977750000001</v>
+        <v>-4.835104120000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2104268129847982</v>
+        <v>0.2172862635258314</v>
       </c>
       <c r="T77">
-        <v>3.122909808950644</v>
+        <v>3.253031050990255</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03900047046412795</v>
+        <v>0.03848730637907363</v>
       </c>
       <c r="W77">
-        <v>0.2266036890645587</v>
+        <v>0.2267246931558144</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2600031364275196</v>
+        <v>0.2565820425271576</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2244594700446185</v>
+        <v>0.2263594700446185</v>
       </c>
       <c r="C78">
-        <v>-33.56514423172437</v>
+        <v>-34.50196833561542</v>
       </c>
       <c r="D78">
-        <v>16.89885576827563</v>
+        <v>16.72103166438459</v>
       </c>
       <c r="E78">
-        <v>16.88400000000001</v>
+        <v>17.64300000000001</v>
       </c>
       <c r="F78">
-        <v>57.684</v>
+        <v>58.443</v>
       </c>
       <c r="G78">
         <v>7.22</v>
@@ -7805,37 +7805,37 @@
         <v>3.49</v>
       </c>
       <c r="M78">
-        <v>13.6018872</v>
+        <v>13.7808594</v>
       </c>
       <c r="N78">
-        <v>-10.1118872</v>
+        <v>-10.2908594</v>
       </c>
       <c r="O78">
-        <v>-1.51678308</v>
+        <v>-1.54362891</v>
       </c>
       <c r="P78">
-        <v>-8.595104120000002</v>
+        <v>-8.747230490000002</v>
       </c>
       <c r="Q78">
-        <v>-4.835104120000002</v>
+        <v>-4.987230490000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2172862635258314</v>
+        <v>0.2247421880269546</v>
       </c>
       <c r="T78">
-        <v>3.253031050990255</v>
+        <v>3.394467183642005</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03848730637907363</v>
+        <v>0.03798747123129345</v>
       </c>
       <c r="W78">
-        <v>0.2267246931558144</v>
+        <v>0.226842554283661</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2565820425271576</v>
+        <v>0.253249808208623</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2263594700446185</v>
+        <v>0.2282594700446185</v>
       </c>
       <c r="C79">
-        <v>-34.50196833561542</v>
+        <v>-35.435088978159</v>
       </c>
       <c r="D79">
-        <v>16.72103166438459</v>
+        <v>16.54691102184101</v>
       </c>
       <c r="E79">
-        <v>17.64300000000001</v>
+        <v>18.40200000000001</v>
       </c>
       <c r="F79">
-        <v>58.443</v>
+        <v>59.20200000000001</v>
       </c>
       <c r="G79">
         <v>7.22</v>
@@ -7887,37 +7887,37 @@
         <v>3.49</v>
       </c>
       <c r="M79">
-        <v>13.7808594</v>
+        <v>13.9598316</v>
       </c>
       <c r="N79">
-        <v>-10.2908594</v>
+        <v>-10.4698316</v>
       </c>
       <c r="O79">
-        <v>-1.54362891</v>
+        <v>-1.57047474</v>
       </c>
       <c r="P79">
-        <v>-8.747230490000002</v>
+        <v>-8.899356860000001</v>
       </c>
       <c r="Q79">
-        <v>-4.987230490000002</v>
+        <v>-5.139356860000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2247421880269546</v>
+        <v>0.2328759238463615</v>
       </c>
       <c r="T79">
-        <v>3.394467183642005</v>
+        <v>3.548761146534823</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03798747123129345</v>
+        <v>0.03750045236935379</v>
       </c>
       <c r="W79">
-        <v>0.226842554283661</v>
+        <v>0.2269573933313064</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.253249808208623</v>
+        <v>0.250003015795692</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2282594700446185</v>
+        <v>0.2301594700446185</v>
       </c>
       <c r="C80">
-        <v>-35.435088978159</v>
+        <v>-36.36462066244887</v>
       </c>
       <c r="D80">
-        <v>16.54691102184101</v>
+        <v>16.37637933755113</v>
       </c>
       <c r="E80">
-        <v>18.40200000000001</v>
+        <v>19.16100000000001</v>
       </c>
       <c r="F80">
-        <v>59.20200000000001</v>
+        <v>59.96100000000001</v>
       </c>
       <c r="G80">
         <v>7.22</v>
@@ -7969,37 +7969,37 @@
         <v>3.49</v>
       </c>
       <c r="M80">
-        <v>13.9598316</v>
+        <v>14.1388038</v>
       </c>
       <c r="N80">
-        <v>-10.4698316</v>
+        <v>-10.6488038</v>
       </c>
       <c r="O80">
-        <v>-1.57047474</v>
+        <v>-1.59732057</v>
       </c>
       <c r="P80">
-        <v>-8.899356860000001</v>
+        <v>-9.051483230000001</v>
       </c>
       <c r="Q80">
-        <v>-5.139356860000001</v>
+        <v>-5.291483230000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2328759238463615</v>
+        <v>0.2417843011723788</v>
       </c>
       <c r="T80">
-        <v>3.548761146534823</v>
+        <v>3.717749772560292</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03750045236935379</v>
+        <v>0.03702576309885564</v>
       </c>
       <c r="W80">
-        <v>0.2269573933313064</v>
+        <v>0.2270693250612899</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.250003015795692</v>
+        <v>0.2468384206590376</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2301594700446185</v>
+        <v>0.2320594700446185</v>
       </c>
       <c r="C81">
-        <v>-36.36462066244887</v>
+        <v>-37.29067321947534</v>
       </c>
       <c r="D81">
-        <v>16.37637933755113</v>
+        <v>16.20932678052467</v>
       </c>
       <c r="E81">
-        <v>19.16100000000001</v>
+        <v>19.92000000000001</v>
       </c>
       <c r="F81">
-        <v>59.96100000000001</v>
+        <v>60.72000000000001</v>
       </c>
       <c r="G81">
         <v>7.22</v>
@@ -8051,37 +8051,37 @@
         <v>3.49</v>
       </c>
       <c r="M81">
-        <v>14.1388038</v>
+        <v>14.317776</v>
       </c>
       <c r="N81">
-        <v>-10.6488038</v>
+        <v>-10.827776</v>
       </c>
       <c r="O81">
-        <v>-1.59732057</v>
+        <v>-1.6241664</v>
       </c>
       <c r="P81">
-        <v>-9.051483230000001</v>
+        <v>-9.203609600000002</v>
       </c>
       <c r="Q81">
-        <v>-5.291483230000001</v>
+        <v>-5.443609600000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2417843011723788</v>
+        <v>0.2515835162309977</v>
       </c>
       <c r="T81">
-        <v>3.717749772560292</v>
+        <v>3.903637261188306</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03702576309885564</v>
+        <v>0.03656294106011995</v>
       </c>
       <c r="W81">
-        <v>0.2270693250612899</v>
+        <v>0.2271784584980237</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2468384206590376</v>
+        <v>0.2437529404007996</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2320594700446185</v>
+        <v>0.2339594700446185</v>
       </c>
       <c r="C82">
-        <v>-37.29067321947534</v>
+        <v>-38.21335204401547</v>
       </c>
       <c r="D82">
-        <v>16.20932678052467</v>
+        <v>16.04564795598454</v>
       </c>
       <c r="E82">
-        <v>19.92000000000001</v>
+        <v>20.67900000000001</v>
       </c>
       <c r="F82">
-        <v>60.72000000000001</v>
+        <v>61.47900000000001</v>
       </c>
       <c r="G82">
         <v>7.22</v>
@@ -8133,37 +8133,37 @@
         <v>3.49</v>
       </c>
       <c r="M82">
-        <v>14.317776</v>
+        <v>14.4967482</v>
       </c>
       <c r="N82">
-        <v>-10.827776</v>
+        <v>-11.0067482</v>
       </c>
       <c r="O82">
-        <v>-1.6241664</v>
+        <v>-1.65101223</v>
       </c>
       <c r="P82">
-        <v>-9.203609600000002</v>
+        <v>-9.355735970000001</v>
       </c>
       <c r="Q82">
-        <v>-5.443609600000002</v>
+        <v>-5.595735970000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2515835162309977</v>
+        <v>0.2624142276115766</v>
       </c>
       <c r="T82">
-        <v>3.903637261188306</v>
+        <v>4.109091853882427</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03656294106011995</v>
+        <v>0.03611154672604439</v>
       </c>
       <c r="W82">
-        <v>0.2271784584980237</v>
+        <v>0.2272848972819987</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2437529404007996</v>
+        <v>0.240743644840296</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2339594700446185</v>
+        <v>0.2358594700446185</v>
       </c>
       <c r="C83">
-        <v>-38.21335204401547</v>
+        <v>-39.13275831637439</v>
       </c>
       <c r="D83">
-        <v>16.04564795598454</v>
+        <v>15.88524168362562</v>
       </c>
       <c r="E83">
-        <v>20.67900000000001</v>
+        <v>21.43800000000001</v>
       </c>
       <c r="F83">
-        <v>61.47900000000001</v>
+        <v>62.23800000000001</v>
       </c>
       <c r="G83">
         <v>7.22</v>
@@ -8215,37 +8215,37 @@
         <v>3.49</v>
       </c>
       <c r="M83">
-        <v>14.4967482</v>
+        <v>14.6757204</v>
       </c>
       <c r="N83">
-        <v>-11.0067482</v>
+        <v>-11.1857204</v>
       </c>
       <c r="O83">
-        <v>-1.65101223</v>
+        <v>-1.67785806</v>
       </c>
       <c r="P83">
-        <v>-9.355735970000001</v>
+        <v>-9.507862340000003</v>
       </c>
       <c r="Q83">
-        <v>-5.595735970000002</v>
+        <v>-5.747862340000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2624142276115766</v>
+        <v>0.2744483513677752</v>
       </c>
       <c r="T83">
-        <v>4.109091853882427</v>
+        <v>4.337374734653674</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03611154672604439</v>
+        <v>0.03567116200987312</v>
       </c>
       <c r="W83">
-        <v>0.2272848972819987</v>
+        <v>0.2273887399980719</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.240743644840296</v>
+        <v>0.2378077467324875</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2358594700446185</v>
+        <v>0.2377594700446185</v>
       </c>
       <c r="C84">
-        <v>-39.13275831637439</v>
+        <v>-40.04898921095788</v>
       </c>
       <c r="D84">
-        <v>15.88524168362562</v>
+        <v>15.72801078904212</v>
       </c>
       <c r="E84">
-        <v>21.43800000000001</v>
+        <v>22.19700000000001</v>
       </c>
       <c r="F84">
-        <v>62.23800000000001</v>
+        <v>62.99700000000001</v>
       </c>
       <c r="G84">
         <v>7.22</v>
@@ -8297,37 +8297,37 @@
         <v>3.49</v>
       </c>
       <c r="M84">
-        <v>14.6757204</v>
+        <v>14.8546926</v>
       </c>
       <c r="N84">
-        <v>-11.1857204</v>
+        <v>-11.3646926</v>
       </c>
       <c r="O84">
-        <v>-1.67785806</v>
+        <v>-1.70470389</v>
       </c>
       <c r="P84">
-        <v>-9.507862340000003</v>
+        <v>-9.65998871</v>
       </c>
       <c r="Q84">
-        <v>-5.747862340000003</v>
+        <v>-5.899988710000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2744483513677752</v>
+        <v>0.2878982543894091</v>
       </c>
       <c r="T84">
-        <v>4.337374734653674</v>
+        <v>4.592514424927419</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03567116200987312</v>
+        <v>0.03524138897360959</v>
       </c>
       <c r="W84">
-        <v>0.2273887399980719</v>
+        <v>0.2274900804800229</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2378077467324875</v>
+        <v>0.2349425931573973</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2377594700446185</v>
+        <v>0.2396594700446186</v>
       </c>
       <c r="C85">
-        <v>-40.04898921095788</v>
+        <v>-40.96213809257974</v>
       </c>
       <c r="D85">
-        <v>15.72801078904212</v>
+        <v>15.57386190742028</v>
       </c>
       <c r="E85">
-        <v>22.19700000000001</v>
+        <v>22.95600000000001</v>
       </c>
       <c r="F85">
-        <v>62.99700000000001</v>
+        <v>63.75600000000001</v>
       </c>
       <c r="G85">
         <v>7.22</v>
@@ -8379,37 +8379,37 @@
         <v>3.49</v>
       </c>
       <c r="M85">
-        <v>14.8546926</v>
+        <v>15.0336648</v>
       </c>
       <c r="N85">
-        <v>-11.3646926</v>
+        <v>-11.5436648</v>
       </c>
       <c r="O85">
-        <v>-1.70470389</v>
+        <v>-1.73154972</v>
       </c>
       <c r="P85">
-        <v>-9.65998871</v>
+        <v>-9.812115080000002</v>
       </c>
       <c r="Q85">
-        <v>-5.899988710000001</v>
+        <v>-6.052115080000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2878982543894091</v>
+        <v>0.3030293952887473</v>
       </c>
       <c r="T85">
-        <v>4.592514424927419</v>
+        <v>4.879546576485384</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03524138897360959</v>
+        <v>0.03482184862868567</v>
       </c>
       <c r="W85">
-        <v>0.2274900804800229</v>
+        <v>0.2275890080933559</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2349425931573973</v>
+        <v>0.2321456575245711</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2396594700446185</v>
+        <v>0.2415594700446185</v>
       </c>
       <c r="C86">
-        <v>-40.96213809257971</v>
+        <v>-41.87229470133716</v>
       </c>
       <c r="D86">
-        <v>15.57386190742029</v>
+        <v>15.42270529866284</v>
       </c>
       <c r="E86">
-        <v>22.956</v>
+        <v>23.715</v>
       </c>
       <c r="F86">
-        <v>63.756</v>
+        <v>64.515</v>
       </c>
       <c r="G86">
         <v>7.22</v>
@@ -8461,37 +8461,37 @@
         <v>3.49</v>
       </c>
       <c r="M86">
-        <v>15.0336648</v>
+        <v>15.212637</v>
       </c>
       <c r="N86">
-        <v>-11.5436648</v>
+        <v>-11.722637</v>
       </c>
       <c r="O86">
-        <v>-1.73154972</v>
+        <v>-1.75839555</v>
       </c>
       <c r="P86">
-        <v>-9.81211508</v>
+        <v>-9.964241450000001</v>
       </c>
       <c r="Q86">
-        <v>-6.05211508</v>
+        <v>-6.204241450000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3030293952887471</v>
+        <v>0.3201780216413302</v>
       </c>
       <c r="T86">
-        <v>4.879546576485381</v>
+        <v>5.204849681584406</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03482184862868567</v>
+        <v>0.03441217982128936</v>
       </c>
       <c r="W86">
-        <v>0.2275890080933559</v>
+        <v>0.22768560799814</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2321456575245712</v>
+        <v>0.2294145321419291</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2415594700446185</v>
+        <v>0.2434594700446185</v>
       </c>
       <c r="C87">
-        <v>-41.87229470133716</v>
+        <v>-42.77954532682374</v>
       </c>
       <c r="D87">
-        <v>15.42270529866284</v>
+        <v>15.27445467317626</v>
       </c>
       <c r="E87">
-        <v>23.715</v>
+        <v>24.474</v>
       </c>
       <c r="F87">
-        <v>64.515</v>
+        <v>65.274</v>
       </c>
       <c r="G87">
         <v>7.22</v>
@@ -8543,37 +8543,37 @@
         <v>3.49</v>
       </c>
       <c r="M87">
-        <v>15.212637</v>
+        <v>15.3916092</v>
       </c>
       <c r="N87">
-        <v>-11.722637</v>
+        <v>-11.9016092</v>
       </c>
       <c r="O87">
-        <v>-1.75839555</v>
+        <v>-1.78524138</v>
       </c>
       <c r="P87">
-        <v>-9.964241450000001</v>
+        <v>-10.11636782</v>
       </c>
       <c r="Q87">
-        <v>-6.204241450000001</v>
+        <v>-6.356367820000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3201780216413302</v>
+        <v>0.3397764517585681</v>
       </c>
       <c r="T87">
-        <v>5.204849681584406</v>
+        <v>5.576624658840435</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03441217982128936</v>
+        <v>0.03401203819546041</v>
       </c>
       <c r="W87">
-        <v>0.22768560799814</v>
+        <v>0.2277799613935104</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2294145321419291</v>
+        <v>0.2267469213030695</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2434594700446185</v>
+        <v>0.2453594700446185</v>
       </c>
       <c r="C88">
-        <v>-42.77954532682374</v>
+        <v>-43.68397297238997</v>
       </c>
       <c r="D88">
-        <v>15.27445467317626</v>
+        <v>15.12902702761003</v>
       </c>
       <c r="E88">
-        <v>24.474</v>
+        <v>25.233</v>
       </c>
       <c r="F88">
-        <v>65.274</v>
+        <v>66.033</v>
       </c>
       <c r="G88">
         <v>7.22</v>
@@ -8625,37 +8625,37 @@
         <v>3.49</v>
       </c>
       <c r="M88">
-        <v>15.3916092</v>
+        <v>15.5705814</v>
       </c>
       <c r="N88">
-        <v>-11.9016092</v>
+        <v>-12.0805814</v>
       </c>
       <c r="O88">
-        <v>-1.78524138</v>
+        <v>-1.81208721</v>
       </c>
       <c r="P88">
-        <v>-10.11636782</v>
+        <v>-10.26849419</v>
       </c>
       <c r="Q88">
-        <v>-6.356367820000001</v>
+        <v>-6.508494190000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3397764517585681</v>
+        <v>0.3623900249707657</v>
       </c>
       <c r="T88">
-        <v>5.576624658840435</v>
+        <v>6.005595786443546</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03401203819546041</v>
+        <v>0.0336210952276965</v>
       </c>
       <c r="W88">
-        <v>0.2277799613935104</v>
+        <v>0.2278721457453092</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2267469213030695</v>
+        <v>0.2241406348513101</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2453594700446185</v>
+        <v>0.2472594700446185</v>
       </c>
       <c r="C89">
-        <v>-43.68397297238997</v>
+        <v>-44.58565751010912</v>
       </c>
       <c r="D89">
-        <v>15.12902702761003</v>
+        <v>14.98634248989089</v>
       </c>
       <c r="E89">
-        <v>25.233</v>
+        <v>25.992</v>
       </c>
       <c r="F89">
-        <v>66.033</v>
+        <v>66.792</v>
       </c>
       <c r="G89">
         <v>7.22</v>
@@ -8707,37 +8707,37 @@
         <v>3.49</v>
       </c>
       <c r="M89">
-        <v>15.5705814</v>
+        <v>15.7495536</v>
       </c>
       <c r="N89">
-        <v>-12.0805814</v>
+        <v>-12.2595536</v>
       </c>
       <c r="O89">
-        <v>-1.81208721</v>
+        <v>-1.83893304</v>
       </c>
       <c r="P89">
-        <v>-10.26849419</v>
+        <v>-10.42062056</v>
       </c>
       <c r="Q89">
-        <v>-6.508494190000002</v>
+        <v>-6.66062056</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3623900249707657</v>
+        <v>0.3887725270516629</v>
       </c>
       <c r="T89">
-        <v>6.005595786443546</v>
+        <v>6.506062101980509</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0336210952276965</v>
+        <v>0.03323903732738177</v>
       </c>
       <c r="W89">
-        <v>0.2278721457453092</v>
+        <v>0.2279622349982034</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2241406348513101</v>
+        <v>0.2215935821825452</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2472594700446185</v>
+        <v>0.2491594700446185</v>
       </c>
       <c r="C90">
-        <v>-44.58565751010912</v>
+        <v>-45.48467582705567</v>
       </c>
       <c r="D90">
-        <v>14.98634248989089</v>
+        <v>14.84632417294433</v>
       </c>
       <c r="E90">
-        <v>25.992</v>
+        <v>26.751</v>
       </c>
       <c r="F90">
-        <v>66.792</v>
+        <v>67.551</v>
       </c>
       <c r="G90">
         <v>7.22</v>
@@ -8789,37 +8789,37 @@
         <v>3.49</v>
       </c>
       <c r="M90">
-        <v>15.7495536</v>
+        <v>15.9285258</v>
       </c>
       <c r="N90">
-        <v>-12.2595536</v>
+        <v>-12.4385258</v>
       </c>
       <c r="O90">
-        <v>-1.83893304</v>
+        <v>-1.86577887</v>
       </c>
       <c r="P90">
-        <v>-10.42062056</v>
+        <v>-10.57274693</v>
       </c>
       <c r="Q90">
-        <v>-6.66062056</v>
+        <v>-6.812746930000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3887725270516629</v>
+        <v>0.419951847692723</v>
       </c>
       <c r="T90">
-        <v>6.506062101980509</v>
+        <v>7.097522293069646</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03323903732738177</v>
+        <v>0.03286556499786063</v>
       </c>
       <c r="W90">
-        <v>0.2279622349982034</v>
+        <v>0.2280502997735045</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2215935821825452</v>
+        <v>0.2191037666524042</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2491594700446185</v>
+        <v>0.2510594700446185</v>
       </c>
       <c r="C91">
-        <v>-45.48467582705567</v>
+        <v>-46.38110196345983</v>
       </c>
       <c r="D91">
-        <v>14.84632417294433</v>
+        <v>14.70889803654018</v>
       </c>
       <c r="E91">
-        <v>26.751</v>
+        <v>27.51000000000001</v>
       </c>
       <c r="F91">
-        <v>67.551</v>
+        <v>68.31</v>
       </c>
       <c r="G91">
         <v>7.22</v>
@@ -8871,37 +8871,37 @@
         <v>3.49</v>
       </c>
       <c r="M91">
-        <v>15.9285258</v>
+        <v>16.107498</v>
       </c>
       <c r="N91">
-        <v>-12.4385258</v>
+        <v>-12.617498</v>
       </c>
       <c r="O91">
-        <v>-1.86577887</v>
+        <v>-1.8926247</v>
       </c>
       <c r="P91">
-        <v>-10.57274693</v>
+        <v>-10.7248733</v>
       </c>
       <c r="Q91">
-        <v>-6.812746930000001</v>
+        <v>-6.964873299999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.419951847692723</v>
+        <v>0.4573670324619955</v>
       </c>
       <c r="T91">
-        <v>7.097522293069646</v>
+        <v>7.807274522376613</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03286556499786063</v>
+        <v>0.03250039205343996</v>
       </c>
       <c r="W91">
-        <v>0.2280502997735045</v>
+        <v>0.2281364075537989</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2191037666524042</v>
+        <v>0.2166692803562664</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2510594700446185</v>
+        <v>0.2529594700446185</v>
       </c>
       <c r="C92">
-        <v>-46.38110196345983</v>
+        <v>-47.27500724325903</v>
       </c>
       <c r="D92">
-        <v>14.70889803654018</v>
+        <v>14.57399275674097</v>
       </c>
       <c r="E92">
-        <v>27.51000000000001</v>
+        <v>28.26900000000001</v>
       </c>
       <c r="F92">
-        <v>68.31</v>
+        <v>69.069</v>
       </c>
       <c r="G92">
         <v>7.22</v>
@@ -8953,37 +8953,37 @@
         <v>3.49</v>
       </c>
       <c r="M92">
-        <v>16.107498</v>
+        <v>16.2864702</v>
       </c>
       <c r="N92">
-        <v>-12.617498</v>
+        <v>-12.7964702</v>
       </c>
       <c r="O92">
-        <v>-1.8926247</v>
+        <v>-1.91947053</v>
       </c>
       <c r="P92">
-        <v>-10.7248733</v>
+        <v>-10.87699967</v>
       </c>
       <c r="Q92">
-        <v>-6.964873299999999</v>
+        <v>-7.11699967</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4573670324619955</v>
+        <v>0.5030967027355505</v>
       </c>
       <c r="T92">
-        <v>7.807274522376613</v>
+        <v>8.674749469307347</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03250039205343996</v>
+        <v>0.03214324488801754</v>
       </c>
       <c r="W92">
-        <v>0.2281364075537989</v>
+        <v>0.2282206228554055</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2166692803562664</v>
+        <v>0.2142882992534503</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2529594700446185</v>
+        <v>0.2548594700446186</v>
       </c>
       <c r="C93">
-        <v>-47.27500724325903</v>
+        <v>-48.16646039753087</v>
       </c>
       <c r="D93">
-        <v>14.57399275674097</v>
+        <v>14.44153960246913</v>
       </c>
       <c r="E93">
-        <v>28.26900000000001</v>
+        <v>29.02800000000001</v>
       </c>
       <c r="F93">
-        <v>69.069</v>
+        <v>69.828</v>
       </c>
       <c r="G93">
         <v>7.22</v>
@@ -9035,37 +9035,37 @@
         <v>3.49</v>
       </c>
       <c r="M93">
-        <v>16.2864702</v>
+        <v>16.4654424</v>
       </c>
       <c r="N93">
-        <v>-12.7964702</v>
+        <v>-12.9754424</v>
       </c>
       <c r="O93">
-        <v>-1.91947053</v>
+        <v>-1.94631636</v>
       </c>
       <c r="P93">
-        <v>-10.87699967</v>
+        <v>-11.02912604</v>
       </c>
       <c r="Q93">
-        <v>-7.11699967</v>
+        <v>-7.269126040000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5030967027355505</v>
+        <v>0.5602587905774945</v>
       </c>
       <c r="T93">
-        <v>8.674749469307347</v>
+        <v>9.759093152970769</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03214324488801754</v>
+        <v>0.03179386179140865</v>
       </c>
       <c r="W93">
-        <v>0.2282206228554055</v>
+        <v>0.2283030073895859</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2142882992534503</v>
+        <v>0.211959078609391</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2548594700446186</v>
+        <v>0.2567594700446185</v>
       </c>
       <c r="C94">
-        <v>-48.16646039753087</v>
+        <v>-49.05552768125551</v>
       </c>
       <c r="D94">
-        <v>14.44153960246913</v>
+        <v>14.3114723187445</v>
       </c>
       <c r="E94">
-        <v>29.02800000000001</v>
+        <v>29.78700000000001</v>
       </c>
       <c r="F94">
-        <v>69.828</v>
+        <v>70.587</v>
       </c>
       <c r="G94">
         <v>7.22</v>
@@ -9117,37 +9117,37 @@
         <v>3.49</v>
       </c>
       <c r="M94">
-        <v>16.4654424</v>
+        <v>16.6444146</v>
       </c>
       <c r="N94">
-        <v>-12.9754424</v>
+        <v>-13.1544146</v>
       </c>
       <c r="O94">
-        <v>-1.94631636</v>
+        <v>-1.97316219</v>
       </c>
       <c r="P94">
-        <v>-11.02912604</v>
+        <v>-11.18125241</v>
       </c>
       <c r="Q94">
-        <v>-7.269126040000002</v>
+        <v>-7.421252410000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5602587905774945</v>
+        <v>0.6337529035171366</v>
       </c>
       <c r="T94">
-        <v>9.759093152970769</v>
+        <v>11.15324931768088</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03179386179140865</v>
+        <v>0.0314519923097806</v>
       </c>
       <c r="W94">
-        <v>0.2283030073895859</v>
+        <v>0.2283836202133538</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.211959078609391</v>
+        <v>0.2096799487318707</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2567594700446185</v>
+        <v>0.2586594700446185</v>
       </c>
       <c r="C95">
-        <v>-49.05552768125551</v>
+        <v>-49.94227298382492</v>
       </c>
       <c r="D95">
-        <v>14.3114723187445</v>
+        <v>14.18372701617509</v>
       </c>
       <c r="E95">
-        <v>29.78700000000001</v>
+        <v>30.54600000000001</v>
       </c>
       <c r="F95">
-        <v>70.587</v>
+        <v>71.346</v>
       </c>
       <c r="G95">
         <v>7.22</v>
@@ -9199,37 +9199,37 @@
         <v>3.49</v>
       </c>
       <c r="M95">
-        <v>16.6444146</v>
+        <v>16.8233868</v>
       </c>
       <c r="N95">
-        <v>-13.1544146</v>
+        <v>-13.3333868</v>
       </c>
       <c r="O95">
-        <v>-1.97316219</v>
+        <v>-2.00000802</v>
       </c>
       <c r="P95">
-        <v>-11.18125241</v>
+        <v>-11.33337878</v>
       </c>
       <c r="Q95">
-        <v>-7.421252410000001</v>
+        <v>-7.573378780000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6337529035171366</v>
+        <v>0.7317450541033262</v>
       </c>
       <c r="T95">
-        <v>11.15324931768088</v>
+        <v>13.01212420396103</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0314519923097806</v>
+        <v>0.03111739664691059</v>
       </c>
       <c r="W95">
-        <v>0.2283836202133538</v>
+        <v>0.2284625178706585</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2096799487318707</v>
+        <v>0.207449310979404</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2586594700446185</v>
+        <v>0.2605594700446185</v>
       </c>
       <c r="C96">
-        <v>-49.94227298382492</v>
+        <v>-50.82675793368595</v>
       </c>
       <c r="D96">
-        <v>14.18372701617509</v>
+        <v>14.05824206631405</v>
       </c>
       <c r="E96">
-        <v>30.54600000000001</v>
+        <v>31.30500000000001</v>
       </c>
       <c r="F96">
-        <v>71.346</v>
+        <v>72.105</v>
       </c>
       <c r="G96">
         <v>7.22</v>
@@ -9281,37 +9281,37 @@
         <v>3.49</v>
       </c>
       <c r="M96">
-        <v>16.8233868</v>
+        <v>17.002359</v>
       </c>
       <c r="N96">
-        <v>-13.3333868</v>
+        <v>-13.512359</v>
       </c>
       <c r="O96">
-        <v>-2.00000802</v>
+        <v>-2.02685385</v>
       </c>
       <c r="P96">
-        <v>-11.33337878</v>
+        <v>-11.48550515</v>
       </c>
       <c r="Q96">
-        <v>-7.573378780000001</v>
+        <v>-7.725505150000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7317450541033262</v>
+        <v>0.8689340649239918</v>
       </c>
       <c r="T96">
-        <v>13.01212420396103</v>
+        <v>15.61454904475324</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03111739664691059</v>
+        <v>0.0307898451032589</v>
       </c>
       <c r="W96">
-        <v>0.2284625178706585</v>
+        <v>0.2285397545246516</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.207449310979404</v>
+        <v>0.205265634021726</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2605594700446185</v>
+        <v>0.2624594700446186</v>
       </c>
       <c r="C97">
-        <v>-50.82675793368595</v>
+        <v>-51.70904199747739</v>
       </c>
       <c r="D97">
-        <v>14.05824206631405</v>
+        <v>13.93495800252262</v>
       </c>
       <c r="E97">
-        <v>31.30500000000001</v>
+        <v>32.06400000000001</v>
       </c>
       <c r="F97">
-        <v>72.105</v>
+        <v>72.864</v>
       </c>
       <c r="G97">
         <v>7.22</v>
@@ -9363,37 +9363,37 @@
         <v>3.49</v>
       </c>
       <c r="M97">
-        <v>17.002359</v>
+        <v>17.1813312</v>
       </c>
       <c r="N97">
-        <v>-13.512359</v>
+        <v>-13.6913312</v>
       </c>
       <c r="O97">
-        <v>-2.02685385</v>
+        <v>-2.05369968</v>
       </c>
       <c r="P97">
-        <v>-11.48550515</v>
+        <v>-11.63763152</v>
       </c>
       <c r="Q97">
-        <v>-7.725505150000002</v>
+        <v>-7.877631520000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8689340649239918</v>
+        <v>1.07471758115499</v>
       </c>
       <c r="T97">
-        <v>15.61454904475324</v>
+        <v>19.51818630594156</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0307898451032589</v>
+        <v>0.03046911755009996</v>
       </c>
       <c r="W97">
-        <v>0.2285397545246516</v>
+        <v>0.2286153820816864</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.205265634021726</v>
+        <v>0.2031274503339997</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2624594700446185</v>
+        <v>0.2643594700446185</v>
       </c>
       <c r="C98">
-        <v>-51.70904199747738</v>
+        <v>-52.58918257399593</v>
       </c>
       <c r="D98">
-        <v>13.93495800252263</v>
+        <v>13.81381742600407</v>
       </c>
       <c r="E98">
-        <v>32.06400000000001</v>
+        <v>32.82300000000001</v>
       </c>
       <c r="F98">
-        <v>72.864</v>
+        <v>73.623</v>
       </c>
       <c r="G98">
         <v>7.22</v>
@@ -9445,37 +9445,37 @@
         <v>3.49</v>
       </c>
       <c r="M98">
-        <v>17.1813312</v>
+        <v>17.3603034</v>
       </c>
       <c r="N98">
-        <v>-13.6913312</v>
+        <v>-13.8703034</v>
       </c>
       <c r="O98">
-        <v>-2.05369968</v>
+        <v>-2.08054551</v>
       </c>
       <c r="P98">
-        <v>-11.63763152</v>
+        <v>-11.78975789</v>
       </c>
       <c r="Q98">
-        <v>-7.877631520000003</v>
+        <v>-8.029757890000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.074717581154988</v>
+        <v>1.41769010820665</v>
       </c>
       <c r="T98">
-        <v>19.51818630594151</v>
+        <v>26.02424840792201</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03046911755009996</v>
+        <v>0.0301550029361814</v>
       </c>
       <c r="W98">
-        <v>0.2286153820816864</v>
+        <v>0.2286894503076484</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2031274503339997</v>
+        <v>0.2010333529078761</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2643594700446185</v>
+        <v>0.2662594700446185</v>
       </c>
       <c r="C99">
-        <v>-52.58918257399593</v>
+        <v>-53.4672350833034</v>
       </c>
       <c r="D99">
-        <v>13.81381742600407</v>
+        <v>13.6947649166966</v>
       </c>
       <c r="E99">
-        <v>32.82300000000001</v>
+        <v>33.58200000000001</v>
       </c>
       <c r="F99">
-        <v>73.623</v>
+        <v>74.38200000000001</v>
       </c>
       <c r="G99">
         <v>7.22</v>
@@ -9527,37 +9527,37 @@
         <v>3.49</v>
       </c>
       <c r="M99">
-        <v>17.3603034</v>
+        <v>17.5392756</v>
       </c>
       <c r="N99">
-        <v>-13.8703034</v>
+        <v>-14.0492756</v>
       </c>
       <c r="O99">
-        <v>-2.08054551</v>
+        <v>-2.10739134</v>
       </c>
       <c r="P99">
-        <v>-11.78975789</v>
+        <v>-11.94188426</v>
       </c>
       <c r="Q99">
-        <v>-8.029757890000003</v>
+        <v>-8.181884260000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.41769010820665</v>
+        <v>2.103635162309975</v>
       </c>
       <c r="T99">
-        <v>26.02424840792201</v>
+        <v>39.03637261188302</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0301550029361814</v>
+        <v>0.02984729882458771</v>
       </c>
       <c r="W99">
-        <v>0.2286894503076484</v>
+        <v>0.2287620069371622</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2010333529078761</v>
+        <v>0.1989819921639181</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2662594700446185</v>
+        <v>0.2681594700446185</v>
       </c>
       <c r="C100">
-        <v>-53.4672350833034</v>
+        <v>-54.34325305126538</v>
       </c>
       <c r="D100">
-        <v>13.6947649166966</v>
+        <v>13.57774694873462</v>
       </c>
       <c r="E100">
-        <v>33.58200000000001</v>
+        <v>34.34100000000001</v>
       </c>
       <c r="F100">
-        <v>74.38200000000001</v>
+        <v>75.14100000000001</v>
       </c>
       <c r="G100">
         <v>7.22</v>
@@ -9609,37 +9609,37 @@
         <v>3.49</v>
       </c>
       <c r="M100">
-        <v>17.5392756</v>
+        <v>17.7182478</v>
       </c>
       <c r="N100">
-        <v>-14.0492756</v>
+        <v>-14.2282478</v>
       </c>
       <c r="O100">
-        <v>-2.10739134</v>
+        <v>-2.13423717</v>
       </c>
       <c r="P100">
-        <v>-11.94188426</v>
+        <v>-12.09401063</v>
       </c>
       <c r="Q100">
-        <v>-8.181884260000002</v>
+        <v>-8.33401063</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.103635162309975</v>
+        <v>4.16147032461995</v>
       </c>
       <c r="T100">
-        <v>39.03637261188302</v>
+        <v>78.07274522376603</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02984729882458771</v>
+        <v>0.02954581095767269</v>
       </c>
       <c r="W100">
-        <v>0.2287620069371622</v>
+        <v>0.2288330977761808</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1989819921639181</v>
+        <v>0.1969720730511513</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2681594700446185</v>
-      </c>
-      <c r="C101">
-        <v>-54.34325305126538</v>
-      </c>
-      <c r="D101">
-        <v>13.57774694873462</v>
-      </c>
-      <c r="E101">
-        <v>34.34100000000001</v>
-      </c>
-      <c r="F101">
-        <v>75.14100000000001</v>
-      </c>
-      <c r="G101">
-        <v>7.22</v>
-      </c>
-      <c r="H101">
-        <v>35.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.25</v>
-      </c>
-      <c r="K101">
-        <v>3.76</v>
-      </c>
-      <c r="L101">
-        <v>3.49</v>
-      </c>
-      <c r="M101">
-        <v>17.7182478</v>
-      </c>
-      <c r="N101">
-        <v>-14.2282478</v>
-      </c>
-      <c r="O101">
-        <v>-2.13423717</v>
-      </c>
-      <c r="P101">
-        <v>-12.09401063</v>
-      </c>
-      <c r="Q101">
-        <v>-8.33401063</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.16147032461995</v>
-      </c>
-      <c r="T101">
-        <v>78.07274522376603</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02954581095767269</v>
-      </c>
-      <c r="W101">
-        <v>0.2288330977761808</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1969720730511513</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
